--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,22 +468,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C2" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.24</v>
+        <v>-0.53</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.44</v>
+        <v>-1.47</v>
       </c>
       <c r="F2" t="n">
         <v>49.42</v>
       </c>
       <c r="G2" t="n">
-        <v>-55.95</v>
+        <v>-62.32</v>
       </c>
     </row>
     <row r="3">
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="D2" t="n">
-        <v>42.5</v>
+        <v>42.3</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.24</v>
+        <v>-0.53</v>
       </c>
     </row>
   </sheetData>
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R430"/>
+  <dimension ref="A1:R458"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16940,8 +16940,12 @@
       <c r="J312" t="n">
         <v>0.26</v>
       </c>
-      <c r="K312" t="inlineStr"/>
-      <c r="L312" t="inlineStr"/>
+      <c r="K312" t="n">
+        <v>2270</v>
+      </c>
+      <c r="L312" t="n">
+        <v>-62.32</v>
+      </c>
       <c r="M312" t="inlineStr"/>
       <c r="N312" t="inlineStr"/>
       <c r="O312" t="inlineStr"/>
@@ -22772,6 +22776,1390 @@
       <c r="P430" t="inlineStr"/>
       <c r="Q430" t="inlineStr"/>
       <c r="R430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>539</v>
+      </c>
+      <c r="F431" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H431" t="n">
+        <v>96</v>
+      </c>
+      <c r="I431" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J431" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K431" t="inlineStr"/>
+      <c r="L431" t="inlineStr"/>
+      <c r="M431" t="inlineStr"/>
+      <c r="N431" t="inlineStr"/>
+      <c r="O431" t="inlineStr"/>
+      <c r="P431" t="inlineStr"/>
+      <c r="Q431" t="inlineStr"/>
+      <c r="R431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>297</v>
+      </c>
+      <c r="F432" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H432" t="n">
+        <v>90</v>
+      </c>
+      <c r="I432" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J432" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K432" t="inlineStr"/>
+      <c r="L432" t="inlineStr"/>
+      <c r="M432" t="inlineStr"/>
+      <c r="N432" t="inlineStr"/>
+      <c r="O432" t="inlineStr"/>
+      <c r="P432" t="inlineStr"/>
+      <c r="Q432" t="inlineStr"/>
+      <c r="R432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>82.40000000000001</v>
+      </c>
+      <c r="F433" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H433" t="n">
+        <v>87</v>
+      </c>
+      <c r="I433" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J433" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K433" t="inlineStr"/>
+      <c r="L433" t="inlineStr"/>
+      <c r="M433" t="inlineStr"/>
+      <c r="N433" t="inlineStr"/>
+      <c r="O433" t="inlineStr"/>
+      <c r="P433" t="inlineStr"/>
+      <c r="Q433" t="inlineStr"/>
+      <c r="R433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>漢科</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="F434" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H434" t="n">
+        <v>77</v>
+      </c>
+      <c r="I434" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J434" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K434" t="inlineStr"/>
+      <c r="L434" t="inlineStr"/>
+      <c r="M434" t="inlineStr"/>
+      <c r="N434" t="inlineStr"/>
+      <c r="O434" t="inlineStr"/>
+      <c r="P434" t="inlineStr"/>
+      <c r="Q434" t="inlineStr"/>
+      <c r="R434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>248.5</v>
+      </c>
+      <c r="F435" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H435" t="n">
+        <v>77</v>
+      </c>
+      <c r="I435" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J435" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K435" t="inlineStr"/>
+      <c r="L435" t="inlineStr"/>
+      <c r="M435" t="inlineStr"/>
+      <c r="N435" t="inlineStr"/>
+      <c r="O435" t="inlineStr"/>
+      <c r="P435" t="inlineStr"/>
+      <c r="Q435" t="inlineStr"/>
+      <c r="R435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>1145</v>
+      </c>
+      <c r="F436" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H436" t="n">
+        <v>76</v>
+      </c>
+      <c r="I436" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J436" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K436" t="inlineStr"/>
+      <c r="L436" t="inlineStr"/>
+      <c r="M436" t="inlineStr"/>
+      <c r="N436" t="inlineStr"/>
+      <c r="O436" t="inlineStr"/>
+      <c r="P436" t="inlineStr"/>
+      <c r="Q436" t="inlineStr"/>
+      <c r="R436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>61.7</v>
+      </c>
+      <c r="F437" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H437" t="n">
+        <v>68</v>
+      </c>
+      <c r="I437" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J437" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K437" t="inlineStr"/>
+      <c r="L437" t="inlineStr"/>
+      <c r="M437" t="inlineStr"/>
+      <c r="N437" t="inlineStr"/>
+      <c r="O437" t="inlineStr"/>
+      <c r="P437" t="inlineStr"/>
+      <c r="Q437" t="inlineStr"/>
+      <c r="R437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>3310</v>
+      </c>
+      <c r="F438" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H438" t="n">
+        <v>100</v>
+      </c>
+      <c r="I438" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J438" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K438" t="inlineStr"/>
+      <c r="L438" t="inlineStr"/>
+      <c r="M438" t="inlineStr"/>
+      <c r="N438" t="inlineStr"/>
+      <c r="O438" t="inlineStr"/>
+      <c r="P438" t="inlineStr"/>
+      <c r="Q438" t="inlineStr"/>
+      <c r="R438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>703</v>
+      </c>
+      <c r="F439" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H439" t="n">
+        <v>100</v>
+      </c>
+      <c r="I439" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J439" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K439" t="inlineStr"/>
+      <c r="L439" t="inlineStr"/>
+      <c r="M439" t="inlineStr"/>
+      <c r="N439" t="inlineStr"/>
+      <c r="O439" t="inlineStr"/>
+      <c r="P439" t="inlineStr"/>
+      <c r="Q439" t="inlineStr"/>
+      <c r="R439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>2380</v>
+      </c>
+      <c r="F440" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H440" t="n">
+        <v>100</v>
+      </c>
+      <c r="I440" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J440" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K440" t="inlineStr"/>
+      <c r="L440" t="inlineStr"/>
+      <c r="M440" t="inlineStr"/>
+      <c r="N440" t="inlineStr"/>
+      <c r="O440" t="inlineStr"/>
+      <c r="P440" t="inlineStr"/>
+      <c r="Q440" t="inlineStr"/>
+      <c r="R440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="F441" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H441" t="n">
+        <v>94</v>
+      </c>
+      <c r="I441" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J441" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K441" t="inlineStr"/>
+      <c r="L441" t="inlineStr"/>
+      <c r="M441" t="inlineStr"/>
+      <c r="N441" t="inlineStr"/>
+      <c r="O441" t="inlineStr"/>
+      <c r="P441" t="inlineStr"/>
+      <c r="Q441" t="inlineStr"/>
+      <c r="R441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>八方雲集</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>177</v>
+      </c>
+      <c r="F442" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H442" t="n">
+        <v>94</v>
+      </c>
+      <c r="I442" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J442" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K442" t="inlineStr"/>
+      <c r="L442" t="inlineStr"/>
+      <c r="M442" t="inlineStr"/>
+      <c r="N442" t="inlineStr"/>
+      <c r="O442" t="inlineStr"/>
+      <c r="P442" t="inlineStr"/>
+      <c r="Q442" t="inlineStr"/>
+      <c r="R442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>42.05</v>
+      </c>
+      <c r="F443" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H443" t="n">
+        <v>92</v>
+      </c>
+      <c r="I443" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J443" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K443" t="inlineStr"/>
+      <c r="L443" t="inlineStr"/>
+      <c r="M443" t="inlineStr"/>
+      <c r="N443" t="inlineStr"/>
+      <c r="O443" t="inlineStr"/>
+      <c r="P443" t="inlineStr"/>
+      <c r="Q443" t="inlineStr"/>
+      <c r="R443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>886</v>
+      </c>
+      <c r="F444" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H444" t="n">
+        <v>90</v>
+      </c>
+      <c r="I444" t="n">
+        <v>25</v>
+      </c>
+      <c r="J444" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K444" t="inlineStr"/>
+      <c r="L444" t="inlineStr"/>
+      <c r="M444" t="inlineStr"/>
+      <c r="N444" t="inlineStr"/>
+      <c r="O444" t="inlineStr"/>
+      <c r="P444" t="inlineStr"/>
+      <c r="Q444" t="inlineStr"/>
+      <c r="R444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>510</v>
+      </c>
+      <c r="F445" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H445" t="n">
+        <v>90</v>
+      </c>
+      <c r="I445" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J445" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K445" t="inlineStr"/>
+      <c r="L445" t="inlineStr"/>
+      <c r="M445" t="inlineStr"/>
+      <c r="N445" t="inlineStr"/>
+      <c r="O445" t="inlineStr"/>
+      <c r="P445" t="inlineStr"/>
+      <c r="Q445" t="inlineStr"/>
+      <c r="R445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>163</v>
+      </c>
+      <c r="F446" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H446" t="n">
+        <v>90</v>
+      </c>
+      <c r="I446" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J446" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K446" t="inlineStr"/>
+      <c r="L446" t="inlineStr"/>
+      <c r="M446" t="inlineStr"/>
+      <c r="N446" t="inlineStr"/>
+      <c r="O446" t="inlineStr"/>
+      <c r="P446" t="inlineStr"/>
+      <c r="Q446" t="inlineStr"/>
+      <c r="R446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>38.7</v>
+      </c>
+      <c r="F447" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H447" t="n">
+        <v>84</v>
+      </c>
+      <c r="I447" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J447" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K447" t="inlineStr"/>
+      <c r="L447" t="inlineStr"/>
+      <c r="M447" t="inlineStr"/>
+      <c r="N447" t="inlineStr"/>
+      <c r="O447" t="inlineStr"/>
+      <c r="P447" t="inlineStr"/>
+      <c r="Q447" t="inlineStr"/>
+      <c r="R447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>1875</v>
+      </c>
+      <c r="F448" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G448" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H448" t="n">
+        <v>80</v>
+      </c>
+      <c r="I448" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J448" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K448" t="inlineStr"/>
+      <c r="L448" t="inlineStr"/>
+      <c r="M448" t="inlineStr"/>
+      <c r="N448" t="inlineStr"/>
+      <c r="O448" t="inlineStr"/>
+      <c r="P448" t="inlineStr"/>
+      <c r="Q448" t="inlineStr"/>
+      <c r="R448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>1305</v>
+      </c>
+      <c r="F449" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G449" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H449" t="n">
+        <v>80</v>
+      </c>
+      <c r="I449" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J449" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K449" t="inlineStr"/>
+      <c r="L449" t="inlineStr"/>
+      <c r="M449" t="inlineStr"/>
+      <c r="N449" t="inlineStr"/>
+      <c r="O449" t="inlineStr"/>
+      <c r="P449" t="inlineStr"/>
+      <c r="Q449" t="inlineStr"/>
+      <c r="R449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>達欣工</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="F450" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G450" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H450" t="n">
+        <v>79</v>
+      </c>
+      <c r="I450" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J450" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K450" t="inlineStr"/>
+      <c r="L450" t="inlineStr"/>
+      <c r="M450" t="inlineStr"/>
+      <c r="N450" t="inlineStr"/>
+      <c r="O450" t="inlineStr"/>
+      <c r="P450" t="inlineStr"/>
+      <c r="Q450" t="inlineStr"/>
+      <c r="R450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>友輝</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>51.2</v>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G451" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H451" t="n">
+        <v>77</v>
+      </c>
+      <c r="I451" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J451" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K451" t="inlineStr"/>
+      <c r="L451" t="inlineStr"/>
+      <c r="M451" t="inlineStr"/>
+      <c r="N451" t="inlineStr"/>
+      <c r="O451" t="inlineStr"/>
+      <c r="P451" t="inlineStr"/>
+      <c r="Q451" t="inlineStr"/>
+      <c r="R451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>332.5</v>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G452" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H452" t="n">
+        <v>65</v>
+      </c>
+      <c r="I452" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J452" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K452" t="inlineStr"/>
+      <c r="L452" t="inlineStr"/>
+      <c r="M452" t="inlineStr"/>
+      <c r="N452" t="inlineStr"/>
+      <c r="O452" t="inlineStr"/>
+      <c r="P452" t="inlineStr"/>
+      <c r="Q452" t="inlineStr"/>
+      <c r="R452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>181</v>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G453" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H453" t="n">
+        <v>62</v>
+      </c>
+      <c r="I453" t="n">
+        <v>10</v>
+      </c>
+      <c r="J453" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K453" t="inlineStr"/>
+      <c r="L453" t="inlineStr"/>
+      <c r="M453" t="inlineStr"/>
+      <c r="N453" t="inlineStr"/>
+      <c r="O453" t="inlineStr"/>
+      <c r="P453" t="inlineStr"/>
+      <c r="Q453" t="inlineStr"/>
+      <c r="R453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>1365</v>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G454" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H454" t="n">
+        <v>60</v>
+      </c>
+      <c r="I454" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J454" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K454" t="inlineStr"/>
+      <c r="L454" t="inlineStr"/>
+      <c r="M454" t="inlineStr"/>
+      <c r="N454" t="inlineStr"/>
+      <c r="O454" t="inlineStr"/>
+      <c r="P454" t="inlineStr"/>
+      <c r="Q454" t="inlineStr"/>
+      <c r="R454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>德昌</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G455" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H455" t="n">
+        <v>79</v>
+      </c>
+      <c r="I455" t="inlineStr"/>
+      <c r="J455" t="inlineStr"/>
+      <c r="K455" t="inlineStr"/>
+      <c r="L455" t="inlineStr"/>
+      <c r="M455" t="inlineStr"/>
+      <c r="N455" t="inlineStr"/>
+      <c r="O455" t="inlineStr"/>
+      <c r="P455" t="inlineStr"/>
+      <c r="Q455" t="inlineStr"/>
+      <c r="R455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>398</v>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G456" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H456" t="n">
+        <v>77</v>
+      </c>
+      <c r="I456" t="inlineStr"/>
+      <c r="J456" t="inlineStr"/>
+      <c r="K456" t="inlineStr"/>
+      <c r="L456" t="inlineStr"/>
+      <c r="M456" t="inlineStr"/>
+      <c r="N456" t="inlineStr"/>
+      <c r="O456" t="inlineStr"/>
+      <c r="P456" t="inlineStr"/>
+      <c r="Q456" t="inlineStr"/>
+      <c r="R456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>鑫龍騰</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>23.65</v>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G457" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H457" t="n">
+        <v>77</v>
+      </c>
+      <c r="I457" t="inlineStr"/>
+      <c r="J457" t="inlineStr"/>
+      <c r="K457" t="inlineStr"/>
+      <c r="L457" t="inlineStr"/>
+      <c r="M457" t="inlineStr"/>
+      <c r="N457" t="inlineStr"/>
+      <c r="O457" t="inlineStr"/>
+      <c r="P457" t="inlineStr"/>
+      <c r="Q457" t="inlineStr"/>
+      <c r="R457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>202</v>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G458" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H458" t="n">
+        <v>69</v>
+      </c>
+      <c r="I458" t="inlineStr"/>
+      <c r="J458" t="inlineStr"/>
+      <c r="K458" t="inlineStr"/>
+      <c r="L458" t="inlineStr"/>
+      <c r="M458" t="inlineStr"/>
+      <c r="N458" t="inlineStr"/>
+      <c r="O458" t="inlineStr"/>
+      <c r="P458" t="inlineStr"/>
+      <c r="Q458" t="inlineStr"/>
+      <c r="R458" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -24125,7 +25513,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -24143,7 +25531,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5925</v>
+        <v>6025</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -24165,10 +25553,10 @@
         <v>0.26</v>
       </c>
       <c r="K2" t="n">
-        <v>2610</v>
+        <v>2270</v>
       </c>
       <c r="L2" t="n">
-        <v>-55.95</v>
+        <v>-62.32</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -24177,12 +25565,12 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>-55.95</v>
+        <v>-62.32</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46202</v>
+        <v>46237</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -24191,16 +25579,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>499.5</v>
+        <v>5925</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -24209,23 +25597,23 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="I3" t="n">
-        <v>21.2</v>
+        <v>9.6</v>
       </c>
       <c r="J3" t="n">
-        <v>0.92</v>
+        <v>0.26</v>
       </c>
       <c r="K3" t="n">
-        <v>339.5</v>
+        <v>2610</v>
       </c>
       <c r="L3" t="n">
-        <v>-32.03</v>
+        <v>-55.95</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -24234,7 +25622,7 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>-32.03</v>
+        <v>-55.95</v>
       </c>
     </row>
     <row r="4">
@@ -24248,16 +25636,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>955</v>
+        <v>499.5</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -24270,19 +25658,19 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I4" t="n">
-        <v>14.2</v>
+        <v>21.2</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4</v>
+        <v>0.92</v>
       </c>
       <c r="K4" t="n">
-        <v>671</v>
+        <v>339.5</v>
       </c>
       <c r="L4" t="n">
-        <v>-29.74</v>
+        <v>-32.03</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -24291,7 +25679,7 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>-29.74</v>
+        <v>-32.03</v>
       </c>
     </row>
     <row r="5">
@@ -24305,16 +25693,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>65.5</v>
+        <v>955</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -24323,23 +25711,23 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>10.4</v>
+        <v>14.2</v>
       </c>
       <c r="J5" t="n">
-        <v>0.71</v>
+        <v>0.4</v>
       </c>
       <c r="K5" t="n">
-        <v>51.7</v>
+        <v>671</v>
       </c>
       <c r="L5" t="n">
-        <v>-21.07</v>
+        <v>-29.74</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -24348,12 +25736,12 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-21.07</v>
+        <v>-29.74</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -24362,20 +25750,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>158</v>
+        <v>65.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -24387,16 +25775,16 @@
         <v>77</v>
       </c>
       <c r="I6" t="n">
-        <v>16.4</v>
+        <v>10.4</v>
       </c>
       <c r="J6" t="n">
-        <v>1.11</v>
+        <v>0.71</v>
       </c>
       <c r="K6" t="n">
-        <v>125.5</v>
+        <v>51.7</v>
       </c>
       <c r="L6" t="n">
-        <v>-20.57</v>
+        <v>-21.07</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -24405,12 +25793,12 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>-20.57</v>
+        <v>-21.07</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -24419,16 +25807,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>344.5</v>
+        <v>158</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -24437,23 +25825,23 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I7" t="n">
-        <v>27.5</v>
+        <v>16.4</v>
       </c>
       <c r="J7" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="K7" t="n">
-        <v>277.5</v>
+        <v>125.5</v>
       </c>
       <c r="L7" t="n">
-        <v>-19.45</v>
+        <v>-20.57</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -24462,7 +25850,7 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>-19.45</v>
+        <v>-20.57</v>
       </c>
     </row>
     <row r="8">
@@ -24476,20 +25864,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1215</v>
+        <v>344.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -24501,16 +25889,16 @@
         <v>90</v>
       </c>
       <c r="I8" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.67</v>
+        <v>1.22</v>
       </c>
       <c r="K8" t="n">
-        <v>981</v>
+        <v>277.5</v>
       </c>
       <c r="L8" t="n">
-        <v>-19.26</v>
+        <v>-19.45</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -24519,7 +25907,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>-19.26</v>
+        <v>-19.45</v>
       </c>
     </row>
     <row r="9">
@@ -24533,41 +25921,41 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>143</v>
+        <v>1215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I9" t="n">
-        <v>16.4</v>
+        <v>25</v>
       </c>
       <c r="J9" t="n">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="K9" t="n">
-        <v>115.5</v>
+        <v>981</v>
       </c>
       <c r="L9" t="n">
-        <v>-19.23</v>
+        <v>-19.26</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -24576,12 +25964,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>-19.23</v>
+        <v>-19.26</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46244</v>
+        <v>46202</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -24590,20 +25978,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>66.7</v>
+        <v>143</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -24612,19 +26000,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I10" t="n">
-        <v>6.8</v>
+        <v>16.4</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="K10" t="n">
-        <v>53.9</v>
+        <v>115.5</v>
       </c>
       <c r="L10" t="n">
-        <v>-19.19</v>
+        <v>-19.23</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -24633,12 +26021,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>-19.19</v>
+        <v>-19.23</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46202</v>
+        <v>46244</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -24647,16 +26035,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>34.2</v>
+        <v>66.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -24665,23 +26053,23 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="I11" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>27.65</v>
+        <v>53.9</v>
       </c>
       <c r="L11" t="n">
-        <v>-19.15</v>
+        <v>-19.19</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -24690,12 +26078,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-19.15</v>
+        <v>-19.19</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -24704,16 +26092,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>373</v>
+        <v>34.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -24722,23 +26110,23 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="I12" t="n">
-        <v>13.2</v>
+        <v>5.9</v>
       </c>
       <c r="J12" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="K12" t="n">
-        <v>302</v>
+        <v>27.65</v>
       </c>
       <c r="L12" t="n">
-        <v>-19.03</v>
+        <v>-19.15</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -24747,12 +26135,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-19.03</v>
+        <v>-19.15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46226</v>
+        <v>46210</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -24761,20 +26149,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1190</v>
+        <v>373</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -24783,19 +26171,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="I13" t="n">
-        <v>38.8</v>
+        <v>13.2</v>
       </c>
       <c r="J13" t="n">
-        <v>1.03</v>
+        <v>0.49</v>
       </c>
       <c r="K13" t="n">
-        <v>967</v>
+        <v>302</v>
       </c>
       <c r="L13" t="n">
-        <v>-18.74</v>
+        <v>-19.03</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -24804,7 +26192,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-18.74</v>
+        <v>-19.03</v>
       </c>
     </row>
     <row r="14">
@@ -24866,7 +26254,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46202</v>
+        <v>46226</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -24875,41 +26263,41 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2340</v>
+        <v>1190</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I15" t="n">
-        <v>30.7</v>
+        <v>38.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.82</v>
+        <v>1.03</v>
       </c>
       <c r="K15" t="n">
-        <v>1910</v>
+        <v>967</v>
       </c>
       <c r="L15" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -24918,12 +26306,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46226</v>
+        <v>46202</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -24932,16 +26320,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1180</v>
+        <v>2340</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -24954,19 +26342,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>30.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0.67</v>
+        <v>0.82</v>
       </c>
       <c r="K16" t="n">
-        <v>967</v>
+        <v>1910</v>
       </c>
       <c r="L16" t="n">
-        <v>-18.05</v>
+        <v>-18.38</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -24975,7 +26363,7 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-18.05</v>
+        <v>-18.38</v>
       </c>
     </row>
     <row r="17">
@@ -24989,16 +26377,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>72.59999999999999</v>
+        <v>1180</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -25007,23 +26395,23 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="K17" t="n">
-        <v>59.6</v>
+        <v>967</v>
       </c>
       <c r="L17" t="n">
-        <v>-17.91</v>
+        <v>-18.05</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -25032,12 +26420,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-17.91</v>
+        <v>-18.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -25055,7 +26443,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>72.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -25077,10 +26465,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>60.4</v>
+        <v>59.6</v>
       </c>
       <c r="L18" t="n">
-        <v>-16.69</v>
+        <v>-17.91</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -25089,12 +26477,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-16.69</v>
+        <v>-17.91</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46210</v>
+        <v>46234</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -25103,16 +26491,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>475.5</v>
+        <v>72.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -25121,23 +26509,23 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I19" t="n">
-        <v>21.2</v>
+        <v>6.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0.92</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>397.5</v>
+        <v>60.4</v>
       </c>
       <c r="L19" t="n">
-        <v>-16.4</v>
+        <v>-16.69</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -25146,12 +26534,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-16.4</v>
+        <v>-16.69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -25160,16 +26548,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>72.7</v>
+        <v>475.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -25178,23 +26566,23 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I20" t="n">
-        <v>6.8</v>
+        <v>21.2</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="K20" t="n">
-        <v>61</v>
+        <v>397.5</v>
       </c>
       <c r="L20" t="n">
-        <v>-16.09</v>
+        <v>-16.4</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -25203,12 +26591,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-16.09</v>
+        <v>-16.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46226</v>
+        <v>46218</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -25217,20 +26605,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>143</v>
+        <v>72.7</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -25239,19 +26627,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I21" t="n">
-        <v>16.4</v>
+        <v>6.8</v>
       </c>
       <c r="J21" t="n">
-        <v>1.11</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>120</v>
+        <v>61</v>
       </c>
       <c r="L21" t="n">
-        <v>-16.08</v>
+        <v>-16.09</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -25260,7 +26648,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-16.08</v>
+        <v>-16.09</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R458"/>
+  <dimension ref="A1:R460"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24160,6 +24160,102 @@
       <c r="P458" t="inlineStr"/>
       <c r="Q458" t="inlineStr"/>
       <c r="R458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>2315</v>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G459" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H459" t="n">
+        <v>65</v>
+      </c>
+      <c r="I459" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J459" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K459" t="inlineStr"/>
+      <c r="L459" t="inlineStr"/>
+      <c r="M459" t="inlineStr"/>
+      <c r="N459" t="inlineStr"/>
+      <c r="O459" t="inlineStr"/>
+      <c r="P459" t="inlineStr"/>
+      <c r="Q459" t="inlineStr"/>
+      <c r="R459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>6189</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>豐藝</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>46.6</v>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G460" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H460" t="n">
+        <v>32</v>
+      </c>
+      <c r="I460" t="inlineStr"/>
+      <c r="J460" t="inlineStr"/>
+      <c r="K460" t="inlineStr"/>
+      <c r="L460" t="inlineStr"/>
+      <c r="M460" t="inlineStr"/>
+      <c r="N460" t="inlineStr"/>
+      <c r="O460" t="inlineStr"/>
+      <c r="P460" t="inlineStr"/>
+      <c r="Q460" t="inlineStr"/>
+      <c r="R460" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C2" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.53</v>
+        <v>-0.65</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.47</v>
+        <v>-1.54</v>
       </c>
       <c r="F2" t="n">
         <v>49.42</v>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D2" t="n">
-        <v>42.3</v>
+        <v>42.1</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.53</v>
+        <v>-0.65</v>
       </c>
     </row>
   </sheetData>
@@ -16990,8 +16990,12 @@
       </c>
       <c r="I313" t="inlineStr"/>
       <c r="J313" t="inlineStr"/>
-      <c r="K313" t="inlineStr"/>
-      <c r="L313" t="inlineStr"/>
+      <c r="K313" t="n">
+        <v>34.8</v>
+      </c>
+      <c r="L313" t="n">
+        <v>-26.19</v>
+      </c>
       <c r="M313" t="inlineStr"/>
       <c r="N313" t="inlineStr"/>
       <c r="O313" t="inlineStr"/>
@@ -25837,7 +25841,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46202</v>
+        <v>46251</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -25846,20 +25850,20 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>65.5</v>
+        <v>47.15</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -25868,19 +25872,15 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>77</v>
-      </c>
-      <c r="I6" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J6" t="n">
-        <v>0.71</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>51.7</v>
+        <v>34.8</v>
       </c>
       <c r="L6" t="n">
-        <v>-21.07</v>
+        <v>-26.19</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -25889,12 +25889,12 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>-21.07</v>
+        <v>-26.19</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -25903,20 +25903,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>158</v>
+        <v>65.5</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -25928,16 +25928,16 @@
         <v>77</v>
       </c>
       <c r="I7" t="n">
-        <v>16.4</v>
+        <v>10.4</v>
       </c>
       <c r="J7" t="n">
-        <v>1.11</v>
+        <v>0.71</v>
       </c>
       <c r="K7" t="n">
-        <v>125.5</v>
+        <v>51.7</v>
       </c>
       <c r="L7" t="n">
-        <v>-20.57</v>
+        <v>-21.07</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -25946,12 +25946,12 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>-20.57</v>
+        <v>-21.07</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -25960,16 +25960,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>344.5</v>
+        <v>158</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -25978,23 +25978,23 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I8" t="n">
-        <v>27.5</v>
+        <v>16.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="K8" t="n">
-        <v>277.5</v>
+        <v>125.5</v>
       </c>
       <c r="L8" t="n">
-        <v>-19.45</v>
+        <v>-20.57</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -26003,7 +26003,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>-19.45</v>
+        <v>-20.57</v>
       </c>
     </row>
     <row r="9">
@@ -26017,20 +26017,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1215</v>
+        <v>344.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -26042,16 +26042,16 @@
         <v>90</v>
       </c>
       <c r="I9" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0.67</v>
+        <v>1.22</v>
       </c>
       <c r="K9" t="n">
-        <v>981</v>
+        <v>277.5</v>
       </c>
       <c r="L9" t="n">
-        <v>-19.26</v>
+        <v>-19.45</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -26060,7 +26060,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>-19.26</v>
+        <v>-19.45</v>
       </c>
     </row>
     <row r="10">
@@ -26074,41 +26074,41 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>143</v>
+        <v>1215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
-        <v>16.4</v>
+        <v>25</v>
       </c>
       <c r="J10" t="n">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="K10" t="n">
-        <v>115.5</v>
+        <v>981</v>
       </c>
       <c r="L10" t="n">
-        <v>-19.23</v>
+        <v>-19.26</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -26117,12 +26117,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>-19.23</v>
+        <v>-19.26</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46244</v>
+        <v>46202</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -26131,20 +26131,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>66.7</v>
+        <v>143</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -26153,19 +26153,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I11" t="n">
-        <v>6.8</v>
+        <v>16.4</v>
       </c>
       <c r="J11" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="K11" t="n">
-        <v>53.9</v>
+        <v>115.5</v>
       </c>
       <c r="L11" t="n">
-        <v>-19.19</v>
+        <v>-19.23</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -26174,12 +26174,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-19.19</v>
+        <v>-19.23</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46202</v>
+        <v>46244</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -26188,16 +26188,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>34.2</v>
+        <v>66.7</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -26206,23 +26206,23 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="I12" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K12" t="n">
-        <v>27.65</v>
+        <v>53.9</v>
       </c>
       <c r="L12" t="n">
-        <v>-19.15</v>
+        <v>-19.19</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -26231,12 +26231,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-19.15</v>
+        <v>-19.19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -26245,16 +26245,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>373</v>
+        <v>34.2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -26263,23 +26263,23 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>65</v>
+        <v>94</v>
       </c>
       <c r="I13" t="n">
-        <v>13.2</v>
+        <v>5.9</v>
       </c>
       <c r="J13" t="n">
-        <v>0.49</v>
+        <v>0.42</v>
       </c>
       <c r="K13" t="n">
-        <v>302</v>
+        <v>27.65</v>
       </c>
       <c r="L13" t="n">
-        <v>-19.03</v>
+        <v>-19.15</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -26288,7 +26288,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-19.03</v>
+        <v>-19.15</v>
       </c>
     </row>
     <row r="14">
@@ -26302,16 +26302,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>34.15</v>
+        <v>373</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -26320,23 +26320,23 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="I14" t="n">
-        <v>5.9</v>
+        <v>13.2</v>
       </c>
       <c r="J14" t="n">
-        <v>0.42</v>
+        <v>0.49</v>
       </c>
       <c r="K14" t="n">
-        <v>27.75</v>
+        <v>302</v>
       </c>
       <c r="L14" t="n">
-        <v>-18.74</v>
+        <v>-19.03</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -26345,7 +26345,7 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-18.74</v>
+        <v>-19.03</v>
       </c>
     </row>
     <row r="15">
@@ -26407,7 +26407,7 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -26416,16 +26416,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2340</v>
+        <v>34.15</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -26438,19 +26438,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I16" t="n">
-        <v>30.7</v>
+        <v>5.9</v>
       </c>
       <c r="J16" t="n">
-        <v>0.82</v>
+        <v>0.42</v>
       </c>
       <c r="K16" t="n">
-        <v>1910</v>
+        <v>27.75</v>
       </c>
       <c r="L16" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -26459,12 +26459,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46226</v>
+        <v>46202</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -26473,16 +26473,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1180</v>
+        <v>2340</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -26495,19 +26495,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>30.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.67</v>
+        <v>0.82</v>
       </c>
       <c r="K17" t="n">
-        <v>967</v>
+        <v>1910</v>
       </c>
       <c r="L17" t="n">
-        <v>-18.05</v>
+        <v>-18.38</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -26516,7 +26516,7 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-18.05</v>
+        <v>-18.38</v>
       </c>
     </row>
     <row r="18">
@@ -26530,16 +26530,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>72.59999999999999</v>
+        <v>1180</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -26548,23 +26548,23 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I18" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="K18" t="n">
-        <v>59.6</v>
+        <v>967</v>
       </c>
       <c r="L18" t="n">
-        <v>-17.91</v>
+        <v>-18.05</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -26573,12 +26573,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-17.91</v>
+        <v>-18.05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -26596,7 +26596,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>72.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -26618,10 +26618,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>60.4</v>
+        <v>59.6</v>
       </c>
       <c r="L19" t="n">
-        <v>-16.69</v>
+        <v>-17.91</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -26630,12 +26630,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-16.69</v>
+        <v>-17.91</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46210</v>
+        <v>46234</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -26644,16 +26644,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>475.5</v>
+        <v>72.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -26662,23 +26662,23 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I20" t="n">
-        <v>21.2</v>
+        <v>6.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0.92</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>397.5</v>
+        <v>60.4</v>
       </c>
       <c r="L20" t="n">
-        <v>-16.4</v>
+        <v>-16.69</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -26687,12 +26687,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-16.4</v>
+        <v>-16.69</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -26701,16 +26701,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>72.7</v>
+        <v>475.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -26719,23 +26719,23 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I21" t="n">
-        <v>6.8</v>
+        <v>21.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="K21" t="n">
-        <v>61</v>
+        <v>397.5</v>
       </c>
       <c r="L21" t="n">
-        <v>-16.09</v>
+        <v>-16.4</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -26744,7 +26744,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-16.09</v>
+        <v>-16.4</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>214</v>
+        <v>249</v>
       </c>
       <c r="C2" t="n">
-        <v>42.1</v>
+        <v>43</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.65</v>
+        <v>-0.53</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.54</v>
+        <v>-1.36</v>
       </c>
       <c r="F2" t="n">
         <v>49.42</v>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>214</v>
+        <v>249</v>
       </c>
       <c r="D2" t="n">
-        <v>42.1</v>
+        <v>43</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.65</v>
+        <v>-0.53</v>
       </c>
     </row>
   </sheetData>
@@ -17044,8 +17044,12 @@
       <c r="J314" t="n">
         <v>1.29</v>
       </c>
-      <c r="K314" t="inlineStr"/>
-      <c r="L314" t="inlineStr"/>
+      <c r="K314" t="n">
+        <v>172</v>
+      </c>
+      <c r="L314" t="n">
+        <v>10.97</v>
+      </c>
       <c r="M314" t="inlineStr"/>
       <c r="N314" t="inlineStr"/>
       <c r="O314" t="inlineStr"/>
@@ -17094,8 +17098,12 @@
       <c r="J315" t="n">
         <v>1.11</v>
       </c>
-      <c r="K315" t="inlineStr"/>
-      <c r="L315" t="inlineStr"/>
+      <c r="K315" t="n">
+        <v>530</v>
+      </c>
+      <c r="L315" t="n">
+        <v>-4.16</v>
+      </c>
       <c r="M315" t="inlineStr"/>
       <c r="N315" t="inlineStr"/>
       <c r="O315" t="inlineStr"/>
@@ -17144,8 +17152,12 @@
       <c r="J316" t="n">
         <v>1.26</v>
       </c>
-      <c r="K316" t="inlineStr"/>
-      <c r="L316" t="inlineStr"/>
+      <c r="K316" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="L316" t="n">
+        <v>-2.85</v>
+      </c>
       <c r="M316" t="inlineStr"/>
       <c r="N316" t="inlineStr"/>
       <c r="O316" t="inlineStr"/>
@@ -17194,8 +17206,12 @@
       <c r="J317" t="n">
         <v>1.22</v>
       </c>
-      <c r="K317" t="inlineStr"/>
-      <c r="L317" t="inlineStr"/>
+      <c r="K317" t="n">
+        <v>304.5</v>
+      </c>
+      <c r="L317" t="n">
+        <v>3.57</v>
+      </c>
       <c r="M317" t="inlineStr"/>
       <c r="N317" t="inlineStr"/>
       <c r="O317" t="inlineStr"/>
@@ -17244,8 +17260,12 @@
       <c r="J318" t="n">
         <v>1.36</v>
       </c>
-      <c r="K318" t="inlineStr"/>
-      <c r="L318" t="inlineStr"/>
+      <c r="K318" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="L318" t="n">
+        <v>-4.19</v>
+      </c>
       <c r="M318" t="inlineStr"/>
       <c r="N318" t="inlineStr"/>
       <c r="O318" t="inlineStr"/>
@@ -17294,8 +17314,12 @@
       <c r="J319" t="n">
         <v>1.11</v>
       </c>
-      <c r="K319" t="inlineStr"/>
-      <c r="L319" t="inlineStr"/>
+      <c r="K319" t="n">
+        <v>125.5</v>
+      </c>
+      <c r="L319" t="n">
+        <v>0.8</v>
+      </c>
       <c r="M319" t="inlineStr"/>
       <c r="N319" t="inlineStr"/>
       <c r="O319" t="inlineStr"/>
@@ -17344,8 +17368,12 @@
       <c r="J320" t="n">
         <v>1.16</v>
       </c>
-      <c r="K320" t="inlineStr"/>
-      <c r="L320" t="inlineStr"/>
+      <c r="K320" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="L320" t="n">
+        <v>0.6</v>
+      </c>
       <c r="M320" t="inlineStr"/>
       <c r="N320" t="inlineStr"/>
       <c r="O320" t="inlineStr"/>
@@ -17394,8 +17422,12 @@
       <c r="J321" t="n">
         <v>1.03</v>
       </c>
-      <c r="K321" t="inlineStr"/>
-      <c r="L321" t="inlineStr"/>
+      <c r="K321" t="n">
+        <v>1080</v>
+      </c>
+      <c r="L321" t="n">
+        <v>5.37</v>
+      </c>
       <c r="M321" t="inlineStr"/>
       <c r="N321" t="inlineStr"/>
       <c r="O321" t="inlineStr"/>
@@ -17444,8 +17476,12 @@
       <c r="J322" t="n">
         <v>1.35</v>
       </c>
-      <c r="K322" t="inlineStr"/>
-      <c r="L322" t="inlineStr"/>
+      <c r="K322" t="n">
+        <v>61.5</v>
+      </c>
+      <c r="L322" t="n">
+        <v>-5.24</v>
+      </c>
       <c r="M322" t="inlineStr"/>
       <c r="N322" t="inlineStr"/>
       <c r="O322" t="inlineStr"/>
@@ -17494,8 +17530,12 @@
       <c r="J323" t="n">
         <v>0.66</v>
       </c>
-      <c r="K323" t="inlineStr"/>
-      <c r="L323" t="inlineStr"/>
+      <c r="K323" t="n">
+        <v>3185</v>
+      </c>
+      <c r="L323" t="n">
+        <v>4.94</v>
+      </c>
       <c r="M323" t="inlineStr"/>
       <c r="N323" t="inlineStr"/>
       <c r="O323" t="inlineStr"/>
@@ -17544,8 +17584,12 @@
       <c r="J324" t="n">
         <v>0.4</v>
       </c>
-      <c r="K324" t="inlineStr"/>
-      <c r="L324" t="inlineStr"/>
+      <c r="K324" t="n">
+        <v>696</v>
+      </c>
+      <c r="L324" t="n">
+        <v>-11</v>
+      </c>
       <c r="M324" t="inlineStr"/>
       <c r="N324" t="inlineStr"/>
       <c r="O324" t="inlineStr"/>
@@ -17594,8 +17638,12 @@
       <c r="J325" t="n">
         <v>0.78</v>
       </c>
-      <c r="K325" t="inlineStr"/>
-      <c r="L325" t="inlineStr"/>
+      <c r="K325" t="n">
+        <v>2425</v>
+      </c>
+      <c r="L325" t="n">
+        <v>1.89</v>
+      </c>
       <c r="M325" t="inlineStr"/>
       <c r="N325" t="inlineStr"/>
       <c r="O325" t="inlineStr"/>
@@ -17644,8 +17692,12 @@
       <c r="J326" t="n">
         <v>0.73</v>
       </c>
-      <c r="K326" t="inlineStr"/>
-      <c r="L326" t="inlineStr"/>
+      <c r="K326" t="n">
+        <v>116</v>
+      </c>
+      <c r="L326" t="n">
+        <v>7.91</v>
+      </c>
       <c r="M326" t="inlineStr"/>
       <c r="N326" t="inlineStr"/>
       <c r="O326" t="inlineStr"/>
@@ -17694,8 +17746,12 @@
       <c r="J327" t="n">
         <v>0.64</v>
       </c>
-      <c r="K327" t="inlineStr"/>
-      <c r="L327" t="inlineStr"/>
+      <c r="K327" t="n">
+        <v>108</v>
+      </c>
+      <c r="L327" t="n">
+        <v>-1.37</v>
+      </c>
       <c r="M327" t="inlineStr"/>
       <c r="N327" t="inlineStr"/>
       <c r="O327" t="inlineStr"/>
@@ -17744,8 +17800,12 @@
       <c r="J328" t="n">
         <v>0.42</v>
       </c>
-      <c r="K328" t="inlineStr"/>
-      <c r="L328" t="inlineStr"/>
+      <c r="K328" t="n">
+        <v>25.25</v>
+      </c>
+      <c r="L328" t="n">
+        <v>-9.17</v>
+      </c>
       <c r="M328" t="inlineStr"/>
       <c r="N328" t="inlineStr"/>
       <c r="O328" t="inlineStr"/>
@@ -17794,8 +17854,12 @@
       <c r="J329" t="n">
         <v>0.76</v>
       </c>
-      <c r="K329" t="inlineStr"/>
-      <c r="L329" t="inlineStr"/>
+      <c r="K329" t="n">
+        <v>107</v>
+      </c>
+      <c r="L329" t="n">
+        <v>-2.73</v>
+      </c>
       <c r="M329" t="inlineStr"/>
       <c r="N329" t="inlineStr"/>
       <c r="O329" t="inlineStr"/>
@@ -17844,8 +17908,12 @@
       <c r="J330" t="n">
         <v>0.59</v>
       </c>
-      <c r="K330" t="inlineStr"/>
-      <c r="L330" t="inlineStr"/>
+      <c r="K330" t="n">
+        <v>178.5</v>
+      </c>
+      <c r="L330" t="n">
+        <v>-2.19</v>
+      </c>
       <c r="M330" t="inlineStr"/>
       <c r="N330" t="inlineStr"/>
       <c r="O330" t="inlineStr"/>
@@ -17894,8 +17962,12 @@
       <c r="J331" t="n">
         <v>0.84</v>
       </c>
-      <c r="K331" t="inlineStr"/>
-      <c r="L331" t="inlineStr"/>
+      <c r="K331" t="n">
+        <v>42.05</v>
+      </c>
+      <c r="L331" t="n">
+        <v>0.36</v>
+      </c>
       <c r="M331" t="inlineStr"/>
       <c r="N331" t="inlineStr"/>
       <c r="O331" t="inlineStr"/>
@@ -17944,8 +18016,12 @@
       <c r="J332" t="n">
         <v>0.67</v>
       </c>
-      <c r="K332" t="inlineStr"/>
-      <c r="L332" t="inlineStr"/>
+      <c r="K332" t="n">
+        <v>891</v>
+      </c>
+      <c r="L332" t="n">
+        <v>-13.07</v>
+      </c>
       <c r="M332" t="inlineStr"/>
       <c r="N332" t="inlineStr"/>
       <c r="O332" t="inlineStr"/>
@@ -17994,8 +18070,12 @@
       <c r="J333" t="n">
         <v>0.92</v>
       </c>
-      <c r="K333" t="inlineStr"/>
-      <c r="L333" t="inlineStr"/>
+      <c r="K333" t="n">
+        <v>502</v>
+      </c>
+      <c r="L333" t="n">
+        <v>2.76</v>
+      </c>
       <c r="M333" t="inlineStr"/>
       <c r="N333" t="inlineStr"/>
       <c r="O333" t="inlineStr"/>
@@ -18044,8 +18124,12 @@
       <c r="J334" t="n">
         <v>0.73</v>
       </c>
-      <c r="K334" t="inlineStr"/>
-      <c r="L334" t="inlineStr"/>
+      <c r="K334" t="n">
+        <v>162</v>
+      </c>
+      <c r="L334" t="n">
+        <v>11.34</v>
+      </c>
       <c r="M334" t="inlineStr"/>
       <c r="N334" t="inlineStr"/>
       <c r="O334" t="inlineStr"/>
@@ -18094,8 +18178,12 @@
       <c r="J335" t="n">
         <v>0.2</v>
       </c>
-      <c r="K335" t="inlineStr"/>
-      <c r="L335" t="inlineStr"/>
+      <c r="K335" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="L335" t="n">
+        <v>1.3</v>
+      </c>
       <c r="M335" t="inlineStr"/>
       <c r="N335" t="inlineStr"/>
       <c r="O335" t="inlineStr"/>
@@ -18144,8 +18232,12 @@
       <c r="J336" t="n">
         <v>0.82</v>
       </c>
-      <c r="K336" t="inlineStr"/>
-      <c r="L336" t="inlineStr"/>
+      <c r="K336" t="n">
+        <v>1800</v>
+      </c>
+      <c r="L336" t="n">
+        <v>-19.1</v>
+      </c>
       <c r="M336" t="inlineStr"/>
       <c r="N336" t="inlineStr"/>
       <c r="O336" t="inlineStr"/>
@@ -18194,8 +18286,12 @@
       <c r="J337" t="n">
         <v>0.75</v>
       </c>
-      <c r="K337" t="inlineStr"/>
-      <c r="L337" t="inlineStr"/>
+      <c r="K337" t="n">
+        <v>1385</v>
+      </c>
+      <c r="L337" t="n">
+        <v>37.81</v>
+      </c>
       <c r="M337" t="inlineStr"/>
       <c r="N337" t="inlineStr"/>
       <c r="O337" t="inlineStr"/>
@@ -18244,8 +18340,12 @@
       <c r="J338" t="n">
         <v>0.36</v>
       </c>
-      <c r="K338" t="inlineStr"/>
-      <c r="L338" t="inlineStr"/>
+      <c r="K338" t="n">
+        <v>89.7</v>
+      </c>
+      <c r="L338" t="n">
+        <v>-0.55</v>
+      </c>
       <c r="M338" t="inlineStr"/>
       <c r="N338" t="inlineStr"/>
       <c r="O338" t="inlineStr"/>
@@ -18294,8 +18394,12 @@
       <c r="J339" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="K339" t="inlineStr"/>
-      <c r="L339" t="inlineStr"/>
+      <c r="K339" t="n">
+        <v>54.7</v>
+      </c>
+      <c r="L339" t="n">
+        <v>-8.83</v>
+      </c>
       <c r="M339" t="inlineStr"/>
       <c r="N339" t="inlineStr"/>
       <c r="O339" t="inlineStr"/>
@@ -18344,8 +18448,12 @@
       <c r="J340" t="n">
         <v>0.71</v>
       </c>
-      <c r="K340" t="inlineStr"/>
-      <c r="L340" t="inlineStr"/>
+      <c r="K340" t="n">
+        <v>51.3</v>
+      </c>
+      <c r="L340" t="n">
+        <v>-4.29</v>
+      </c>
       <c r="M340" t="inlineStr"/>
       <c r="N340" t="inlineStr"/>
       <c r="O340" t="inlineStr"/>
@@ -18394,8 +18502,12 @@
       <c r="J341" t="n">
         <v>0.49</v>
       </c>
-      <c r="K341" t="inlineStr"/>
-      <c r="L341" t="inlineStr"/>
+      <c r="K341" t="n">
+        <v>344</v>
+      </c>
+      <c r="L341" t="n">
+        <v>5.2</v>
+      </c>
       <c r="M341" t="inlineStr"/>
       <c r="N341" t="inlineStr"/>
       <c r="O341" t="inlineStr"/>
@@ -18444,8 +18556,12 @@
       <c r="J342" t="n">
         <v>0.31</v>
       </c>
-      <c r="K342" t="inlineStr"/>
-      <c r="L342" t="inlineStr"/>
+      <c r="K342" t="n">
+        <v>186.5</v>
+      </c>
+      <c r="L342" t="n">
+        <v>3.04</v>
+      </c>
       <c r="M342" t="inlineStr"/>
       <c r="N342" t="inlineStr"/>
       <c r="O342" t="inlineStr"/>
@@ -18494,8 +18610,12 @@
       <c r="J343" t="n">
         <v>0.36</v>
       </c>
-      <c r="K343" t="inlineStr"/>
-      <c r="L343" t="inlineStr"/>
+      <c r="K343" t="n">
+        <v>1480</v>
+      </c>
+      <c r="L343" t="n">
+        <v>8.82</v>
+      </c>
       <c r="M343" t="inlineStr"/>
       <c r="N343" t="inlineStr"/>
       <c r="O343" t="inlineStr"/>
@@ -18540,8 +18660,12 @@
       </c>
       <c r="I344" t="inlineStr"/>
       <c r="J344" t="inlineStr"/>
-      <c r="K344" t="inlineStr"/>
-      <c r="L344" t="inlineStr"/>
+      <c r="K344" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="L344" t="n">
+        <v>-0.71</v>
+      </c>
       <c r="M344" t="inlineStr"/>
       <c r="N344" t="inlineStr"/>
       <c r="O344" t="inlineStr"/>
@@ -18586,8 +18710,12 @@
       </c>
       <c r="I345" t="inlineStr"/>
       <c r="J345" t="inlineStr"/>
-      <c r="K345" t="inlineStr"/>
-      <c r="L345" t="inlineStr"/>
+      <c r="K345" t="n">
+        <v>395</v>
+      </c>
+      <c r="L345" t="n">
+        <v>-1.25</v>
+      </c>
       <c r="M345" t="inlineStr"/>
       <c r="N345" t="inlineStr"/>
       <c r="O345" t="inlineStr"/>
@@ -18632,8 +18760,12 @@
       </c>
       <c r="I346" t="inlineStr"/>
       <c r="J346" t="inlineStr"/>
-      <c r="K346" t="inlineStr"/>
-      <c r="L346" t="inlineStr"/>
+      <c r="K346" t="n">
+        <v>23.9</v>
+      </c>
+      <c r="L346" t="n">
+        <v>1.49</v>
+      </c>
       <c r="M346" t="inlineStr"/>
       <c r="N346" t="inlineStr"/>
       <c r="O346" t="inlineStr"/>
@@ -18678,8 +18810,12 @@
       </c>
       <c r="I347" t="inlineStr"/>
       <c r="J347" t="inlineStr"/>
-      <c r="K347" t="inlineStr"/>
-      <c r="L347" t="inlineStr"/>
+      <c r="K347" t="n">
+        <v>204</v>
+      </c>
+      <c r="L347" t="n">
+        <v>-8.52</v>
+      </c>
       <c r="M347" t="inlineStr"/>
       <c r="N347" t="inlineStr"/>
       <c r="O347" t="inlineStr"/>
@@ -18724,8 +18860,12 @@
       </c>
       <c r="I348" t="inlineStr"/>
       <c r="J348" t="inlineStr"/>
-      <c r="K348" t="inlineStr"/>
-      <c r="L348" t="inlineStr"/>
+      <c r="K348" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="L348" t="n">
+        <v>-0.21</v>
+      </c>
       <c r="M348" t="inlineStr"/>
       <c r="N348" t="inlineStr"/>
       <c r="O348" t="inlineStr"/>
@@ -24602,7 +24742,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -24620,7 +24760,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -24645,7 +24785,7 @@
         <v>1385</v>
       </c>
       <c r="L6" t="n">
-        <v>37.13</v>
+        <v>37.81</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -24654,12 +24794,12 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>37.13</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -24668,16 +24808,16 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>131</v>
+        <v>1010</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -24690,19 +24830,19 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I7" t="n">
-        <v>14.1</v>
+        <v>21.8</v>
       </c>
       <c r="J7" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="K7" t="n">
-        <v>179.5</v>
+        <v>1385</v>
       </c>
       <c r="L7" t="n">
-        <v>37.02</v>
+        <v>37.13</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -24711,7 +24851,7 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>37.02</v>
+        <v>37.13</v>
       </c>
     </row>
     <row r="8">
@@ -24725,16 +24865,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>369</v>
+        <v>131</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -24750,16 +24890,16 @@
         <v>90</v>
       </c>
       <c r="I8" t="n">
-        <v>21.2</v>
+        <v>14.1</v>
       </c>
       <c r="J8" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="K8" t="n">
-        <v>496.5</v>
+        <v>179.5</v>
       </c>
       <c r="L8" t="n">
-        <v>34.55</v>
+        <v>37.02</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -24768,12 +24908,12 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>34.55</v>
+        <v>37.02</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46210</v>
+        <v>46234</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -24782,37 +24922,41 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>185.5</v>
+        <v>369</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>69</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="I9" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.92</v>
+      </c>
       <c r="K9" t="n">
-        <v>247</v>
+        <v>496.5</v>
       </c>
       <c r="L9" t="n">
-        <v>33.15</v>
+        <v>34.55</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -24821,12 +24965,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>33.15</v>
+        <v>34.55</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -24835,41 +24979,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>145.5</v>
+        <v>185.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>62</v>
-      </c>
-      <c r="I10" t="n">
-        <v>10</v>
-      </c>
-      <c r="J10" t="n">
-        <v>0.31</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="n">
-        <v>193.5</v>
+        <v>247</v>
       </c>
       <c r="L10" t="n">
-        <v>32.99</v>
+        <v>33.15</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -24878,12 +25018,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>32.99</v>
+        <v>33.15</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -24892,16 +25032,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5115</v>
+        <v>145.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -24910,23 +25050,23 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I11" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="J11" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="K11" t="n">
-        <v>6620</v>
+        <v>193.5</v>
       </c>
       <c r="L11" t="n">
-        <v>29.42</v>
+        <v>32.99</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -24935,12 +25075,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>29.42</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -24949,20 +25089,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>181.5</v>
+        <v>5115</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -24971,15 +25111,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>69</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="I12" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.26</v>
+      </c>
       <c r="K12" t="n">
-        <v>233</v>
+        <v>6620</v>
       </c>
       <c r="L12" t="n">
-        <v>28.37</v>
+        <v>29.42</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -24988,12 +25132,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>28.37</v>
+        <v>29.42</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46244</v>
+        <v>46218</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -25002,41 +25146,37 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>401.5</v>
+        <v>181.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>90</v>
-      </c>
-      <c r="I13" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.92</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>509</v>
+        <v>233</v>
       </c>
       <c r="L13" t="n">
-        <v>26.77</v>
+        <v>28.37</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -25045,12 +25185,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>26.77</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46211</v>
+        <v>46244</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -25059,16 +25199,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5050</v>
+        <v>401.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -25077,23 +25217,23 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="I14" t="n">
-        <v>9.6</v>
+        <v>21.2</v>
       </c>
       <c r="J14" t="n">
-        <v>0.26</v>
+        <v>0.92</v>
       </c>
       <c r="K14" t="n">
-        <v>6265</v>
+        <v>509</v>
       </c>
       <c r="L14" t="n">
-        <v>24.06</v>
+        <v>26.77</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -25102,12 +25242,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>24.06</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46244</v>
+        <v>46211</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -25116,16 +25256,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2765</v>
+        <v>5050</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -25134,23 +25274,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I15" t="n">
-        <v>24.6</v>
+        <v>9.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0.66</v>
+        <v>0.26</v>
       </c>
       <c r="K15" t="n">
-        <v>3380</v>
+        <v>6265</v>
       </c>
       <c r="L15" t="n">
-        <v>22.24</v>
+        <v>24.06</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -25159,12 +25299,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>22.24</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46210</v>
+        <v>46244</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -25173,16 +25313,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>155.5</v>
+        <v>2765</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -25191,23 +25331,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>24.6</v>
       </c>
       <c r="J16" t="n">
-        <v>0.31</v>
+        <v>0.66</v>
       </c>
       <c r="K16" t="n">
-        <v>189.5</v>
+        <v>3380</v>
       </c>
       <c r="L16" t="n">
-        <v>21.86</v>
+        <v>22.24</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -25216,7 +25356,7 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>21.86</v>
+        <v>22.24</v>
       </c>
     </row>
     <row r="17">
@@ -25230,16 +25370,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2450</v>
+        <v>155.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -25248,23 +25388,23 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="I17" t="n">
-        <v>24.6</v>
+        <v>10</v>
       </c>
       <c r="J17" t="n">
-        <v>0.66</v>
+        <v>0.31</v>
       </c>
       <c r="K17" t="n">
-        <v>2940</v>
+        <v>189.5</v>
       </c>
       <c r="L17" t="n">
-        <v>20</v>
+        <v>21.86</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -25273,12 +25413,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>20</v>
+        <v>21.86</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46226</v>
+        <v>46210</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -25296,7 +25436,7 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2440</v>
+        <v>2450</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -25318,10 +25458,10 @@
         <v>0.66</v>
       </c>
       <c r="K18" t="n">
-        <v>2855</v>
+        <v>2940</v>
       </c>
       <c r="L18" t="n">
-        <v>17.01</v>
+        <v>20</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -25330,12 +25470,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>17.01</v>
+        <v>20</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -25344,16 +25484,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>291.5</v>
+        <v>2440</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -25362,23 +25502,23 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>13.2</v>
+        <v>24.6</v>
       </c>
       <c r="J19" t="n">
-        <v>0.49</v>
+        <v>0.66</v>
       </c>
       <c r="K19" t="n">
-        <v>338.5</v>
+        <v>2855</v>
       </c>
       <c r="L19" t="n">
-        <v>16.12</v>
+        <v>17.01</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -25387,12 +25527,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>16.12</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46202</v>
+        <v>46234</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -25401,20 +25541,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>193.5</v>
+        <v>291.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -25423,15 +25563,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>69</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="I20" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.49</v>
+      </c>
       <c r="K20" t="n">
-        <v>222.5</v>
+        <v>338.5</v>
       </c>
       <c r="L20" t="n">
-        <v>14.99</v>
+        <v>16.12</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -25440,12 +25584,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>14.99</v>
+        <v>16.12</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -25454,41 +25598,37 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>426</v>
+        <v>193.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>90</v>
-      </c>
-      <c r="I21" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.92</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="n">
-        <v>488</v>
+        <v>222.5</v>
       </c>
       <c r="L21" t="n">
-        <v>14.55</v>
+        <v>14.99</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -25497,7 +25637,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>14.55</v>
+        <v>14.99</v>
       </c>
     </row>
   </sheetData>
@@ -26293,7 +26433,7 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46210</v>
+        <v>46252</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -26302,16 +26442,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>373</v>
+        <v>2225</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -26320,23 +26460,23 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I14" t="n">
-        <v>13.2</v>
+        <v>30.7</v>
       </c>
       <c r="J14" t="n">
-        <v>0.49</v>
+        <v>0.82</v>
       </c>
       <c r="K14" t="n">
-        <v>302</v>
+        <v>1800</v>
       </c>
       <c r="L14" t="n">
-        <v>-19.03</v>
+        <v>-19.1</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -26345,12 +26485,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-19.03</v>
+        <v>-19.1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46226</v>
+        <v>46210</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -26359,20 +26499,20 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1190</v>
+        <v>373</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -26381,19 +26521,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="I15" t="n">
-        <v>38.8</v>
+        <v>13.2</v>
       </c>
       <c r="J15" t="n">
-        <v>1.03</v>
+        <v>0.49</v>
       </c>
       <c r="K15" t="n">
-        <v>967</v>
+        <v>302</v>
       </c>
       <c r="L15" t="n">
-        <v>-18.74</v>
+        <v>-19.03</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -26402,7 +26542,7 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-18.74</v>
+        <v>-19.03</v>
       </c>
     </row>
     <row r="16">
@@ -26464,7 +26604,7 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46202</v>
+        <v>46226</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -26473,41 +26613,41 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2340</v>
+        <v>1190</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I17" t="n">
-        <v>30.7</v>
+        <v>38.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.82</v>
+        <v>1.03</v>
       </c>
       <c r="K17" t="n">
-        <v>1910</v>
+        <v>967</v>
       </c>
       <c r="L17" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -26516,12 +26656,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46226</v>
+        <v>46202</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -26530,16 +26670,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1180</v>
+        <v>2340</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -26552,19 +26692,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>30.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0.67</v>
+        <v>0.82</v>
       </c>
       <c r="K18" t="n">
-        <v>967</v>
+        <v>1910</v>
       </c>
       <c r="L18" t="n">
-        <v>-18.05</v>
+        <v>-18.38</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -26573,7 +26713,7 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-18.05</v>
+        <v>-18.38</v>
       </c>
     </row>
     <row r="19">
@@ -26587,16 +26727,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>72.59999999999999</v>
+        <v>1180</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -26605,23 +26745,23 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="K19" t="n">
-        <v>59.6</v>
+        <v>967</v>
       </c>
       <c r="L19" t="n">
-        <v>-17.91</v>
+        <v>-18.05</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -26630,12 +26770,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-17.91</v>
+        <v>-18.05</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -26653,7 +26793,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>72.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -26675,10 +26815,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>60.4</v>
+        <v>59.6</v>
       </c>
       <c r="L20" t="n">
-        <v>-16.69</v>
+        <v>-17.91</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -26687,12 +26827,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-16.69</v>
+        <v>-17.91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46210</v>
+        <v>46234</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -26701,16 +26841,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>475.5</v>
+        <v>72.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -26719,23 +26859,23 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I21" t="n">
-        <v>21.2</v>
+        <v>6.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0.92</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>397.5</v>
+        <v>60.4</v>
       </c>
       <c r="L21" t="n">
-        <v>-16.4</v>
+        <v>-16.69</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -26744,7 +26884,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-16.4</v>
+        <v>-16.69</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R460"/>
+  <dimension ref="A1:R461"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24400,6 +24400,52 @@
       <c r="P460" t="inlineStr"/>
       <c r="Q460" t="inlineStr"/>
       <c r="R460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>信立</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>35.7</v>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G461" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H461" t="n">
+        <v>75</v>
+      </c>
+      <c r="I461" t="inlineStr"/>
+      <c r="J461" t="inlineStr"/>
+      <c r="K461" t="inlineStr"/>
+      <c r="L461" t="inlineStr"/>
+      <c r="M461" t="inlineStr"/>
+      <c r="N461" t="inlineStr"/>
+      <c r="O461" t="inlineStr"/>
+      <c r="P461" t="inlineStr"/>
+      <c r="Q461" t="inlineStr"/>
+      <c r="R461" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,22 +468,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C2" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.53</v>
+        <v>-0.79</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.36</v>
+        <v>-1.37</v>
       </c>
       <c r="F2" t="n">
         <v>49.42</v>
       </c>
       <c r="G2" t="n">
-        <v>-62.32</v>
+        <v>-66.01000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="D2" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.53</v>
+        <v>-0.79</v>
       </c>
     </row>
   </sheetData>
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R461"/>
+  <dimension ref="A1:R467"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18914,8 +18914,12 @@
       <c r="J349" t="n">
         <v>0.26</v>
       </c>
-      <c r="K349" t="inlineStr"/>
-      <c r="L349" t="inlineStr"/>
+      <c r="K349" t="n">
+        <v>2150</v>
+      </c>
+      <c r="L349" t="n">
+        <v>-66.01000000000001</v>
+      </c>
       <c r="M349" t="inlineStr"/>
       <c r="N349" t="inlineStr"/>
       <c r="O349" t="inlineStr"/>
@@ -24446,6 +24450,306 @@
       <c r="P461" t="inlineStr"/>
       <c r="Q461" t="inlineStr"/>
       <c r="R461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>大車隊</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>166</v>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G462" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H462" t="n">
+        <v>97</v>
+      </c>
+      <c r="I462" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J462" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K462" t="inlineStr"/>
+      <c r="L462" t="inlineStr"/>
+      <c r="M462" t="inlineStr"/>
+      <c r="N462" t="inlineStr"/>
+      <c r="O462" t="inlineStr"/>
+      <c r="P462" t="inlineStr"/>
+      <c r="Q462" t="inlineStr"/>
+      <c r="R462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>崇友</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>119</v>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G463" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H463" t="n">
+        <v>91</v>
+      </c>
+      <c r="I463" t="n">
+        <v>15</v>
+      </c>
+      <c r="J463" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K463" t="inlineStr"/>
+      <c r="L463" t="inlineStr"/>
+      <c r="M463" t="inlineStr"/>
+      <c r="N463" t="inlineStr"/>
+      <c r="O463" t="inlineStr"/>
+      <c r="P463" t="inlineStr"/>
+      <c r="Q463" t="inlineStr"/>
+      <c r="R463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>零壹</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>121</v>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G464" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H464" t="n">
+        <v>97</v>
+      </c>
+      <c r="I464" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J464" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K464" t="inlineStr"/>
+      <c r="L464" t="inlineStr"/>
+      <c r="M464" t="inlineStr"/>
+      <c r="N464" t="inlineStr"/>
+      <c r="O464" t="inlineStr"/>
+      <c r="P464" t="inlineStr"/>
+      <c r="Q464" t="inlineStr"/>
+      <c r="R464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>109.5</v>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G465" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H465" t="n">
+        <v>94</v>
+      </c>
+      <c r="I465" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J465" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K465" t="inlineStr"/>
+      <c r="L465" t="inlineStr"/>
+      <c r="M465" t="inlineStr"/>
+      <c r="N465" t="inlineStr"/>
+      <c r="O465" t="inlineStr"/>
+      <c r="P465" t="inlineStr"/>
+      <c r="Q465" t="inlineStr"/>
+      <c r="R465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>隆大</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>25.95</v>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G466" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H466" t="n">
+        <v>94</v>
+      </c>
+      <c r="I466" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J466" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K466" t="inlineStr"/>
+      <c r="L466" t="inlineStr"/>
+      <c r="M466" t="inlineStr"/>
+      <c r="N466" t="inlineStr"/>
+      <c r="O466" t="inlineStr"/>
+      <c r="P466" t="inlineStr"/>
+      <c r="Q466" t="inlineStr"/>
+      <c r="R466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>東科-KY</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>55.7</v>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G467" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H467" t="n">
+        <v>78</v>
+      </c>
+      <c r="I467" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J467" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K467" t="inlineStr"/>
+      <c r="L467" t="inlineStr"/>
+      <c r="M467" t="inlineStr"/>
+      <c r="N467" t="inlineStr"/>
+      <c r="O467" t="inlineStr"/>
+      <c r="P467" t="inlineStr"/>
+      <c r="Q467" t="inlineStr"/>
+      <c r="R467" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25799,7 +26103,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -25817,7 +26121,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6025</v>
+        <v>6325</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -25839,10 +26143,10 @@
         <v>0.26</v>
       </c>
       <c r="K2" t="n">
-        <v>2270</v>
+        <v>2150</v>
       </c>
       <c r="L2" t="n">
-        <v>-62.32</v>
+        <v>-66.01000000000001</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -25851,12 +26155,12 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>-62.32</v>
+        <v>-66.01000000000001</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -25874,7 +26178,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5925</v>
+        <v>6025</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -25896,10 +26200,10 @@
         <v>0.26</v>
       </c>
       <c r="K3" t="n">
-        <v>2610</v>
+        <v>2270</v>
       </c>
       <c r="L3" t="n">
-        <v>-55.95</v>
+        <v>-62.32</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -25908,12 +26212,12 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>-55.95</v>
+        <v>-62.32</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46202</v>
+        <v>46237</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -25922,16 +26226,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>499.5</v>
+        <v>5925</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -25940,23 +26244,23 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="I4" t="n">
-        <v>21.2</v>
+        <v>9.6</v>
       </c>
       <c r="J4" t="n">
-        <v>0.92</v>
+        <v>0.26</v>
       </c>
       <c r="K4" t="n">
-        <v>339.5</v>
+        <v>2610</v>
       </c>
       <c r="L4" t="n">
-        <v>-32.03</v>
+        <v>-55.95</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -25965,7 +26269,7 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>-32.03</v>
+        <v>-55.95</v>
       </c>
     </row>
     <row r="5">
@@ -25979,16 +26283,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>955</v>
+        <v>499.5</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -26001,19 +26305,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I5" t="n">
-        <v>14.2</v>
+        <v>21.2</v>
       </c>
       <c r="J5" t="n">
-        <v>0.4</v>
+        <v>0.92</v>
       </c>
       <c r="K5" t="n">
-        <v>671</v>
+        <v>339.5</v>
       </c>
       <c r="L5" t="n">
-        <v>-29.74</v>
+        <v>-32.03</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -26022,12 +26326,12 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-29.74</v>
+        <v>-32.03</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46251</v>
+        <v>46202</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -26036,37 +26340,41 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>47.15</v>
+        <v>955</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>75</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I6" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.4</v>
+      </c>
       <c r="K6" t="n">
-        <v>34.8</v>
+        <v>671</v>
       </c>
       <c r="L6" t="n">
-        <v>-26.19</v>
+        <v>-29.74</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -26075,12 +26383,12 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>-26.19</v>
+        <v>-29.74</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46202</v>
+        <v>46251</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -26089,20 +26397,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>65.5</v>
+        <v>47.15</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -26111,19 +26419,15 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>77</v>
-      </c>
-      <c r="I7" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.71</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>51.7</v>
+        <v>34.8</v>
       </c>
       <c r="L7" t="n">
-        <v>-21.07</v>
+        <v>-26.19</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -26132,12 +26436,12 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>-21.07</v>
+        <v>-26.19</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -26146,20 +26450,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>158</v>
+        <v>65.5</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -26171,16 +26475,16 @@
         <v>77</v>
       </c>
       <c r="I8" t="n">
-        <v>16.4</v>
+        <v>10.4</v>
       </c>
       <c r="J8" t="n">
-        <v>1.11</v>
+        <v>0.71</v>
       </c>
       <c r="K8" t="n">
-        <v>125.5</v>
+        <v>51.7</v>
       </c>
       <c r="L8" t="n">
-        <v>-20.57</v>
+        <v>-21.07</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -26189,12 +26493,12 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>-20.57</v>
+        <v>-21.07</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -26203,16 +26507,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>344.5</v>
+        <v>158</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -26221,23 +26525,23 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I9" t="n">
-        <v>27.5</v>
+        <v>16.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="K9" t="n">
-        <v>277.5</v>
+        <v>125.5</v>
       </c>
       <c r="L9" t="n">
-        <v>-19.45</v>
+        <v>-20.57</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -26246,7 +26550,7 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>-19.45</v>
+        <v>-20.57</v>
       </c>
     </row>
     <row r="10">
@@ -26260,20 +26564,20 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1215</v>
+        <v>344.5</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -26285,16 +26589,16 @@
         <v>90</v>
       </c>
       <c r="I10" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0.67</v>
+        <v>1.22</v>
       </c>
       <c r="K10" t="n">
-        <v>981</v>
+        <v>277.5</v>
       </c>
       <c r="L10" t="n">
-        <v>-19.26</v>
+        <v>-19.45</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -26303,7 +26607,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>-19.26</v>
+        <v>-19.45</v>
       </c>
     </row>
     <row r="11">
@@ -26317,41 +26621,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>143</v>
+        <v>1215</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
-        <v>16.4</v>
+        <v>25</v>
       </c>
       <c r="J11" t="n">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="K11" t="n">
-        <v>115.5</v>
+        <v>981</v>
       </c>
       <c r="L11" t="n">
-        <v>-19.23</v>
+        <v>-19.26</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -26360,12 +26664,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-19.23</v>
+        <v>-19.26</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46244</v>
+        <v>46202</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -26374,20 +26678,20 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>66.7</v>
+        <v>143</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -26396,19 +26700,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I12" t="n">
-        <v>6.8</v>
+        <v>16.4</v>
       </c>
       <c r="J12" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="K12" t="n">
-        <v>53.9</v>
+        <v>115.5</v>
       </c>
       <c r="L12" t="n">
-        <v>-19.19</v>
+        <v>-19.23</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -26417,12 +26721,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-19.19</v>
+        <v>-19.23</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46202</v>
+        <v>46244</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -26431,16 +26735,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>34.2</v>
+        <v>66.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -26449,23 +26753,23 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="I13" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>27.65</v>
+        <v>53.9</v>
       </c>
       <c r="L13" t="n">
-        <v>-19.15</v>
+        <v>-19.19</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -26474,12 +26778,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-19.15</v>
+        <v>-19.19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46252</v>
+        <v>46202</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -26488,16 +26792,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2225</v>
+        <v>34.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -26510,19 +26814,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I14" t="n">
-        <v>30.7</v>
+        <v>5.9</v>
       </c>
       <c r="J14" t="n">
-        <v>0.82</v>
+        <v>0.42</v>
       </c>
       <c r="K14" t="n">
-        <v>1800</v>
+        <v>27.65</v>
       </c>
       <c r="L14" t="n">
-        <v>-19.1</v>
+        <v>-19.15</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -26531,12 +26835,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-19.1</v>
+        <v>-19.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46210</v>
+        <v>46252</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -26545,16 +26849,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>373</v>
+        <v>2225</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -26563,23 +26867,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I15" t="n">
-        <v>13.2</v>
+        <v>30.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.49</v>
+        <v>0.82</v>
       </c>
       <c r="K15" t="n">
-        <v>302</v>
+        <v>1800</v>
       </c>
       <c r="L15" t="n">
-        <v>-19.03</v>
+        <v>-19.1</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -26588,7 +26892,7 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-19.03</v>
+        <v>-19.1</v>
       </c>
     </row>
     <row r="16">
@@ -26602,16 +26906,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>34.15</v>
+        <v>373</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -26620,23 +26924,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>94</v>
+        <v>65</v>
       </c>
       <c r="I16" t="n">
-        <v>5.9</v>
+        <v>13.2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.42</v>
+        <v>0.49</v>
       </c>
       <c r="K16" t="n">
-        <v>27.75</v>
+        <v>302</v>
       </c>
       <c r="L16" t="n">
-        <v>-18.74</v>
+        <v>-19.03</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -26645,7 +26949,7 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-18.74</v>
+        <v>-19.03</v>
       </c>
     </row>
     <row r="17">
@@ -26707,7 +27011,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -26716,16 +27020,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2340</v>
+        <v>34.15</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -26738,19 +27042,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I18" t="n">
-        <v>30.7</v>
+        <v>5.9</v>
       </c>
       <c r="J18" t="n">
-        <v>0.82</v>
+        <v>0.42</v>
       </c>
       <c r="K18" t="n">
-        <v>1910</v>
+        <v>27.75</v>
       </c>
       <c r="L18" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -26759,12 +27063,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46226</v>
+        <v>46202</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -26773,16 +27077,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1180</v>
+        <v>2340</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -26795,19 +27099,19 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>30.7</v>
       </c>
       <c r="J19" t="n">
-        <v>0.67</v>
+        <v>0.82</v>
       </c>
       <c r="K19" t="n">
-        <v>967</v>
+        <v>1910</v>
       </c>
       <c r="L19" t="n">
-        <v>-18.05</v>
+        <v>-18.38</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -26816,7 +27120,7 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-18.05</v>
+        <v>-18.38</v>
       </c>
     </row>
     <row r="20">
@@ -26830,16 +27134,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>72.59999999999999</v>
+        <v>1180</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -26848,23 +27152,23 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I20" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="K20" t="n">
-        <v>59.6</v>
+        <v>967</v>
       </c>
       <c r="L20" t="n">
-        <v>-17.91</v>
+        <v>-18.05</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -26873,12 +27177,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-17.91</v>
+        <v>-18.05</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -26896,7 +27200,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>72.5</v>
+        <v>72.59999999999999</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -26918,10 +27222,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>60.4</v>
+        <v>59.6</v>
       </c>
       <c r="L21" t="n">
-        <v>-16.69</v>
+        <v>-17.91</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -26930,7 +27234,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-16.69</v>
+        <v>-17.91</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R467"/>
+  <dimension ref="A1:R495"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -24750,6 +24750,1390 @@
       <c r="P467" t="inlineStr"/>
       <c r="Q467" t="inlineStr"/>
       <c r="R467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>534</v>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G468" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H468" t="n">
+        <v>96</v>
+      </c>
+      <c r="I468" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J468" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K468" t="inlineStr"/>
+      <c r="L468" t="inlineStr"/>
+      <c r="M468" t="inlineStr"/>
+      <c r="N468" t="inlineStr"/>
+      <c r="O468" t="inlineStr"/>
+      <c r="P468" t="inlineStr"/>
+      <c r="Q468" t="inlineStr"/>
+      <c r="R468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>317.5</v>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G469" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H469" t="n">
+        <v>90</v>
+      </c>
+      <c r="I469" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J469" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K469" t="inlineStr"/>
+      <c r="L469" t="inlineStr"/>
+      <c r="M469" t="inlineStr"/>
+      <c r="N469" t="inlineStr"/>
+      <c r="O469" t="inlineStr"/>
+      <c r="P469" t="inlineStr"/>
+      <c r="Q469" t="inlineStr"/>
+      <c r="R469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>82</v>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G470" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H470" t="n">
+        <v>87</v>
+      </c>
+      <c r="I470" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J470" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K470" t="inlineStr"/>
+      <c r="L470" t="inlineStr"/>
+      <c r="M470" t="inlineStr"/>
+      <c r="N470" t="inlineStr"/>
+      <c r="O470" t="inlineStr"/>
+      <c r="P470" t="inlineStr"/>
+      <c r="Q470" t="inlineStr"/>
+      <c r="R470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>漢科</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>126.5</v>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G471" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H471" t="n">
+        <v>77</v>
+      </c>
+      <c r="I471" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J471" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K471" t="inlineStr"/>
+      <c r="L471" t="inlineStr"/>
+      <c r="M471" t="inlineStr"/>
+      <c r="N471" t="inlineStr"/>
+      <c r="O471" t="inlineStr"/>
+      <c r="P471" t="inlineStr"/>
+      <c r="Q471" t="inlineStr"/>
+      <c r="R471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>253</v>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G472" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H472" t="n">
+        <v>77</v>
+      </c>
+      <c r="I472" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J472" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K472" t="inlineStr"/>
+      <c r="L472" t="inlineStr"/>
+      <c r="M472" t="inlineStr"/>
+      <c r="N472" t="inlineStr"/>
+      <c r="O472" t="inlineStr"/>
+      <c r="P472" t="inlineStr"/>
+      <c r="Q472" t="inlineStr"/>
+      <c r="R472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G473" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H473" t="n">
+        <v>76</v>
+      </c>
+      <c r="I473" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J473" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K473" t="inlineStr"/>
+      <c r="L473" t="inlineStr"/>
+      <c r="M473" t="inlineStr"/>
+      <c r="N473" t="inlineStr"/>
+      <c r="O473" t="inlineStr"/>
+      <c r="P473" t="inlineStr"/>
+      <c r="Q473" t="inlineStr"/>
+      <c r="R473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>61.2</v>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G474" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H474" t="n">
+        <v>68</v>
+      </c>
+      <c r="I474" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J474" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K474" t="inlineStr"/>
+      <c r="L474" t="inlineStr"/>
+      <c r="M474" t="inlineStr"/>
+      <c r="N474" t="inlineStr"/>
+      <c r="O474" t="inlineStr"/>
+      <c r="P474" t="inlineStr"/>
+      <c r="Q474" t="inlineStr"/>
+      <c r="R474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>3390</v>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G475" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H475" t="n">
+        <v>100</v>
+      </c>
+      <c r="I475" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J475" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K475" t="inlineStr"/>
+      <c r="L475" t="inlineStr"/>
+      <c r="M475" t="inlineStr"/>
+      <c r="N475" t="inlineStr"/>
+      <c r="O475" t="inlineStr"/>
+      <c r="P475" t="inlineStr"/>
+      <c r="Q475" t="inlineStr"/>
+      <c r="R475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>715</v>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G476" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H476" t="n">
+        <v>100</v>
+      </c>
+      <c r="I476" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J476" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K476" t="inlineStr"/>
+      <c r="L476" t="inlineStr"/>
+      <c r="M476" t="inlineStr"/>
+      <c r="N476" t="inlineStr"/>
+      <c r="O476" t="inlineStr"/>
+      <c r="P476" t="inlineStr"/>
+      <c r="Q476" t="inlineStr"/>
+      <c r="R476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>2460</v>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G477" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H477" t="n">
+        <v>100</v>
+      </c>
+      <c r="I477" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J477" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K477" t="inlineStr"/>
+      <c r="L477" t="inlineStr"/>
+      <c r="M477" t="inlineStr"/>
+      <c r="N477" t="inlineStr"/>
+      <c r="O477" t="inlineStr"/>
+      <c r="P477" t="inlineStr"/>
+      <c r="Q477" t="inlineStr"/>
+      <c r="R477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>105</v>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G478" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H478" t="n">
+        <v>94</v>
+      </c>
+      <c r="I478" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J478" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K478" t="inlineStr"/>
+      <c r="L478" t="inlineStr"/>
+      <c r="M478" t="inlineStr"/>
+      <c r="N478" t="inlineStr"/>
+      <c r="O478" t="inlineStr"/>
+      <c r="P478" t="inlineStr"/>
+      <c r="Q478" t="inlineStr"/>
+      <c r="R478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>八方雲集</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>181</v>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G479" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H479" t="n">
+        <v>94</v>
+      </c>
+      <c r="I479" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J479" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K479" t="inlineStr"/>
+      <c r="L479" t="inlineStr"/>
+      <c r="M479" t="inlineStr"/>
+      <c r="N479" t="inlineStr"/>
+      <c r="O479" t="inlineStr"/>
+      <c r="P479" t="inlineStr"/>
+      <c r="Q479" t="inlineStr"/>
+      <c r="R479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>42.5</v>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G480" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H480" t="n">
+        <v>92</v>
+      </c>
+      <c r="I480" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J480" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K480" t="inlineStr"/>
+      <c r="L480" t="inlineStr"/>
+      <c r="M480" t="inlineStr"/>
+      <c r="N480" t="inlineStr"/>
+      <c r="O480" t="inlineStr"/>
+      <c r="P480" t="inlineStr"/>
+      <c r="Q480" t="inlineStr"/>
+      <c r="R480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="E481" t="n">
+        <v>898</v>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G481" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H481" t="n">
+        <v>90</v>
+      </c>
+      <c r="I481" t="n">
+        <v>25</v>
+      </c>
+      <c r="J481" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K481" t="inlineStr"/>
+      <c r="L481" t="inlineStr"/>
+      <c r="M481" t="inlineStr"/>
+      <c r="N481" t="inlineStr"/>
+      <c r="O481" t="inlineStr"/>
+      <c r="P481" t="inlineStr"/>
+      <c r="Q481" t="inlineStr"/>
+      <c r="R481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="E482" t="n">
+        <v>539</v>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G482" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H482" t="n">
+        <v>90</v>
+      </c>
+      <c r="I482" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J482" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K482" t="inlineStr"/>
+      <c r="L482" t="inlineStr"/>
+      <c r="M482" t="inlineStr"/>
+      <c r="N482" t="inlineStr"/>
+      <c r="O482" t="inlineStr"/>
+      <c r="P482" t="inlineStr"/>
+      <c r="Q482" t="inlineStr"/>
+      <c r="R482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="E483" t="n">
+        <v>167</v>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G483" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H483" t="n">
+        <v>90</v>
+      </c>
+      <c r="I483" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J483" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K483" t="inlineStr"/>
+      <c r="L483" t="inlineStr"/>
+      <c r="M483" t="inlineStr"/>
+      <c r="N483" t="inlineStr"/>
+      <c r="O483" t="inlineStr"/>
+      <c r="P483" t="inlineStr"/>
+      <c r="Q483" t="inlineStr"/>
+      <c r="R483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+      <c r="E484" t="n">
+        <v>39.2</v>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G484" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H484" t="n">
+        <v>84</v>
+      </c>
+      <c r="I484" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J484" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K484" t="inlineStr"/>
+      <c r="L484" t="inlineStr"/>
+      <c r="M484" t="inlineStr"/>
+      <c r="N484" t="inlineStr"/>
+      <c r="O484" t="inlineStr"/>
+      <c r="P484" t="inlineStr"/>
+      <c r="Q484" t="inlineStr"/>
+      <c r="R484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="E485" t="n">
+        <v>1915</v>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G485" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H485" t="n">
+        <v>80</v>
+      </c>
+      <c r="I485" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J485" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K485" t="inlineStr"/>
+      <c r="L485" t="inlineStr"/>
+      <c r="M485" t="inlineStr"/>
+      <c r="N485" t="inlineStr"/>
+      <c r="O485" t="inlineStr"/>
+      <c r="P485" t="inlineStr"/>
+      <c r="Q485" t="inlineStr"/>
+      <c r="R485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="E486" t="n">
+        <v>1600</v>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G486" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H486" t="n">
+        <v>80</v>
+      </c>
+      <c r="I486" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J486" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K486" t="inlineStr"/>
+      <c r="L486" t="inlineStr"/>
+      <c r="M486" t="inlineStr"/>
+      <c r="N486" t="inlineStr"/>
+      <c r="O486" t="inlineStr"/>
+      <c r="P486" t="inlineStr"/>
+      <c r="Q486" t="inlineStr"/>
+      <c r="R486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>達欣工</t>
+        </is>
+      </c>
+      <c r="E487" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G487" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H487" t="n">
+        <v>79</v>
+      </c>
+      <c r="I487" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J487" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K487" t="inlineStr"/>
+      <c r="L487" t="inlineStr"/>
+      <c r="M487" t="inlineStr"/>
+      <c r="N487" t="inlineStr"/>
+      <c r="O487" t="inlineStr"/>
+      <c r="P487" t="inlineStr"/>
+      <c r="Q487" t="inlineStr"/>
+      <c r="R487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>友輝</t>
+        </is>
+      </c>
+      <c r="E488" t="n">
+        <v>53.1</v>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G488" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H488" t="n">
+        <v>77</v>
+      </c>
+      <c r="I488" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J488" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K488" t="inlineStr"/>
+      <c r="L488" t="inlineStr"/>
+      <c r="M488" t="inlineStr"/>
+      <c r="N488" t="inlineStr"/>
+      <c r="O488" t="inlineStr"/>
+      <c r="P488" t="inlineStr"/>
+      <c r="Q488" t="inlineStr"/>
+      <c r="R488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="E489" t="n">
+        <v>342</v>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G489" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H489" t="n">
+        <v>65</v>
+      </c>
+      <c r="I489" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J489" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K489" t="inlineStr"/>
+      <c r="L489" t="inlineStr"/>
+      <c r="M489" t="inlineStr"/>
+      <c r="N489" t="inlineStr"/>
+      <c r="O489" t="inlineStr"/>
+      <c r="P489" t="inlineStr"/>
+      <c r="Q489" t="inlineStr"/>
+      <c r="R489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="E490" t="n">
+        <v>180.5</v>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G490" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H490" t="n">
+        <v>62</v>
+      </c>
+      <c r="I490" t="n">
+        <v>10</v>
+      </c>
+      <c r="J490" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K490" t="inlineStr"/>
+      <c r="L490" t="inlineStr"/>
+      <c r="M490" t="inlineStr"/>
+      <c r="N490" t="inlineStr"/>
+      <c r="O490" t="inlineStr"/>
+      <c r="P490" t="inlineStr"/>
+      <c r="Q490" t="inlineStr"/>
+      <c r="R490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+      <c r="E491" t="n">
+        <v>1475</v>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G491" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H491" t="n">
+        <v>60</v>
+      </c>
+      <c r="I491" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J491" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K491" t="inlineStr"/>
+      <c r="L491" t="inlineStr"/>
+      <c r="M491" t="inlineStr"/>
+      <c r="N491" t="inlineStr"/>
+      <c r="O491" t="inlineStr"/>
+      <c r="P491" t="inlineStr"/>
+      <c r="Q491" t="inlineStr"/>
+      <c r="R491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>德昌</t>
+        </is>
+      </c>
+      <c r="E492" t="n">
+        <v>69.3</v>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G492" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H492" t="n">
+        <v>79</v>
+      </c>
+      <c r="I492" t="inlineStr"/>
+      <c r="J492" t="inlineStr"/>
+      <c r="K492" t="inlineStr"/>
+      <c r="L492" t="inlineStr"/>
+      <c r="M492" t="inlineStr"/>
+      <c r="N492" t="inlineStr"/>
+      <c r="O492" t="inlineStr"/>
+      <c r="P492" t="inlineStr"/>
+      <c r="Q492" t="inlineStr"/>
+      <c r="R492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+      <c r="E493" t="n">
+        <v>384</v>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G493" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H493" t="n">
+        <v>77</v>
+      </c>
+      <c r="I493" t="inlineStr"/>
+      <c r="J493" t="inlineStr"/>
+      <c r="K493" t="inlineStr"/>
+      <c r="L493" t="inlineStr"/>
+      <c r="M493" t="inlineStr"/>
+      <c r="N493" t="inlineStr"/>
+      <c r="O493" t="inlineStr"/>
+      <c r="P493" t="inlineStr"/>
+      <c r="Q493" t="inlineStr"/>
+      <c r="R493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>鑫龍騰</t>
+        </is>
+      </c>
+      <c r="E494" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G494" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H494" t="n">
+        <v>77</v>
+      </c>
+      <c r="I494" t="inlineStr"/>
+      <c r="J494" t="inlineStr"/>
+      <c r="K494" t="inlineStr"/>
+      <c r="L494" t="inlineStr"/>
+      <c r="M494" t="inlineStr"/>
+      <c r="N494" t="inlineStr"/>
+      <c r="O494" t="inlineStr"/>
+      <c r="P494" t="inlineStr"/>
+      <c r="Q494" t="inlineStr"/>
+      <c r="R494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="E495" t="n">
+        <v>201.5</v>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G495" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H495" t="n">
+        <v>69</v>
+      </c>
+      <c r="I495" t="inlineStr"/>
+      <c r="J495" t="inlineStr"/>
+      <c r="K495" t="inlineStr"/>
+      <c r="L495" t="inlineStr"/>
+      <c r="M495" t="inlineStr"/>
+      <c r="N495" t="inlineStr"/>
+      <c r="O495" t="inlineStr"/>
+      <c r="P495" t="inlineStr"/>
+      <c r="Q495" t="inlineStr"/>
+      <c r="R495" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -604,7 +604,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R495"/>
+  <dimension ref="A1:R496"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26134,6 +26134,56 @@
       <c r="P495" t="inlineStr"/>
       <c r="Q495" t="inlineStr"/>
       <c r="R495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="E496" t="n">
+        <v>2105</v>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G496" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H496" t="n">
+        <v>65</v>
+      </c>
+      <c r="I496" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J496" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K496" t="inlineStr"/>
+      <c r="L496" t="inlineStr"/>
+      <c r="M496" t="inlineStr"/>
+      <c r="N496" t="inlineStr"/>
+      <c r="O496" t="inlineStr"/>
+      <c r="P496" t="inlineStr"/>
+      <c r="Q496" t="inlineStr"/>
+      <c r="R496" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="C2" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.79</v>
+        <v>-0.93</v>
       </c>
       <c r="E2" t="n">
         <v>-1.37</v>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="D2" t="n">
-        <v>42.8</v>
+        <v>42.6</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.79</v>
+        <v>-0.93</v>
       </c>
     </row>
   </sheetData>
@@ -18964,8 +18964,12 @@
       </c>
       <c r="I350" t="inlineStr"/>
       <c r="J350" t="inlineStr"/>
-      <c r="K350" t="inlineStr"/>
-      <c r="L350" t="inlineStr"/>
+      <c r="K350" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="L350" t="n">
+        <v>-36</v>
+      </c>
       <c r="M350" t="inlineStr"/>
       <c r="N350" t="inlineStr"/>
       <c r="O350" t="inlineStr"/>
@@ -27708,7 +27712,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46202</v>
+        <v>46259</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -27717,41 +27721,37 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>499.5</v>
+        <v>53.2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>90</v>
-      </c>
-      <c r="I5" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="J5" t="n">
-        <v>0.92</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>339.5</v>
+        <v>34.05</v>
       </c>
       <c r="L5" t="n">
-        <v>-32.03</v>
+        <v>-36</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -27760,7 +27760,7 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-32.03</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="6">
@@ -27774,16 +27774,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>955</v>
+        <v>499.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -27796,19 +27796,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I6" t="n">
-        <v>14.2</v>
+        <v>21.2</v>
       </c>
       <c r="J6" t="n">
-        <v>0.4</v>
+        <v>0.92</v>
       </c>
       <c r="K6" t="n">
-        <v>671</v>
+        <v>339.5</v>
       </c>
       <c r="L6" t="n">
-        <v>-29.74</v>
+        <v>-32.03</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -27817,12 +27817,12 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>-29.74</v>
+        <v>-32.03</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46251</v>
+        <v>46202</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -27831,37 +27831,41 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>47.15</v>
+        <v>955</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>75</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+        <v>100</v>
+      </c>
+      <c r="I7" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.4</v>
+      </c>
       <c r="K7" t="n">
-        <v>34.8</v>
+        <v>671</v>
       </c>
       <c r="L7" t="n">
-        <v>-26.19</v>
+        <v>-29.74</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -27870,12 +27874,12 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>-26.19</v>
+        <v>-29.74</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46202</v>
+        <v>46251</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -27884,20 +27888,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>65.5</v>
+        <v>47.15</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -27906,19 +27910,15 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>77</v>
-      </c>
-      <c r="I8" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.71</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>51.7</v>
+        <v>34.8</v>
       </c>
       <c r="L8" t="n">
-        <v>-21.07</v>
+        <v>-26.19</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -27927,12 +27927,12 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>-21.07</v>
+        <v>-26.19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -27941,20 +27941,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>158</v>
+        <v>65.5</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -27966,16 +27966,16 @@
         <v>77</v>
       </c>
       <c r="I9" t="n">
-        <v>16.4</v>
+        <v>10.4</v>
       </c>
       <c r="J9" t="n">
-        <v>1.11</v>
+        <v>0.71</v>
       </c>
       <c r="K9" t="n">
-        <v>125.5</v>
+        <v>51.7</v>
       </c>
       <c r="L9" t="n">
-        <v>-20.57</v>
+        <v>-21.07</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -27984,12 +27984,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>-20.57</v>
+        <v>-21.07</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -27998,16 +27998,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>344.5</v>
+        <v>158</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -28016,23 +28016,23 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I10" t="n">
-        <v>27.5</v>
+        <v>16.4</v>
       </c>
       <c r="J10" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="K10" t="n">
-        <v>277.5</v>
+        <v>125.5</v>
       </c>
       <c r="L10" t="n">
-        <v>-19.45</v>
+        <v>-20.57</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -28041,7 +28041,7 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>-19.45</v>
+        <v>-20.57</v>
       </c>
     </row>
     <row r="11">
@@ -28055,20 +28055,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1215</v>
+        <v>344.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -28080,16 +28080,16 @@
         <v>90</v>
       </c>
       <c r="I11" t="n">
-        <v>25</v>
+        <v>27.5</v>
       </c>
       <c r="J11" t="n">
-        <v>0.67</v>
+        <v>1.22</v>
       </c>
       <c r="K11" t="n">
-        <v>981</v>
+        <v>277.5</v>
       </c>
       <c r="L11" t="n">
-        <v>-19.26</v>
+        <v>-19.45</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -28098,7 +28098,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-19.26</v>
+        <v>-19.45</v>
       </c>
     </row>
     <row r="12">
@@ -28112,41 +28112,41 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>143</v>
+        <v>1215</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
-        <v>16.4</v>
+        <v>25</v>
       </c>
       <c r="J12" t="n">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="K12" t="n">
-        <v>115.5</v>
+        <v>981</v>
       </c>
       <c r="L12" t="n">
-        <v>-19.23</v>
+        <v>-19.26</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -28155,12 +28155,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-19.23</v>
+        <v>-19.26</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46244</v>
+        <v>46202</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -28169,20 +28169,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>66.7</v>
+        <v>143</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -28191,19 +28191,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I13" t="n">
-        <v>6.8</v>
+        <v>16.4</v>
       </c>
       <c r="J13" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="K13" t="n">
-        <v>53.9</v>
+        <v>115.5</v>
       </c>
       <c r="L13" t="n">
-        <v>-19.19</v>
+        <v>-19.23</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -28212,12 +28212,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-19.19</v>
+        <v>-19.23</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46202</v>
+        <v>46244</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -28226,16 +28226,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>34.2</v>
+        <v>66.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -28244,23 +28244,23 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="I14" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>27.65</v>
+        <v>53.9</v>
       </c>
       <c r="L14" t="n">
-        <v>-19.15</v>
+        <v>-19.19</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -28269,12 +28269,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-19.15</v>
+        <v>-19.19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46252</v>
+        <v>46202</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -28283,16 +28283,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2225</v>
+        <v>34.2</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -28305,19 +28305,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>80</v>
+        <v>94</v>
       </c>
       <c r="I15" t="n">
-        <v>30.7</v>
+        <v>5.9</v>
       </c>
       <c r="J15" t="n">
-        <v>0.82</v>
+        <v>0.42</v>
       </c>
       <c r="K15" t="n">
-        <v>1800</v>
+        <v>27.65</v>
       </c>
       <c r="L15" t="n">
-        <v>-19.1</v>
+        <v>-19.15</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -28326,12 +28326,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-19.1</v>
+        <v>-19.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46210</v>
+        <v>46252</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -28340,16 +28340,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>373</v>
+        <v>2225</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -28358,23 +28358,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I16" t="n">
-        <v>13.2</v>
+        <v>30.7</v>
       </c>
       <c r="J16" t="n">
-        <v>0.49</v>
+        <v>0.82</v>
       </c>
       <c r="K16" t="n">
-        <v>302</v>
+        <v>1800</v>
       </c>
       <c r="L16" t="n">
-        <v>-19.03</v>
+        <v>-19.1</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -28383,12 +28383,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-19.03</v>
+        <v>-19.1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46226</v>
+        <v>46210</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -28397,20 +28397,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1190</v>
+        <v>373</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -28419,19 +28419,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="I17" t="n">
-        <v>38.8</v>
+        <v>13.2</v>
       </c>
       <c r="J17" t="n">
-        <v>1.03</v>
+        <v>0.49</v>
       </c>
       <c r="K17" t="n">
-        <v>967</v>
+        <v>302</v>
       </c>
       <c r="L17" t="n">
-        <v>-18.74</v>
+        <v>-19.03</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -28440,7 +28440,7 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-18.74</v>
+        <v>-19.03</v>
       </c>
     </row>
     <row r="18">
@@ -28502,7 +28502,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46202</v>
+        <v>46226</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -28511,41 +28511,41 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2340</v>
+        <v>1190</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I19" t="n">
-        <v>30.7</v>
+        <v>38.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0.82</v>
+        <v>1.03</v>
       </c>
       <c r="K19" t="n">
-        <v>1910</v>
+        <v>967</v>
       </c>
       <c r="L19" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -28554,12 +28554,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-18.38</v>
+        <v>-18.74</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46226</v>
+        <v>46202</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -28568,16 +28568,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1180</v>
+        <v>2340</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -28590,19 +28590,19 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I20" t="n">
-        <v>25</v>
+        <v>30.7</v>
       </c>
       <c r="J20" t="n">
-        <v>0.67</v>
+        <v>0.82</v>
       </c>
       <c r="K20" t="n">
-        <v>967</v>
+        <v>1910</v>
       </c>
       <c r="L20" t="n">
-        <v>-18.05</v>
+        <v>-18.38</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -28611,7 +28611,7 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-18.05</v>
+        <v>-18.38</v>
       </c>
     </row>
     <row r="21">
@@ -28625,16 +28625,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>72.59999999999999</v>
+        <v>1180</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -28643,23 +28643,23 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I21" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="J21" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="K21" t="n">
-        <v>59.6</v>
+        <v>967</v>
       </c>
       <c r="L21" t="n">
-        <v>-17.91</v>
+        <v>-18.05</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -28668,7 +28668,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-17.91</v>
+        <v>-18.05</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,19 +468,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="C2" t="n">
-        <v>42.6</v>
+        <v>43.2</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.93</v>
+        <v>-0.64</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.37</v>
+        <v>-1.25</v>
       </c>
       <c r="F2" t="n">
-        <v>49.42</v>
+        <v>60.56</v>
       </c>
       <c r="G2" t="n">
         <v>-66.01000000000001</v>
@@ -584,13 +584,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>251</v>
+        <v>285</v>
       </c>
       <c r="D2" t="n">
-        <v>42.6</v>
+        <v>43.2</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.93</v>
+        <v>-0.64</v>
       </c>
     </row>
   </sheetData>
@@ -19018,8 +19018,12 @@
       <c r="J351" t="n">
         <v>1.29</v>
       </c>
-      <c r="K351" t="inlineStr"/>
-      <c r="L351" t="inlineStr"/>
+      <c r="K351" t="n">
+        <v>157</v>
+      </c>
+      <c r="L351" t="n">
+        <v>0</v>
+      </c>
       <c r="M351" t="inlineStr"/>
       <c r="N351" t="inlineStr"/>
       <c r="O351" t="inlineStr"/>
@@ -19068,8 +19072,12 @@
       <c r="J352" t="n">
         <v>1.11</v>
       </c>
-      <c r="K352" t="inlineStr"/>
-      <c r="L352" t="inlineStr"/>
+      <c r="K352" t="n">
+        <v>542</v>
+      </c>
+      <c r="L352" t="n">
+        <v>1.12</v>
+      </c>
       <c r="M352" t="inlineStr"/>
       <c r="N352" t="inlineStr"/>
       <c r="O352" t="inlineStr"/>
@@ -19118,8 +19126,12 @@
       <c r="J353" t="n">
         <v>1.26</v>
       </c>
-      <c r="K353" t="inlineStr"/>
-      <c r="L353" t="inlineStr"/>
+      <c r="K353" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="L353" t="n">
+        <v>-4.05</v>
+      </c>
       <c r="M353" t="inlineStr"/>
       <c r="N353" t="inlineStr"/>
       <c r="O353" t="inlineStr"/>
@@ -19168,8 +19180,12 @@
       <c r="J354" t="n">
         <v>1.22</v>
       </c>
-      <c r="K354" t="inlineStr"/>
-      <c r="L354" t="inlineStr"/>
+      <c r="K354" t="n">
+        <v>320</v>
+      </c>
+      <c r="L354" t="n">
+        <v>4.23</v>
+      </c>
       <c r="M354" t="inlineStr"/>
       <c r="N354" t="inlineStr"/>
       <c r="O354" t="inlineStr"/>
@@ -19218,8 +19234,12 @@
       <c r="J355" t="n">
         <v>1.36</v>
       </c>
-      <c r="K355" t="inlineStr"/>
-      <c r="L355" t="inlineStr"/>
+      <c r="K355" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="L355" t="n">
+        <v>-5.4</v>
+      </c>
       <c r="M355" t="inlineStr"/>
       <c r="N355" t="inlineStr"/>
       <c r="O355" t="inlineStr"/>
@@ -19268,8 +19288,12 @@
       <c r="J356" t="n">
         <v>1.11</v>
       </c>
-      <c r="K356" t="inlineStr"/>
-      <c r="L356" t="inlineStr"/>
+      <c r="K356" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="L356" t="n">
+        <v>7.47</v>
+      </c>
       <c r="M356" t="inlineStr"/>
       <c r="N356" t="inlineStr"/>
       <c r="O356" t="inlineStr"/>
@@ -19318,8 +19342,12 @@
       <c r="J357" t="n">
         <v>1.16</v>
       </c>
-      <c r="K357" t="inlineStr"/>
-      <c r="L357" t="inlineStr"/>
+      <c r="K357" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="L357" t="n">
+        <v>1.62</v>
+      </c>
       <c r="M357" t="inlineStr"/>
       <c r="N357" t="inlineStr"/>
       <c r="O357" t="inlineStr"/>
@@ -19368,8 +19396,12 @@
       <c r="J358" t="n">
         <v>1.03</v>
       </c>
-      <c r="K358" t="inlineStr"/>
-      <c r="L358" t="inlineStr"/>
+      <c r="K358" t="n">
+        <v>1110</v>
+      </c>
+      <c r="L358" t="n">
+        <v>15.62</v>
+      </c>
       <c r="M358" t="inlineStr"/>
       <c r="N358" t="inlineStr"/>
       <c r="O358" t="inlineStr"/>
@@ -19418,8 +19450,12 @@
       <c r="J359" t="n">
         <v>1.35</v>
       </c>
-      <c r="K359" t="inlineStr"/>
-      <c r="L359" t="inlineStr"/>
+      <c r="K359" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="L359" t="n">
+        <v>-10.33</v>
+      </c>
       <c r="M359" t="inlineStr"/>
       <c r="N359" t="inlineStr"/>
       <c r="O359" t="inlineStr"/>
@@ -19468,8 +19504,12 @@
       <c r="J360" t="n">
         <v>0.66</v>
       </c>
-      <c r="K360" t="inlineStr"/>
-      <c r="L360" t="inlineStr"/>
+      <c r="K360" t="n">
+        <v>3555</v>
+      </c>
+      <c r="L360" t="n">
+        <v>12.68</v>
+      </c>
       <c r="M360" t="inlineStr"/>
       <c r="N360" t="inlineStr"/>
       <c r="O360" t="inlineStr"/>
@@ -19518,8 +19558,12 @@
       <c r="J361" t="n">
         <v>0.4</v>
       </c>
-      <c r="K361" t="inlineStr"/>
-      <c r="L361" t="inlineStr"/>
+      <c r="K361" t="n">
+        <v>753</v>
+      </c>
+      <c r="L361" t="n">
+        <v>-5.87</v>
+      </c>
       <c r="M361" t="inlineStr"/>
       <c r="N361" t="inlineStr"/>
       <c r="O361" t="inlineStr"/>
@@ -19568,8 +19612,12 @@
       <c r="J362" t="n">
         <v>0.78</v>
       </c>
-      <c r="K362" t="inlineStr"/>
-      <c r="L362" t="inlineStr"/>
+      <c r="K362" t="n">
+        <v>2475</v>
+      </c>
+      <c r="L362" t="n">
+        <v>2.48</v>
+      </c>
       <c r="M362" t="inlineStr"/>
       <c r="N362" t="inlineStr"/>
       <c r="O362" t="inlineStr"/>
@@ -19618,8 +19666,12 @@
       <c r="J363" t="n">
         <v>0.73</v>
       </c>
-      <c r="K363" t="inlineStr"/>
-      <c r="L363" t="inlineStr"/>
+      <c r="K363" t="n">
+        <v>120</v>
+      </c>
+      <c r="L363" t="n">
+        <v>9.09</v>
+      </c>
       <c r="M363" t="inlineStr"/>
       <c r="N363" t="inlineStr"/>
       <c r="O363" t="inlineStr"/>
@@ -19668,8 +19720,12 @@
       <c r="J364" t="n">
         <v>0.64</v>
       </c>
-      <c r="K364" t="inlineStr"/>
-      <c r="L364" t="inlineStr"/>
+      <c r="K364" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="L364" t="n">
+        <v>4.25</v>
+      </c>
       <c r="M364" t="inlineStr"/>
       <c r="N364" t="inlineStr"/>
       <c r="O364" t="inlineStr"/>
@@ -19718,8 +19774,12 @@
       <c r="J365" t="n">
         <v>0.42</v>
       </c>
-      <c r="K365" t="inlineStr"/>
-      <c r="L365" t="inlineStr"/>
+      <c r="K365" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="L365" t="n">
+        <v>-10.54</v>
+      </c>
       <c r="M365" t="inlineStr"/>
       <c r="N365" t="inlineStr"/>
       <c r="O365" t="inlineStr"/>
@@ -19768,8 +19828,12 @@
       <c r="J366" t="n">
         <v>0.76</v>
       </c>
-      <c r="K366" t="inlineStr"/>
-      <c r="L366" t="inlineStr"/>
+      <c r="K366" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="L366" t="n">
+        <v>-3.21</v>
+      </c>
       <c r="M366" t="inlineStr"/>
       <c r="N366" t="inlineStr"/>
       <c r="O366" t="inlineStr"/>
@@ -19818,8 +19882,12 @@
       <c r="J367" t="n">
         <v>0.59</v>
       </c>
-      <c r="K367" t="inlineStr"/>
-      <c r="L367" t="inlineStr"/>
+      <c r="K367" t="n">
+        <v>180</v>
+      </c>
+      <c r="L367" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="M367" t="inlineStr"/>
       <c r="N367" t="inlineStr"/>
       <c r="O367" t="inlineStr"/>
@@ -19868,8 +19936,12 @@
       <c r="J368" t="n">
         <v>0.84</v>
       </c>
-      <c r="K368" t="inlineStr"/>
-      <c r="L368" t="inlineStr"/>
+      <c r="K368" t="n">
+        <v>42</v>
+      </c>
+      <c r="L368" t="n">
+        <v>-2.33</v>
+      </c>
       <c r="M368" t="inlineStr"/>
       <c r="N368" t="inlineStr"/>
       <c r="O368" t="inlineStr"/>
@@ -19918,8 +19990,12 @@
       <c r="J369" t="n">
         <v>0.67</v>
       </c>
-      <c r="K369" t="inlineStr"/>
-      <c r="L369" t="inlineStr"/>
+      <c r="K369" t="n">
+        <v>897</v>
+      </c>
+      <c r="L369" t="n">
+        <v>-7.91</v>
+      </c>
       <c r="M369" t="inlineStr"/>
       <c r="N369" t="inlineStr"/>
       <c r="O369" t="inlineStr"/>
@@ -19968,8 +20044,12 @@
       <c r="J370" t="n">
         <v>0.92</v>
       </c>
-      <c r="K370" t="inlineStr"/>
-      <c r="L370" t="inlineStr"/>
+      <c r="K370" t="n">
+        <v>538</v>
+      </c>
+      <c r="L370" t="n">
+        <v>11.85</v>
+      </c>
       <c r="M370" t="inlineStr"/>
       <c r="N370" t="inlineStr"/>
       <c r="O370" t="inlineStr"/>
@@ -20018,8 +20098,12 @@
       <c r="J371" t="n">
         <v>0.73</v>
       </c>
-      <c r="K371" t="inlineStr"/>
-      <c r="L371" t="inlineStr"/>
+      <c r="K371" t="n">
+        <v>167</v>
+      </c>
+      <c r="L371" t="n">
+        <v>10.23</v>
+      </c>
       <c r="M371" t="inlineStr"/>
       <c r="N371" t="inlineStr"/>
       <c r="O371" t="inlineStr"/>
@@ -20068,8 +20152,12 @@
       <c r="J372" t="n">
         <v>0.2</v>
       </c>
-      <c r="K372" t="inlineStr"/>
-      <c r="L372" t="inlineStr"/>
+      <c r="K372" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="L372" t="n">
+        <v>-2.4</v>
+      </c>
       <c r="M372" t="inlineStr"/>
       <c r="N372" t="inlineStr"/>
       <c r="O372" t="inlineStr"/>
@@ -20118,8 +20206,12 @@
       <c r="J373" t="n">
         <v>0.82</v>
       </c>
-      <c r="K373" t="inlineStr"/>
-      <c r="L373" t="inlineStr"/>
+      <c r="K373" t="n">
+        <v>1895</v>
+      </c>
+      <c r="L373" t="n">
+        <v>-7.79</v>
+      </c>
       <c r="M373" t="inlineStr"/>
       <c r="N373" t="inlineStr"/>
       <c r="O373" t="inlineStr"/>
@@ -20168,8 +20260,12 @@
       <c r="J374" t="n">
         <v>0.75</v>
       </c>
-      <c r="K374" t="inlineStr"/>
-      <c r="L374" t="inlineStr"/>
+      <c r="K374" t="n">
+        <v>1710</v>
+      </c>
+      <c r="L374" t="n">
+        <v>60.56</v>
+      </c>
       <c r="M374" t="inlineStr"/>
       <c r="N374" t="inlineStr"/>
       <c r="O374" t="inlineStr"/>
@@ -20218,8 +20314,12 @@
       <c r="J375" t="n">
         <v>0.36</v>
       </c>
-      <c r="K375" t="inlineStr"/>
-      <c r="L375" t="inlineStr"/>
+      <c r="K375" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="L375" t="n">
+        <v>-0.66</v>
+      </c>
       <c r="M375" t="inlineStr"/>
       <c r="N375" t="inlineStr"/>
       <c r="O375" t="inlineStr"/>
@@ -20268,8 +20368,12 @@
       <c r="J376" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="K376" t="inlineStr"/>
-      <c r="L376" t="inlineStr"/>
+      <c r="K376" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="L376" t="n">
+        <v>-7.72</v>
+      </c>
       <c r="M376" t="inlineStr"/>
       <c r="N376" t="inlineStr"/>
       <c r="O376" t="inlineStr"/>
@@ -20318,8 +20422,12 @@
       <c r="J377" t="n">
         <v>0.71</v>
       </c>
-      <c r="K377" t="inlineStr"/>
-      <c r="L377" t="inlineStr"/>
+      <c r="K377" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="L377" t="n">
+        <v>-0.37</v>
+      </c>
       <c r="M377" t="inlineStr"/>
       <c r="N377" t="inlineStr"/>
       <c r="O377" t="inlineStr"/>
@@ -20368,8 +20476,12 @@
       <c r="J378" t="n">
         <v>0.49</v>
       </c>
-      <c r="K378" t="inlineStr"/>
-      <c r="L378" t="inlineStr"/>
+      <c r="K378" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="L378" t="n">
+        <v>1.8</v>
+      </c>
       <c r="M378" t="inlineStr"/>
       <c r="N378" t="inlineStr"/>
       <c r="O378" t="inlineStr"/>
@@ -20418,8 +20530,12 @@
       <c r="J379" t="n">
         <v>0.31</v>
       </c>
-      <c r="K379" t="inlineStr"/>
-      <c r="L379" t="inlineStr"/>
+      <c r="K379" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="L379" t="n">
+        <v>1.37</v>
+      </c>
       <c r="M379" t="inlineStr"/>
       <c r="N379" t="inlineStr"/>
       <c r="O379" t="inlineStr"/>
@@ -20468,8 +20584,12 @@
       <c r="J380" t="n">
         <v>0.36</v>
       </c>
-      <c r="K380" t="inlineStr"/>
-      <c r="L380" t="inlineStr"/>
+      <c r="K380" t="n">
+        <v>1480</v>
+      </c>
+      <c r="L380" t="n">
+        <v>1.72</v>
+      </c>
       <c r="M380" t="inlineStr"/>
       <c r="N380" t="inlineStr"/>
       <c r="O380" t="inlineStr"/>
@@ -20514,8 +20634,12 @@
       </c>
       <c r="I381" t="inlineStr"/>
       <c r="J381" t="inlineStr"/>
-      <c r="K381" t="inlineStr"/>
-      <c r="L381" t="inlineStr"/>
+      <c r="K381" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="L381" t="n">
+        <v>-2.23</v>
+      </c>
       <c r="M381" t="inlineStr"/>
       <c r="N381" t="inlineStr"/>
       <c r="O381" t="inlineStr"/>
@@ -20560,8 +20684,12 @@
       </c>
       <c r="I382" t="inlineStr"/>
       <c r="J382" t="inlineStr"/>
-      <c r="K382" t="inlineStr"/>
-      <c r="L382" t="inlineStr"/>
+      <c r="K382" t="n">
+        <v>378</v>
+      </c>
+      <c r="L382" t="n">
+        <v>-9.68</v>
+      </c>
       <c r="M382" t="inlineStr"/>
       <c r="N382" t="inlineStr"/>
       <c r="O382" t="inlineStr"/>
@@ -20606,8 +20734,12 @@
       </c>
       <c r="I383" t="inlineStr"/>
       <c r="J383" t="inlineStr"/>
-      <c r="K383" t="inlineStr"/>
-      <c r="L383" t="inlineStr"/>
+      <c r="K383" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="L383" t="n">
+        <v>-2.49</v>
+      </c>
       <c r="M383" t="inlineStr"/>
       <c r="N383" t="inlineStr"/>
       <c r="O383" t="inlineStr"/>
@@ -20652,8 +20784,12 @@
       </c>
       <c r="I384" t="inlineStr"/>
       <c r="J384" t="inlineStr"/>
-      <c r="K384" t="inlineStr"/>
-      <c r="L384" t="inlineStr"/>
+      <c r="K384" t="n">
+        <v>200</v>
+      </c>
+      <c r="L384" t="n">
+        <v>-13.42</v>
+      </c>
       <c r="M384" t="inlineStr"/>
       <c r="N384" t="inlineStr"/>
       <c r="O384" t="inlineStr"/>
@@ -26302,7 +26438,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46218</v>
+        <v>46260</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -26311,16 +26447,16 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2165</v>
+        <v>1065</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -26333,19 +26469,19 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I2" t="n">
-        <v>24.6</v>
+        <v>21.8</v>
       </c>
       <c r="J2" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="K2" t="n">
-        <v>3235</v>
+        <v>1710</v>
       </c>
       <c r="L2" t="n">
-        <v>49.42</v>
+        <v>60.56</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -26354,12 +26490,12 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>49.42</v>
+        <v>60.56</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46234</v>
+        <v>46218</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -26377,7 +26513,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2320</v>
+        <v>2165</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -26399,10 +26535,10 @@
         <v>0.66</v>
       </c>
       <c r="K3" t="n">
-        <v>3425</v>
+        <v>3235</v>
       </c>
       <c r="L3" t="n">
-        <v>47.63</v>
+        <v>49.42</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -26411,7 +26547,7 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>47.63</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="4">
@@ -26425,41 +26561,41 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>821</v>
+        <v>2320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="I4" t="n">
-        <v>38.8</v>
+        <v>24.6</v>
       </c>
       <c r="J4" t="n">
-        <v>1.03</v>
+        <v>0.66</v>
       </c>
       <c r="K4" t="n">
-        <v>1180</v>
+        <v>3425</v>
       </c>
       <c r="L4" t="n">
-        <v>43.73</v>
+        <v>47.63</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -26468,7 +26604,7 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>43.73</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="5">
@@ -26482,41 +26618,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>902</v>
+        <v>821</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I5" t="n">
-        <v>21.8</v>
+        <v>38.8</v>
       </c>
       <c r="J5" t="n">
-        <v>0.75</v>
+        <v>1.03</v>
       </c>
       <c r="K5" t="n">
-        <v>1250</v>
+        <v>1180</v>
       </c>
       <c r="L5" t="n">
-        <v>38.58</v>
+        <v>43.73</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -26525,12 +26661,12 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>38.58</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46252</v>
+        <v>46234</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -26548,7 +26684,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1005</v>
+        <v>902</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -26570,10 +26706,10 @@
         <v>0.75</v>
       </c>
       <c r="K6" t="n">
-        <v>1385</v>
+        <v>1250</v>
       </c>
       <c r="L6" t="n">
-        <v>37.81</v>
+        <v>38.58</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -26582,12 +26718,12 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>37.81</v>
+        <v>38.58</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -26605,7 +26741,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -26630,7 +26766,7 @@
         <v>1385</v>
       </c>
       <c r="L7" t="n">
-        <v>37.13</v>
+        <v>37.81</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -26639,12 +26775,12 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>37.13</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -26653,16 +26789,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>131</v>
+        <v>1010</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -26675,19 +26811,19 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I8" t="n">
-        <v>14.1</v>
+        <v>21.8</v>
       </c>
       <c r="J8" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="K8" t="n">
-        <v>179.5</v>
+        <v>1385</v>
       </c>
       <c r="L8" t="n">
-        <v>37.02</v>
+        <v>37.13</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -26696,7 +26832,7 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>37.02</v>
+        <v>37.13</v>
       </c>
     </row>
     <row r="9">
@@ -26710,16 +26846,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>369</v>
+        <v>131</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -26735,16 +26871,16 @@
         <v>90</v>
       </c>
       <c r="I9" t="n">
-        <v>21.2</v>
+        <v>14.1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="K9" t="n">
-        <v>496.5</v>
+        <v>179.5</v>
       </c>
       <c r="L9" t="n">
-        <v>34.55</v>
+        <v>37.02</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -26753,12 +26889,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>34.55</v>
+        <v>37.02</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46210</v>
+        <v>46234</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -26767,37 +26903,41 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>185.5</v>
+        <v>369</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>69</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="I10" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.92</v>
+      </c>
       <c r="K10" t="n">
-        <v>247</v>
+        <v>496.5</v>
       </c>
       <c r="L10" t="n">
-        <v>33.15</v>
+        <v>34.55</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -26806,12 +26946,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>33.15</v>
+        <v>34.55</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -26820,41 +26960,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>145.5</v>
+        <v>185.5</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>62</v>
-      </c>
-      <c r="I11" t="n">
-        <v>10</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.31</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>193.5</v>
+        <v>247</v>
       </c>
       <c r="L11" t="n">
-        <v>32.99</v>
+        <v>33.15</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -26863,12 +26999,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>32.99</v>
+        <v>33.15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -26877,16 +27013,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5115</v>
+        <v>145.5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -26895,23 +27031,23 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I12" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="J12" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="K12" t="n">
-        <v>6620</v>
+        <v>193.5</v>
       </c>
       <c r="L12" t="n">
-        <v>29.42</v>
+        <v>32.99</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -26920,12 +27056,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>29.42</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -26934,20 +27070,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>181.5</v>
+        <v>5115</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -26956,15 +27092,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>69</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="I13" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.26</v>
+      </c>
       <c r="K13" t="n">
-        <v>233</v>
+        <v>6620</v>
       </c>
       <c r="L13" t="n">
-        <v>28.37</v>
+        <v>29.42</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -26973,12 +27113,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>28.37</v>
+        <v>29.42</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46244</v>
+        <v>46218</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -26987,41 +27127,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>401.5</v>
+        <v>181.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
-      </c>
-      <c r="I14" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.92</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>509</v>
+        <v>233</v>
       </c>
       <c r="L14" t="n">
-        <v>26.77</v>
+        <v>28.37</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -27030,12 +27166,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>26.77</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46211</v>
+        <v>46244</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -27044,16 +27180,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5050</v>
+        <v>401.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -27062,23 +27198,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="I15" t="n">
-        <v>9.6</v>
+        <v>21.2</v>
       </c>
       <c r="J15" t="n">
-        <v>0.26</v>
+        <v>0.92</v>
       </c>
       <c r="K15" t="n">
-        <v>6265</v>
+        <v>509</v>
       </c>
       <c r="L15" t="n">
-        <v>24.06</v>
+        <v>26.77</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -27087,12 +27223,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>24.06</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46244</v>
+        <v>46211</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -27101,16 +27237,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2765</v>
+        <v>5050</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -27119,23 +27255,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I16" t="n">
-        <v>24.6</v>
+        <v>9.6</v>
       </c>
       <c r="J16" t="n">
-        <v>0.66</v>
+        <v>0.26</v>
       </c>
       <c r="K16" t="n">
-        <v>3380</v>
+        <v>6265</v>
       </c>
       <c r="L16" t="n">
-        <v>22.24</v>
+        <v>24.06</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -27144,12 +27280,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>22.24</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46210</v>
+        <v>46244</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -27158,16 +27294,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>155.5</v>
+        <v>2765</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -27176,23 +27312,23 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>62</v>
+        <v>100</v>
       </c>
       <c r="I17" t="n">
-        <v>10</v>
+        <v>24.6</v>
       </c>
       <c r="J17" t="n">
-        <v>0.31</v>
+        <v>0.66</v>
       </c>
       <c r="K17" t="n">
-        <v>189.5</v>
+        <v>3380</v>
       </c>
       <c r="L17" t="n">
-        <v>21.86</v>
+        <v>22.24</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -27201,7 +27337,7 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>21.86</v>
+        <v>22.24</v>
       </c>
     </row>
     <row r="18">
@@ -27215,16 +27351,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2450</v>
+        <v>155.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -27233,23 +27369,23 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>62</v>
       </c>
       <c r="I18" t="n">
-        <v>24.6</v>
+        <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>0.66</v>
+        <v>0.31</v>
       </c>
       <c r="K18" t="n">
-        <v>2940</v>
+        <v>189.5</v>
       </c>
       <c r="L18" t="n">
-        <v>20</v>
+        <v>21.86</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -27258,12 +27394,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>20</v>
+        <v>21.86</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46226</v>
+        <v>46210</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -27281,7 +27417,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2440</v>
+        <v>2450</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -27303,10 +27439,10 @@
         <v>0.66</v>
       </c>
       <c r="K19" t="n">
-        <v>2855</v>
+        <v>2940</v>
       </c>
       <c r="L19" t="n">
-        <v>17.01</v>
+        <v>20</v>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
@@ -27315,12 +27451,12 @@
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>17.01</v>
+        <v>20</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46234</v>
+        <v>46226</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -27329,16 +27465,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>291.5</v>
+        <v>2440</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -27347,23 +27483,23 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>13.2</v>
+        <v>24.6</v>
       </c>
       <c r="J20" t="n">
-        <v>0.49</v>
+        <v>0.66</v>
       </c>
       <c r="K20" t="n">
-        <v>338.5</v>
+        <v>2855</v>
       </c>
       <c r="L20" t="n">
-        <v>16.12</v>
+        <v>17.01</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -27372,12 +27508,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>16.12</v>
+        <v>17.01</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46202</v>
+        <v>46234</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -27386,20 +27522,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>193.5</v>
+        <v>291.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -27408,15 +27544,19 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>69</v>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="I21" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0.49</v>
+      </c>
       <c r="K21" t="n">
-        <v>222.5</v>
+        <v>338.5</v>
       </c>
       <c r="L21" t="n">
-        <v>14.99</v>
+        <v>16.12</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -27425,7 +27565,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>14.99</v>
+        <v>16.12</v>
       </c>
     </row>
   </sheetData>
@@ -28445,7 +28585,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46210</v>
+        <v>46226</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -28454,38 +28594,38 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34.15</v>
+        <v>1190</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="I18" t="n">
-        <v>5.9</v>
+        <v>38.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.42</v>
+        <v>1.03</v>
       </c>
       <c r="K18" t="n">
-        <v>27.75</v>
+        <v>967</v>
       </c>
       <c r="L18" t="n">
         <v>-18.74</v>
@@ -28502,7 +28642,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46226</v>
+        <v>46210</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -28511,38 +28651,38 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1190</v>
+        <v>34.15</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="I19" t="n">
-        <v>38.8</v>
+        <v>5.9</v>
       </c>
       <c r="J19" t="n">
-        <v>1.03</v>
+        <v>0.42</v>
       </c>
       <c r="K19" t="n">
-        <v>967</v>
+        <v>27.75</v>
       </c>
       <c r="L19" t="n">
         <v>-18.74</v>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="C2" t="n">
         <v>43.2</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.64</v>
+        <v>-0.87</v>
       </c>
       <c r="E2" t="n">
         <v>-1.25</v>
@@ -483,7 +483,7 @@
         <v>60.56</v>
       </c>
       <c r="G2" t="n">
-        <v>-66.01000000000001</v>
+        <v>-68.97</v>
       </c>
     </row>
     <row r="3">
@@ -493,13 +493,23 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+        <v>35</v>
+      </c>
+      <c r="C3" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="D3" t="n">
+        <v>-1.56</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-4.33</v>
+      </c>
+      <c r="F3" t="n">
+        <v>71.86</v>
+      </c>
+      <c r="G3" t="n">
+        <v>-54.37</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -542,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -584,13 +594,34 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D2" t="n">
         <v>43.2</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.64</v>
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>3m</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>35</v>
+      </c>
+      <c r="D3" t="n">
+        <v>37.1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>-1.56</v>
       </c>
     </row>
   </sheetData>
@@ -604,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R496"/>
+  <dimension ref="A1:R497"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -746,8 +777,12 @@
       <c r="L2" t="n">
         <v>-5.61</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="n">
+        <v>157</v>
+      </c>
+      <c r="N2" t="n">
+        <v>3.63</v>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
@@ -800,8 +835,12 @@
       <c r="L3" t="n">
         <v>-8.81</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="M3" t="n">
+        <v>542</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0.5600000000000001</v>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
@@ -854,8 +893,12 @@
       <c r="L4" t="n">
         <v>0.84</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="M4" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-0.84</v>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
@@ -908,8 +951,12 @@
       <c r="L5" t="n">
         <v>-19.45</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="M5" t="n">
+        <v>320</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-7.11</v>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
@@ -962,8 +1009,12 @@
       <c r="L6" t="n">
         <v>-7.89</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="M6" t="n">
+        <v>82.3</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-9.76</v>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
@@ -1016,8 +1067,12 @@
       <c r="L7" t="n">
         <v>-19.23</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="M7" t="n">
+        <v>129.5</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-9.44</v>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
@@ -1070,8 +1125,12 @@
       <c r="L8" t="n">
         <v>-3.85</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="M8" t="n">
+        <v>250.5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.62</v>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
@@ -1124,8 +1183,12 @@
       <c r="L9" t="n">
         <v>-14.96</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="M9" t="n">
+        <v>1110</v>
+      </c>
+      <c r="N9" t="n">
+        <v>11.45</v>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
@@ -1178,8 +1241,12 @@
       <c r="L10" t="n">
         <v>-6.22</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+      <c r="M10" t="n">
+        <v>59.9</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-6.84</v>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
@@ -1232,8 +1299,12 @@
       <c r="L11" t="n">
         <v>-8.91</v>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+      <c r="M11" t="n">
+        <v>3555</v>
+      </c>
+      <c r="N11" t="n">
+        <v>54.57</v>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
@@ -1286,8 +1357,12 @@
       <c r="L12" t="n">
         <v>-29.74</v>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>753</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-21.15</v>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
@@ -1340,8 +1415,12 @@
       <c r="L13" t="n">
         <v>-7.17</v>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+      <c r="M13" t="n">
+        <v>2475</v>
+      </c>
+      <c r="N13" t="n">
+        <v>4.43</v>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
@@ -1394,8 +1473,12 @@
       <c r="L14" t="n">
         <v>1.95</v>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="n">
+        <v>120</v>
+      </c>
+      <c r="N14" t="n">
+        <v>23.2</v>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
@@ -1448,8 +1531,12 @@
       <c r="L15" t="n">
         <v>-13.28</v>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+      <c r="M15" t="n">
+        <v>110.5</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-3.49</v>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
@@ -1502,8 +1589,12 @@
       <c r="L16" t="n">
         <v>-19.15</v>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-26.75</v>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
@@ -1556,8 +1647,12 @@
       <c r="L17" t="n">
         <v>-7.79</v>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+      <c r="M17" t="n">
+        <v>105.5</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-8.66</v>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
@@ -1610,8 +1705,12 @@
       <c r="L18" t="n">
         <v>-6.88</v>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+      <c r="M18" t="n">
+        <v>180</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-4.76</v>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
@@ -1664,8 +1763,12 @@
       <c r="L19" t="n">
         <v>-5.58</v>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+      <c r="M19" t="n">
+        <v>42</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-4.33</v>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
@@ -1718,8 +1821,12 @@
       <c r="L20" t="n">
         <v>-19.26</v>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+      <c r="M20" t="n">
+        <v>897</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-26.17</v>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
@@ -1772,8 +1879,12 @@
       <c r="L21" t="n">
         <v>-32.03</v>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+      <c r="M21" t="n">
+        <v>538</v>
+      </c>
+      <c r="N21" t="n">
+        <v>7.71</v>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
@@ -1826,8 +1937,12 @@
       <c r="L22" t="n">
         <v>-9.779999999999999</v>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
+      <c r="M22" t="n">
+        <v>167</v>
+      </c>
+      <c r="N22" t="n">
+        <v>21.01</v>
+      </c>
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr"/>
       <c r="Q22" t="inlineStr"/>
@@ -1880,8 +1995,12 @@
       <c r="L23" t="n">
         <v>-9.49</v>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
+      <c r="M23" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-4.69</v>
+      </c>
       <c r="O23" t="inlineStr"/>
       <c r="P23" t="inlineStr"/>
       <c r="Q23" t="inlineStr"/>
@@ -1934,8 +2053,12 @@
       <c r="L24" t="n">
         <v>-18.38</v>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
+      <c r="M24" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-19.02</v>
+      </c>
       <c r="O24" t="inlineStr"/>
       <c r="P24" t="inlineStr"/>
       <c r="Q24" t="inlineStr"/>
@@ -1988,8 +2111,12 @@
       <c r="L25" t="n">
         <v>-14.07</v>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
+      <c r="M25" t="n">
+        <v>1710</v>
+      </c>
+      <c r="N25" t="n">
+        <v>71.86</v>
+      </c>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr"/>
       <c r="Q25" t="inlineStr"/>
@@ -2042,8 +2169,12 @@
       <c r="L26" t="n">
         <v>-7.2</v>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
+      <c r="M26" t="n">
+        <v>89.8</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-3.44</v>
+      </c>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr"/>
       <c r="Q26" t="inlineStr"/>
@@ -2096,8 +2227,12 @@
       <c r="L27" t="n">
         <v>-1.39</v>
       </c>
-      <c r="M27" t="inlineStr"/>
-      <c r="N27" t="inlineStr"/>
+      <c r="M27" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="N27" t="n">
+        <v>-21.62</v>
+      </c>
       <c r="O27" t="inlineStr"/>
       <c r="P27" t="inlineStr"/>
       <c r="Q27" t="inlineStr"/>
@@ -2150,8 +2285,12 @@
       <c r="L28" t="n">
         <v>-21.07</v>
       </c>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
+      <c r="M28" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-18.63</v>
+      </c>
       <c r="O28" t="inlineStr"/>
       <c r="P28" t="inlineStr"/>
       <c r="Q28" t="inlineStr"/>
@@ -2204,8 +2343,12 @@
       <c r="L29" t="n">
         <v>-15.67</v>
       </c>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
+      <c r="M29" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="N29" t="n">
+        <v>-7.77</v>
+      </c>
       <c r="O29" t="inlineStr"/>
       <c r="P29" t="inlineStr"/>
       <c r="Q29" t="inlineStr"/>
@@ -2258,8 +2401,12 @@
       <c r="L30" t="n">
         <v>9.710000000000001</v>
       </c>
-      <c r="M30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
+      <c r="M30" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="N30" t="n">
+        <v>19.42</v>
+      </c>
       <c r="O30" t="inlineStr"/>
       <c r="P30" t="inlineStr"/>
       <c r="Q30" t="inlineStr"/>
@@ -2312,8 +2459,12 @@
       <c r="L31" t="n">
         <v>-1.69</v>
       </c>
-      <c r="M31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
+      <c r="M31" t="n">
+        <v>1480</v>
+      </c>
+      <c r="N31" t="n">
+        <v>0.34</v>
+      </c>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr"/>
       <c r="Q31" t="inlineStr"/>
@@ -2362,8 +2513,12 @@
       <c r="L32" t="n">
         <v>-5.75</v>
       </c>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="M32" t="n">
+        <v>70.09999999999999</v>
+      </c>
+      <c r="N32" t="n">
+        <v>-10.47</v>
+      </c>
       <c r="O32" t="inlineStr"/>
       <c r="P32" t="inlineStr"/>
       <c r="Q32" t="inlineStr"/>
@@ -2412,8 +2567,12 @@
       <c r="L33" t="n">
         <v>-2.48</v>
       </c>
-      <c r="M33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="M33" t="n">
+        <v>378</v>
+      </c>
+      <c r="N33" t="n">
+        <v>-6.44</v>
+      </c>
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr"/>
       <c r="Q33" t="inlineStr"/>
@@ -2462,8 +2621,12 @@
       <c r="L34" t="n">
         <v>-5.85</v>
       </c>
-      <c r="M34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
+      <c r="M34" t="n">
+        <v>23.5</v>
+      </c>
+      <c r="N34" t="n">
+        <v>-1.88</v>
+      </c>
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr"/>
       <c r="Q34" t="inlineStr"/>
@@ -2512,8 +2675,12 @@
       <c r="L35" t="n">
         <v>14.99</v>
       </c>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
+      <c r="M35" t="n">
+        <v>200</v>
+      </c>
+      <c r="N35" t="n">
+        <v>3.36</v>
+      </c>
       <c r="O35" t="inlineStr"/>
       <c r="P35" t="inlineStr"/>
       <c r="Q35" t="inlineStr"/>
@@ -6086,8 +6253,12 @@
       <c r="L107" t="n">
         <v>5.72</v>
       </c>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
+      <c r="M107" t="n">
+        <v>2115</v>
+      </c>
+      <c r="N107" t="n">
+        <v>-54.37</v>
+      </c>
       <c r="O107" t="inlineStr"/>
       <c r="P107" t="inlineStr"/>
       <c r="Q107" t="inlineStr"/>
@@ -20838,8 +21009,12 @@
       <c r="J385" t="n">
         <v>0.26</v>
       </c>
-      <c r="K385" t="inlineStr"/>
-      <c r="L385" t="inlineStr"/>
+      <c r="K385" t="n">
+        <v>2115</v>
+      </c>
+      <c r="L385" t="n">
+        <v>-68.97</v>
+      </c>
       <c r="M385" t="inlineStr"/>
       <c r="N385" t="inlineStr"/>
       <c r="O385" t="inlineStr"/>
@@ -20884,8 +21059,12 @@
       </c>
       <c r="I386" t="inlineStr"/>
       <c r="J386" t="inlineStr"/>
-      <c r="K386" t="inlineStr"/>
-      <c r="L386" t="inlineStr"/>
+      <c r="K386" t="n">
+        <v>49.2</v>
+      </c>
+      <c r="L386" t="n">
+        <v>2.18</v>
+      </c>
       <c r="M386" t="inlineStr"/>
       <c r="N386" t="inlineStr"/>
       <c r="O386" t="inlineStr"/>
@@ -26324,6 +26503,52 @@
       <c r="P496" t="inlineStr"/>
       <c r="Q496" t="inlineStr"/>
       <c r="R496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>信立</t>
+        </is>
+      </c>
+      <c r="E497" t="n">
+        <v>34.05</v>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G497" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H497" t="n">
+        <v>75</v>
+      </c>
+      <c r="I497" t="inlineStr"/>
+      <c r="J497" t="inlineStr"/>
+      <c r="K497" t="inlineStr"/>
+      <c r="L497" t="inlineStr"/>
+      <c r="M497" t="inlineStr"/>
+      <c r="N497" t="inlineStr"/>
+      <c r="O497" t="inlineStr"/>
+      <c r="P497" t="inlineStr"/>
+      <c r="Q497" t="inlineStr"/>
+      <c r="R497" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26438,7 +26663,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46260</v>
+        <v>46202</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -26456,7 +26681,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1065</v>
+        <v>995</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -26478,24 +26703,28 @@
         <v>0.75</v>
       </c>
       <c r="K2" t="n">
+        <v>855</v>
+      </c>
+      <c r="L2" t="n">
+        <v>-14.07</v>
+      </c>
+      <c r="M2" t="n">
         <v>1710</v>
       </c>
-      <c r="L2" t="n">
-        <v>60.56</v>
-      </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="N2" t="n">
+        <v>71.86</v>
+      </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>60.56</v>
+        <v>71.86</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46218</v>
+        <v>46260</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -26504,16 +26733,16 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2165</v>
+        <v>1065</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -26526,19 +26755,19 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I3" t="n">
-        <v>24.6</v>
+        <v>21.8</v>
       </c>
       <c r="J3" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="K3" t="n">
-        <v>3235</v>
+        <v>1710</v>
       </c>
       <c r="L3" t="n">
-        <v>49.42</v>
+        <v>60.56</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -26547,12 +26776,12 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>49.42</v>
+        <v>60.56</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46234</v>
+        <v>46202</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -26570,7 +26799,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2320</v>
+        <v>2300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -26592,24 +26821,28 @@
         <v>0.66</v>
       </c>
       <c r="K4" t="n">
-        <v>3425</v>
+        <v>2095</v>
       </c>
       <c r="L4" t="n">
-        <v>47.63</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+        <v>-8.91</v>
+      </c>
+      <c r="M4" t="n">
+        <v>3555</v>
+      </c>
+      <c r="N4" t="n">
+        <v>54.57</v>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>47.63</v>
+        <v>54.57</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46234</v>
+        <v>46218</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -26618,41 +26851,41 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>821</v>
+        <v>2165</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="I5" t="n">
-        <v>38.8</v>
+        <v>24.6</v>
       </c>
       <c r="J5" t="n">
-        <v>1.03</v>
+        <v>0.66</v>
       </c>
       <c r="K5" t="n">
-        <v>1180</v>
+        <v>3235</v>
       </c>
       <c r="L5" t="n">
-        <v>43.73</v>
+        <v>49.42</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -26661,7 +26894,7 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>43.73</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="6">
@@ -26675,16 +26908,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>902</v>
+        <v>2320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -26697,19 +26930,19 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I6" t="n">
-        <v>21.8</v>
+        <v>24.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="K6" t="n">
-        <v>1250</v>
+        <v>3425</v>
       </c>
       <c r="L6" t="n">
-        <v>38.58</v>
+        <v>47.63</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -26718,12 +26951,12 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>38.58</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46252</v>
+        <v>46234</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -26732,41 +26965,41 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1005</v>
+        <v>821</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I7" t="n">
-        <v>21.8</v>
+        <v>38.8</v>
       </c>
       <c r="J7" t="n">
-        <v>0.75</v>
+        <v>1.03</v>
       </c>
       <c r="K7" t="n">
-        <v>1385</v>
+        <v>1180</v>
       </c>
       <c r="L7" t="n">
-        <v>37.81</v>
+        <v>43.73</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -26775,12 +27008,12 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>37.81</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46244</v>
+        <v>46234</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -26798,7 +27031,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1010</v>
+        <v>902</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -26820,10 +27053,10 @@
         <v>0.75</v>
       </c>
       <c r="K8" t="n">
-        <v>1385</v>
+        <v>1250</v>
       </c>
       <c r="L8" t="n">
-        <v>37.13</v>
+        <v>38.58</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -26832,12 +27065,12 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>37.13</v>
+        <v>38.58</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46234</v>
+        <v>46252</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -26846,16 +27079,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>131</v>
+        <v>1005</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -26868,19 +27101,19 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I9" t="n">
-        <v>14.1</v>
+        <v>21.8</v>
       </c>
       <c r="J9" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="K9" t="n">
-        <v>179.5</v>
+        <v>1385</v>
       </c>
       <c r="L9" t="n">
-        <v>37.02</v>
+        <v>37.81</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -26889,12 +27122,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>37.02</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -26903,16 +27136,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>369</v>
+        <v>1010</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -26925,19 +27158,19 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I10" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="K10" t="n">
-        <v>496.5</v>
+        <v>1385</v>
       </c>
       <c r="L10" t="n">
-        <v>34.55</v>
+        <v>37.13</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -26946,12 +27179,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>34.55</v>
+        <v>37.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46210</v>
+        <v>46234</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -26960,37 +27193,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>185.5</v>
+        <v>131</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>69</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="I11" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.73</v>
+      </c>
       <c r="K11" t="n">
-        <v>247</v>
+        <v>179.5</v>
       </c>
       <c r="L11" t="n">
-        <v>33.15</v>
+        <v>37.02</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -26999,12 +27236,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>33.15</v>
+        <v>37.02</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46218</v>
+        <v>46234</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -27013,16 +27250,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>145.5</v>
+        <v>369</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -27031,23 +27268,23 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
-        <v>10</v>
+        <v>21.2</v>
       </c>
       <c r="J12" t="n">
-        <v>0.31</v>
+        <v>0.92</v>
       </c>
       <c r="K12" t="n">
-        <v>193.5</v>
+        <v>496.5</v>
       </c>
       <c r="L12" t="n">
-        <v>32.99</v>
+        <v>34.55</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -27056,12 +27293,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>32.99</v>
+        <v>34.55</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46219</v>
+        <v>46210</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -27070,20 +27307,20 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5115</v>
+        <v>185.5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -27092,19 +27329,15 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>65</v>
-      </c>
-      <c r="I13" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.26</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>6620</v>
+        <v>247</v>
       </c>
       <c r="L13" t="n">
-        <v>29.42</v>
+        <v>33.15</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -27113,7 +27346,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>29.42</v>
+        <v>33.15</v>
       </c>
     </row>
     <row r="14">
@@ -27127,37 +27360,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>181.5</v>
+        <v>145.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>69</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+        <v>62</v>
+      </c>
+      <c r="I14" t="n">
+        <v>10</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.31</v>
+      </c>
       <c r="K14" t="n">
-        <v>233</v>
+        <v>193.5</v>
       </c>
       <c r="L14" t="n">
-        <v>28.37</v>
+        <v>32.99</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -27166,12 +27403,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>28.37</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46244</v>
+        <v>46219</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -27180,16 +27417,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>401.5</v>
+        <v>5115</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -27198,23 +27435,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="I15" t="n">
-        <v>21.2</v>
+        <v>9.6</v>
       </c>
       <c r="J15" t="n">
-        <v>0.92</v>
+        <v>0.26</v>
       </c>
       <c r="K15" t="n">
-        <v>509</v>
+        <v>6620</v>
       </c>
       <c r="L15" t="n">
-        <v>26.77</v>
+        <v>29.42</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -27223,12 +27460,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>26.77</v>
+        <v>29.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46211</v>
+        <v>46218</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -27237,20 +27474,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5050</v>
+        <v>181.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -27259,19 +27496,15 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>65</v>
-      </c>
-      <c r="I16" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J16" t="n">
-        <v>0.26</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>6265</v>
+        <v>233</v>
       </c>
       <c r="L16" t="n">
-        <v>24.06</v>
+        <v>28.37</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -27280,7 +27513,7 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>24.06</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="17">
@@ -27294,16 +27527,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2765</v>
+        <v>401.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -27316,19 +27549,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I17" t="n">
-        <v>24.6</v>
+        <v>21.2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.66</v>
+        <v>0.92</v>
       </c>
       <c r="K17" t="n">
-        <v>3380</v>
+        <v>509</v>
       </c>
       <c r="L17" t="n">
-        <v>22.24</v>
+        <v>26.77</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -27337,12 +27570,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>22.24</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -27351,16 +27584,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>155.5</v>
+        <v>5050</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -27369,23 +27602,23 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I18" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="J18" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="K18" t="n">
-        <v>189.5</v>
+        <v>6265</v>
       </c>
       <c r="L18" t="n">
-        <v>21.86</v>
+        <v>24.06</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -27394,12 +27627,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>21.86</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -27408,16 +27641,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2450</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -27430,33 +27663,37 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I19" t="n">
-        <v>24.6</v>
+        <v>12.4</v>
       </c>
       <c r="J19" t="n">
-        <v>0.66</v>
+        <v>0.73</v>
       </c>
       <c r="K19" t="n">
-        <v>2940</v>
+        <v>99.3</v>
       </c>
       <c r="L19" t="n">
-        <v>20</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+        <v>1.95</v>
+      </c>
+      <c r="M19" t="n">
+        <v>120</v>
+      </c>
+      <c r="N19" t="n">
+        <v>23.2</v>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46226</v>
+        <v>46244</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -27474,7 +27711,7 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2440</v>
+        <v>2765</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -27496,10 +27733,10 @@
         <v>0.66</v>
       </c>
       <c r="K20" t="n">
-        <v>2855</v>
+        <v>3380</v>
       </c>
       <c r="L20" t="n">
-        <v>17.01</v>
+        <v>22.24</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -27508,12 +27745,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>17.01</v>
+        <v>22.24</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46234</v>
+        <v>46210</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -27522,16 +27759,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>291.5</v>
+        <v>155.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -27540,23 +27777,23 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I21" t="n">
-        <v>13.2</v>
+        <v>10</v>
       </c>
       <c r="J21" t="n">
-        <v>0.49</v>
+        <v>0.31</v>
       </c>
       <c r="K21" t="n">
-        <v>338.5</v>
+        <v>189.5</v>
       </c>
       <c r="L21" t="n">
-        <v>16.12</v>
+        <v>21.86</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -27565,7 +27802,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>16.12</v>
+        <v>21.86</v>
       </c>
     </row>
   </sheetData>
@@ -27681,7 +27918,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46254</v>
+        <v>46262</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -27699,7 +27936,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6325</v>
+        <v>6815</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -27721,10 +27958,10 @@
         <v>0.26</v>
       </c>
       <c r="K2" t="n">
-        <v>2150</v>
+        <v>2115</v>
       </c>
       <c r="L2" t="n">
-        <v>-66.01000000000001</v>
+        <v>-68.97</v>
       </c>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
@@ -27733,12 +27970,12 @@
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>-66.01000000000001</v>
+        <v>-68.97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46246</v>
+        <v>46254</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -27756,7 +27993,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6025</v>
+        <v>6325</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -27778,10 +28015,10 @@
         <v>0.26</v>
       </c>
       <c r="K3" t="n">
-        <v>2270</v>
+        <v>2150</v>
       </c>
       <c r="L3" t="n">
-        <v>-62.32</v>
+        <v>-66.01000000000001</v>
       </c>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -27790,12 +28027,12 @@
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>-62.32</v>
+        <v>-66.01000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46237</v>
+        <v>46246</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -27813,7 +28050,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5925</v>
+        <v>6025</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -27835,10 +28072,10 @@
         <v>0.26</v>
       </c>
       <c r="K4" t="n">
-        <v>2610</v>
+        <v>2270</v>
       </c>
       <c r="L4" t="n">
-        <v>-55.95</v>
+        <v>-62.32</v>
       </c>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
@@ -27847,12 +28084,12 @@
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>-55.95</v>
+        <v>-62.32</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46259</v>
+        <v>46237</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -27861,20 +28098,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>53.2</v>
+        <v>5925</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -27883,15 +28120,19 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>75</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="I5" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.26</v>
+      </c>
       <c r="K5" t="n">
-        <v>34.05</v>
+        <v>2610</v>
       </c>
       <c r="L5" t="n">
-        <v>-36</v>
+        <v>-55.95</v>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
@@ -27900,12 +28141,12 @@
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-36</v>
+        <v>-55.95</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -27914,16 +28155,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>499.5</v>
+        <v>4635</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -27932,37 +28173,41 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="I6" t="n">
-        <v>21.2</v>
+        <v>9.6</v>
       </c>
       <c r="J6" t="n">
-        <v>0.92</v>
+        <v>0.26</v>
       </c>
       <c r="K6" t="n">
-        <v>339.5</v>
+        <v>4900</v>
       </c>
       <c r="L6" t="n">
-        <v>-32.03</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+        <v>5.72</v>
+      </c>
+      <c r="M6" t="n">
+        <v>2115</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-54.37</v>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>-32.03</v>
+        <v>-54.37</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46202</v>
+        <v>46259</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -27971,41 +28216,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>955</v>
+        <v>53.2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>100</v>
-      </c>
-      <c r="I7" t="n">
-        <v>14.2</v>
-      </c>
-      <c r="J7" t="n">
-        <v>0.4</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="n">
-        <v>671</v>
+        <v>34.05</v>
       </c>
       <c r="L7" t="n">
-        <v>-29.74</v>
+        <v>-36</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -28014,12 +28255,12 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>-29.74</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46251</v>
+        <v>46202</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -28028,51 +28269,59 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>47.15</v>
+        <v>34.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>75</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="I8" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.42</v>
+      </c>
       <c r="K8" t="n">
-        <v>34.8</v>
+        <v>27.65</v>
       </c>
       <c r="L8" t="n">
-        <v>-26.19</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+        <v>-19.15</v>
+      </c>
+      <c r="M8" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-26.75</v>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>-26.19</v>
+        <v>-26.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46202</v>
+        <v>46251</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -28081,20 +28330,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>65.5</v>
+        <v>47.15</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -28103,19 +28352,15 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>77</v>
-      </c>
-      <c r="I9" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.71</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>51.7</v>
+        <v>34.8</v>
       </c>
       <c r="L9" t="n">
-        <v>-21.07</v>
+        <v>-26.19</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -28124,12 +28369,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>-21.07</v>
+        <v>-26.19</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -28138,50 +28383,54 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>158</v>
+        <v>1215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I10" t="n">
-        <v>16.4</v>
+        <v>25</v>
       </c>
       <c r="J10" t="n">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="K10" t="n">
-        <v>125.5</v>
+        <v>981</v>
       </c>
       <c r="L10" t="n">
-        <v>-20.57</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+        <v>-19.26</v>
+      </c>
+      <c r="M10" t="n">
+        <v>897</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-26.17</v>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>-20.57</v>
+        <v>-26.17</v>
       </c>
     </row>
     <row r="11">
@@ -28195,50 +28444,54 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>6197</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>佳必琪</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>344.5</v>
+        <v>71.7</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I11" t="n">
-        <v>27.5</v>
+        <v>6.8</v>
       </c>
       <c r="J11" t="n">
-        <v>1.22</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>277.5</v>
+        <v>70.7</v>
       </c>
       <c r="L11" t="n">
-        <v>-19.45</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+        <v>-1.39</v>
+      </c>
+      <c r="M11" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-21.62</v>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-19.45</v>
+        <v>-21.62</v>
       </c>
     </row>
     <row r="12">
@@ -28252,16 +28505,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1215</v>
+        <v>955</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -28274,33 +28527,37 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="I12" t="n">
-        <v>25</v>
+        <v>14.2</v>
       </c>
       <c r="J12" t="n">
-        <v>0.67</v>
+        <v>0.4</v>
       </c>
       <c r="K12" t="n">
-        <v>981</v>
+        <v>671</v>
       </c>
       <c r="L12" t="n">
-        <v>-19.26</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+        <v>-29.74</v>
+      </c>
+      <c r="M12" t="n">
+        <v>753</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-21.15</v>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-19.26</v>
+        <v>-21.15</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -28318,7 +28575,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>143</v>
+        <v>158</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -28340,10 +28597,10 @@
         <v>1.11</v>
       </c>
       <c r="K13" t="n">
-        <v>115.5</v>
+        <v>125.5</v>
       </c>
       <c r="L13" t="n">
-        <v>-19.23</v>
+        <v>-20.57</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -28352,7 +28609,7 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-19.23</v>
+        <v>-20.57</v>
       </c>
     </row>
     <row r="14">
@@ -28414,7 +28671,7 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46202</v>
+        <v>46252</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -28423,16 +28680,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>34.2</v>
+        <v>2225</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -28445,19 +28702,19 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I15" t="n">
-        <v>5.9</v>
+        <v>30.7</v>
       </c>
       <c r="J15" t="n">
-        <v>0.42</v>
+        <v>0.82</v>
       </c>
       <c r="K15" t="n">
-        <v>27.65</v>
+        <v>1800</v>
       </c>
       <c r="L15" t="n">
-        <v>-19.15</v>
+        <v>-19.1</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -28466,12 +28723,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-19.15</v>
+        <v>-19.1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46252</v>
+        <v>46210</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -28480,16 +28737,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2382</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>廣達</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>2225</v>
+        <v>373</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -28498,23 +28755,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="I16" t="n">
-        <v>30.7</v>
+        <v>13.2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.82</v>
+        <v>0.49</v>
       </c>
       <c r="K16" t="n">
-        <v>1800</v>
+        <v>302</v>
       </c>
       <c r="L16" t="n">
-        <v>-19.1</v>
+        <v>-19.03</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -28523,12 +28780,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-19.1</v>
+        <v>-19.03</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -28537,16 +28794,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>373</v>
+        <v>2340</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -28555,32 +28812,36 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="I17" t="n">
-        <v>13.2</v>
+        <v>30.7</v>
       </c>
       <c r="J17" t="n">
-        <v>0.49</v>
+        <v>0.82</v>
       </c>
       <c r="K17" t="n">
-        <v>302</v>
+        <v>1910</v>
       </c>
       <c r="L17" t="n">
-        <v>-19.03</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+        <v>-18.38</v>
+      </c>
+      <c r="M17" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-19.02</v>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-19.03</v>
+        <v>-19.02</v>
       </c>
     </row>
     <row r="18">
@@ -28708,16 +28969,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2340</v>
+        <v>65.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -28726,32 +28987,36 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="I20" t="n">
-        <v>30.7</v>
+        <v>10.4</v>
       </c>
       <c r="J20" t="n">
-        <v>0.82</v>
+        <v>0.71</v>
       </c>
       <c r="K20" t="n">
-        <v>1910</v>
+        <v>51.7</v>
       </c>
       <c r="L20" t="n">
-        <v>-18.38</v>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+        <v>-21.07</v>
+      </c>
+      <c r="M20" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-18.63</v>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-18.38</v>
+        <v>-18.63</v>
       </c>
     </row>
     <row r="21">

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R497"/>
+  <dimension ref="A1:R503"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -26549,6 +26549,306 @@
       <c r="P497" t="inlineStr"/>
       <c r="Q497" t="inlineStr"/>
       <c r="R497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>大車隊</t>
+        </is>
+      </c>
+      <c r="E498" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G498" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H498" t="n">
+        <v>97</v>
+      </c>
+      <c r="I498" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J498" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K498" t="inlineStr"/>
+      <c r="L498" t="inlineStr"/>
+      <c r="M498" t="inlineStr"/>
+      <c r="N498" t="inlineStr"/>
+      <c r="O498" t="inlineStr"/>
+      <c r="P498" t="inlineStr"/>
+      <c r="Q498" t="inlineStr"/>
+      <c r="R498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>崇友</t>
+        </is>
+      </c>
+      <c r="E499" t="n">
+        <v>118</v>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G499" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H499" t="n">
+        <v>91</v>
+      </c>
+      <c r="I499" t="n">
+        <v>15</v>
+      </c>
+      <c r="J499" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K499" t="inlineStr"/>
+      <c r="L499" t="inlineStr"/>
+      <c r="M499" t="inlineStr"/>
+      <c r="N499" t="inlineStr"/>
+      <c r="O499" t="inlineStr"/>
+      <c r="P499" t="inlineStr"/>
+      <c r="Q499" t="inlineStr"/>
+      <c r="R499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>零壹</t>
+        </is>
+      </c>
+      <c r="E500" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G500" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H500" t="n">
+        <v>97</v>
+      </c>
+      <c r="I500" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J500" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K500" t="inlineStr"/>
+      <c r="L500" t="inlineStr"/>
+      <c r="M500" t="inlineStr"/>
+      <c r="N500" t="inlineStr"/>
+      <c r="O500" t="inlineStr"/>
+      <c r="P500" t="inlineStr"/>
+      <c r="Q500" t="inlineStr"/>
+      <c r="R500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="E501" t="n">
+        <v>110</v>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G501" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H501" t="n">
+        <v>94</v>
+      </c>
+      <c r="I501" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J501" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K501" t="inlineStr"/>
+      <c r="L501" t="inlineStr"/>
+      <c r="M501" t="inlineStr"/>
+      <c r="N501" t="inlineStr"/>
+      <c r="O501" t="inlineStr"/>
+      <c r="P501" t="inlineStr"/>
+      <c r="Q501" t="inlineStr"/>
+      <c r="R501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>隆大</t>
+        </is>
+      </c>
+      <c r="E502" t="n">
+        <v>25</v>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G502" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H502" t="n">
+        <v>94</v>
+      </c>
+      <c r="I502" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J502" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K502" t="inlineStr"/>
+      <c r="L502" t="inlineStr"/>
+      <c r="M502" t="inlineStr"/>
+      <c r="N502" t="inlineStr"/>
+      <c r="O502" t="inlineStr"/>
+      <c r="P502" t="inlineStr"/>
+      <c r="Q502" t="inlineStr"/>
+      <c r="R502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>東科-KY</t>
+        </is>
+      </c>
+      <c r="E503" t="n">
+        <v>55.3</v>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G503" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H503" t="n">
+        <v>78</v>
+      </c>
+      <c r="I503" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J503" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K503" t="inlineStr"/>
+      <c r="L503" t="inlineStr"/>
+      <c r="M503" t="inlineStr"/>
+      <c r="N503" t="inlineStr"/>
+      <c r="O503" t="inlineStr"/>
+      <c r="P503" t="inlineStr"/>
+      <c r="Q503" t="inlineStr"/>
+      <c r="R503" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -28846,7 +29146,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46226</v>
+        <v>46210</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -28855,38 +29155,38 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1190</v>
+        <v>34.15</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="I18" t="n">
-        <v>38.8</v>
+        <v>5.9</v>
       </c>
       <c r="J18" t="n">
-        <v>1.03</v>
+        <v>0.42</v>
       </c>
       <c r="K18" t="n">
-        <v>967</v>
+        <v>27.75</v>
       </c>
       <c r="L18" t="n">
         <v>-18.74</v>
@@ -28903,7 +29203,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46210</v>
+        <v>46226</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -28912,38 +29212,38 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>34.15</v>
+        <v>1190</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="I19" t="n">
-        <v>5.9</v>
+        <v>38.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0.42</v>
+        <v>1.03</v>
       </c>
       <c r="K19" t="n">
-        <v>27.75</v>
+        <v>967</v>
       </c>
       <c r="L19" t="n">
         <v>-18.74</v>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -493,19 +493,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="C3" t="n">
-        <v>37.1</v>
+        <v>39.5</v>
       </c>
       <c r="D3" t="n">
-        <v>-1.56</v>
+        <v>1.26</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.33</v>
+        <v>-3.91</v>
       </c>
       <c r="F3" t="n">
-        <v>71.86</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="G3" t="n">
         <v>-54.37</v>
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D3" t="n">
-        <v>37.1</v>
+        <v>39.5</v>
       </c>
       <c r="E3" t="n">
-        <v>-1.56</v>
+        <v>1.26</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R503"/>
+  <dimension ref="A1:R531"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6307,8 +6307,12 @@
       <c r="L108" t="n">
         <v>-11.19</v>
       </c>
-      <c r="M108" t="inlineStr"/>
-      <c r="N108" t="inlineStr"/>
+      <c r="M108" t="n">
+        <v>123.5</v>
+      </c>
+      <c r="N108" t="n">
+        <v>-7.84</v>
+      </c>
       <c r="O108" t="inlineStr"/>
       <c r="P108" t="inlineStr"/>
       <c r="Q108" t="inlineStr"/>
@@ -6357,8 +6361,12 @@
       <c r="L109" t="n">
         <v>-15.03</v>
       </c>
-      <c r="M109" t="inlineStr"/>
-      <c r="N109" t="inlineStr"/>
+      <c r="M109" t="n">
+        <v>68.7</v>
+      </c>
+      <c r="N109" t="n">
+        <v>82.70999999999999</v>
+      </c>
       <c r="O109" t="inlineStr"/>
       <c r="P109" t="inlineStr"/>
       <c r="Q109" t="inlineStr"/>
@@ -6407,8 +6415,12 @@
       <c r="L110" t="n">
         <v>-2.58</v>
       </c>
-      <c r="M110" t="inlineStr"/>
-      <c r="N110" t="inlineStr"/>
+      <c r="M110" t="n">
+        <v>519</v>
+      </c>
+      <c r="N110" t="n">
+        <v>27.52</v>
+      </c>
       <c r="O110" t="inlineStr"/>
       <c r="P110" t="inlineStr"/>
       <c r="Q110" t="inlineStr"/>
@@ -26849,6 +26861,1390 @@
       <c r="P503" t="inlineStr"/>
       <c r="Q503" t="inlineStr"/>
       <c r="R503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+      <c r="E504" t="n">
+        <v>555</v>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G504" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H504" t="n">
+        <v>96</v>
+      </c>
+      <c r="I504" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J504" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K504" t="inlineStr"/>
+      <c r="L504" t="inlineStr"/>
+      <c r="M504" t="inlineStr"/>
+      <c r="N504" t="inlineStr"/>
+      <c r="O504" t="inlineStr"/>
+      <c r="P504" t="inlineStr"/>
+      <c r="Q504" t="inlineStr"/>
+      <c r="R504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+      <c r="E505" t="n">
+        <v>326</v>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G505" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H505" t="n">
+        <v>90</v>
+      </c>
+      <c r="I505" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J505" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K505" t="inlineStr"/>
+      <c r="L505" t="inlineStr"/>
+      <c r="M505" t="inlineStr"/>
+      <c r="N505" t="inlineStr"/>
+      <c r="O505" t="inlineStr"/>
+      <c r="P505" t="inlineStr"/>
+      <c r="Q505" t="inlineStr"/>
+      <c r="R505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+      <c r="E506" t="n">
+        <v>83.40000000000001</v>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G506" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H506" t="n">
+        <v>87</v>
+      </c>
+      <c r="I506" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J506" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K506" t="inlineStr"/>
+      <c r="L506" t="inlineStr"/>
+      <c r="M506" t="inlineStr"/>
+      <c r="N506" t="inlineStr"/>
+      <c r="O506" t="inlineStr"/>
+      <c r="P506" t="inlineStr"/>
+      <c r="Q506" t="inlineStr"/>
+      <c r="R506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>漢科</t>
+        </is>
+      </c>
+      <c r="E507" t="n">
+        <v>136</v>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G507" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H507" t="n">
+        <v>77</v>
+      </c>
+      <c r="I507" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J507" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K507" t="inlineStr"/>
+      <c r="L507" t="inlineStr"/>
+      <c r="M507" t="inlineStr"/>
+      <c r="N507" t="inlineStr"/>
+      <c r="O507" t="inlineStr"/>
+      <c r="P507" t="inlineStr"/>
+      <c r="Q507" t="inlineStr"/>
+      <c r="R507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="E508" t="n">
+        <v>251.5</v>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G508" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H508" t="n">
+        <v>77</v>
+      </c>
+      <c r="I508" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J508" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K508" t="inlineStr"/>
+      <c r="L508" t="inlineStr"/>
+      <c r="M508" t="inlineStr"/>
+      <c r="N508" t="inlineStr"/>
+      <c r="O508" t="inlineStr"/>
+      <c r="P508" t="inlineStr"/>
+      <c r="Q508" t="inlineStr"/>
+      <c r="R508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="E509" t="n">
+        <v>1135</v>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G509" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H509" t="n">
+        <v>76</v>
+      </c>
+      <c r="I509" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J509" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K509" t="inlineStr"/>
+      <c r="L509" t="inlineStr"/>
+      <c r="M509" t="inlineStr"/>
+      <c r="N509" t="inlineStr"/>
+      <c r="O509" t="inlineStr"/>
+      <c r="P509" t="inlineStr"/>
+      <c r="Q509" t="inlineStr"/>
+      <c r="R509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="E510" t="n">
+        <v>59.5</v>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G510" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H510" t="n">
+        <v>68</v>
+      </c>
+      <c r="I510" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J510" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K510" t="inlineStr"/>
+      <c r="L510" t="inlineStr"/>
+      <c r="M510" t="inlineStr"/>
+      <c r="N510" t="inlineStr"/>
+      <c r="O510" t="inlineStr"/>
+      <c r="P510" t="inlineStr"/>
+      <c r="Q510" t="inlineStr"/>
+      <c r="R510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="E511" t="n">
+        <v>3435</v>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G511" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H511" t="n">
+        <v>100</v>
+      </c>
+      <c r="I511" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J511" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K511" t="inlineStr"/>
+      <c r="L511" t="inlineStr"/>
+      <c r="M511" t="inlineStr"/>
+      <c r="N511" t="inlineStr"/>
+      <c r="O511" t="inlineStr"/>
+      <c r="P511" t="inlineStr"/>
+      <c r="Q511" t="inlineStr"/>
+      <c r="R511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="E512" t="n">
+        <v>756</v>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G512" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H512" t="n">
+        <v>100</v>
+      </c>
+      <c r="I512" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J512" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K512" t="inlineStr"/>
+      <c r="L512" t="inlineStr"/>
+      <c r="M512" t="inlineStr"/>
+      <c r="N512" t="inlineStr"/>
+      <c r="O512" t="inlineStr"/>
+      <c r="P512" t="inlineStr"/>
+      <c r="Q512" t="inlineStr"/>
+      <c r="R512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E513" t="n">
+        <v>2480</v>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G513" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H513" t="n">
+        <v>100</v>
+      </c>
+      <c r="I513" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J513" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K513" t="inlineStr"/>
+      <c r="L513" t="inlineStr"/>
+      <c r="M513" t="inlineStr"/>
+      <c r="N513" t="inlineStr"/>
+      <c r="O513" t="inlineStr"/>
+      <c r="P513" t="inlineStr"/>
+      <c r="Q513" t="inlineStr"/>
+      <c r="R513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="E514" t="n">
+        <v>105</v>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G514" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H514" t="n">
+        <v>94</v>
+      </c>
+      <c r="I514" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J514" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K514" t="inlineStr"/>
+      <c r="L514" t="inlineStr"/>
+      <c r="M514" t="inlineStr"/>
+      <c r="N514" t="inlineStr"/>
+      <c r="O514" t="inlineStr"/>
+      <c r="P514" t="inlineStr"/>
+      <c r="Q514" t="inlineStr"/>
+      <c r="R514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>八方雲集</t>
+        </is>
+      </c>
+      <c r="E515" t="n">
+        <v>180</v>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G515" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H515" t="n">
+        <v>94</v>
+      </c>
+      <c r="I515" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J515" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K515" t="inlineStr"/>
+      <c r="L515" t="inlineStr"/>
+      <c r="M515" t="inlineStr"/>
+      <c r="N515" t="inlineStr"/>
+      <c r="O515" t="inlineStr"/>
+      <c r="P515" t="inlineStr"/>
+      <c r="Q515" t="inlineStr"/>
+      <c r="R515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="E516" t="n">
+        <v>42.85</v>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G516" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H516" t="n">
+        <v>92</v>
+      </c>
+      <c r="I516" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J516" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K516" t="inlineStr"/>
+      <c r="L516" t="inlineStr"/>
+      <c r="M516" t="inlineStr"/>
+      <c r="N516" t="inlineStr"/>
+      <c r="O516" t="inlineStr"/>
+      <c r="P516" t="inlineStr"/>
+      <c r="Q516" t="inlineStr"/>
+      <c r="R516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="E517" t="n">
+        <v>836</v>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G517" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H517" t="n">
+        <v>90</v>
+      </c>
+      <c r="I517" t="n">
+        <v>25</v>
+      </c>
+      <c r="J517" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K517" t="inlineStr"/>
+      <c r="L517" t="inlineStr"/>
+      <c r="M517" t="inlineStr"/>
+      <c r="N517" t="inlineStr"/>
+      <c r="O517" t="inlineStr"/>
+      <c r="P517" t="inlineStr"/>
+      <c r="Q517" t="inlineStr"/>
+      <c r="R517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="E518" t="n">
+        <v>525</v>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G518" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H518" t="n">
+        <v>90</v>
+      </c>
+      <c r="I518" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J518" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K518" t="inlineStr"/>
+      <c r="L518" t="inlineStr"/>
+      <c r="M518" t="inlineStr"/>
+      <c r="N518" t="inlineStr"/>
+      <c r="O518" t="inlineStr"/>
+      <c r="P518" t="inlineStr"/>
+      <c r="Q518" t="inlineStr"/>
+      <c r="R518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="E519" t="n">
+        <v>160.5</v>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G519" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H519" t="n">
+        <v>90</v>
+      </c>
+      <c r="I519" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J519" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K519" t="inlineStr"/>
+      <c r="L519" t="inlineStr"/>
+      <c r="M519" t="inlineStr"/>
+      <c r="N519" t="inlineStr"/>
+      <c r="O519" t="inlineStr"/>
+      <c r="P519" t="inlineStr"/>
+      <c r="Q519" t="inlineStr"/>
+      <c r="R519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+      <c r="E520" t="n">
+        <v>38.95</v>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G520" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H520" t="n">
+        <v>84</v>
+      </c>
+      <c r="I520" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J520" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K520" t="inlineStr"/>
+      <c r="L520" t="inlineStr"/>
+      <c r="M520" t="inlineStr"/>
+      <c r="N520" t="inlineStr"/>
+      <c r="O520" t="inlineStr"/>
+      <c r="P520" t="inlineStr"/>
+      <c r="Q520" t="inlineStr"/>
+      <c r="R520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="E521" t="n">
+        <v>1775</v>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G521" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H521" t="n">
+        <v>80</v>
+      </c>
+      <c r="I521" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J521" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K521" t="inlineStr"/>
+      <c r="L521" t="inlineStr"/>
+      <c r="M521" t="inlineStr"/>
+      <c r="N521" t="inlineStr"/>
+      <c r="O521" t="inlineStr"/>
+      <c r="P521" t="inlineStr"/>
+      <c r="Q521" t="inlineStr"/>
+      <c r="R521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="E522" t="n">
+        <v>1530</v>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G522" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H522" t="n">
+        <v>80</v>
+      </c>
+      <c r="I522" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J522" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K522" t="inlineStr"/>
+      <c r="L522" t="inlineStr"/>
+      <c r="M522" t="inlineStr"/>
+      <c r="N522" t="inlineStr"/>
+      <c r="O522" t="inlineStr"/>
+      <c r="P522" t="inlineStr"/>
+      <c r="Q522" t="inlineStr"/>
+      <c r="R522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>達欣工</t>
+        </is>
+      </c>
+      <c r="E523" t="n">
+        <v>89.2</v>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G523" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H523" t="n">
+        <v>79</v>
+      </c>
+      <c r="I523" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J523" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K523" t="inlineStr"/>
+      <c r="L523" t="inlineStr"/>
+      <c r="M523" t="inlineStr"/>
+      <c r="N523" t="inlineStr"/>
+      <c r="O523" t="inlineStr"/>
+      <c r="P523" t="inlineStr"/>
+      <c r="Q523" t="inlineStr"/>
+      <c r="R523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>友輝</t>
+        </is>
+      </c>
+      <c r="E524" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G524" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H524" t="n">
+        <v>77</v>
+      </c>
+      <c r="I524" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J524" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K524" t="inlineStr"/>
+      <c r="L524" t="inlineStr"/>
+      <c r="M524" t="inlineStr"/>
+      <c r="N524" t="inlineStr"/>
+      <c r="O524" t="inlineStr"/>
+      <c r="P524" t="inlineStr"/>
+      <c r="Q524" t="inlineStr"/>
+      <c r="R524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="E525" t="n">
+        <v>333.5</v>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G525" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H525" t="n">
+        <v>65</v>
+      </c>
+      <c r="I525" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J525" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K525" t="inlineStr"/>
+      <c r="L525" t="inlineStr"/>
+      <c r="M525" t="inlineStr"/>
+      <c r="N525" t="inlineStr"/>
+      <c r="O525" t="inlineStr"/>
+      <c r="P525" t="inlineStr"/>
+      <c r="Q525" t="inlineStr"/>
+      <c r="R525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="E526" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G526" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H526" t="n">
+        <v>62</v>
+      </c>
+      <c r="I526" t="n">
+        <v>10</v>
+      </c>
+      <c r="J526" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K526" t="inlineStr"/>
+      <c r="L526" t="inlineStr"/>
+      <c r="M526" t="inlineStr"/>
+      <c r="N526" t="inlineStr"/>
+      <c r="O526" t="inlineStr"/>
+      <c r="P526" t="inlineStr"/>
+      <c r="Q526" t="inlineStr"/>
+      <c r="R526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+      <c r="E527" t="n">
+        <v>1460</v>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G527" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H527" t="n">
+        <v>60</v>
+      </c>
+      <c r="I527" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J527" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K527" t="inlineStr"/>
+      <c r="L527" t="inlineStr"/>
+      <c r="M527" t="inlineStr"/>
+      <c r="N527" t="inlineStr"/>
+      <c r="O527" t="inlineStr"/>
+      <c r="P527" t="inlineStr"/>
+      <c r="Q527" t="inlineStr"/>
+      <c r="R527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>德昌</t>
+        </is>
+      </c>
+      <c r="E528" t="n">
+        <v>69.59999999999999</v>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G528" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H528" t="n">
+        <v>79</v>
+      </c>
+      <c r="I528" t="inlineStr"/>
+      <c r="J528" t="inlineStr"/>
+      <c r="K528" t="inlineStr"/>
+      <c r="L528" t="inlineStr"/>
+      <c r="M528" t="inlineStr"/>
+      <c r="N528" t="inlineStr"/>
+      <c r="O528" t="inlineStr"/>
+      <c r="P528" t="inlineStr"/>
+      <c r="Q528" t="inlineStr"/>
+      <c r="R528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+      <c r="E529" t="n">
+        <v>377.5</v>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G529" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H529" t="n">
+        <v>77</v>
+      </c>
+      <c r="I529" t="inlineStr"/>
+      <c r="J529" t="inlineStr"/>
+      <c r="K529" t="inlineStr"/>
+      <c r="L529" t="inlineStr"/>
+      <c r="M529" t="inlineStr"/>
+      <c r="N529" t="inlineStr"/>
+      <c r="O529" t="inlineStr"/>
+      <c r="P529" t="inlineStr"/>
+      <c r="Q529" t="inlineStr"/>
+      <c r="R529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>鑫龍騰</t>
+        </is>
+      </c>
+      <c r="E530" t="n">
+        <v>23.3</v>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G530" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H530" t="n">
+        <v>77</v>
+      </c>
+      <c r="I530" t="inlineStr"/>
+      <c r="J530" t="inlineStr"/>
+      <c r="K530" t="inlineStr"/>
+      <c r="L530" t="inlineStr"/>
+      <c r="M530" t="inlineStr"/>
+      <c r="N530" t="inlineStr"/>
+      <c r="O530" t="inlineStr"/>
+      <c r="P530" t="inlineStr"/>
+      <c r="Q530" t="inlineStr"/>
+      <c r="R530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="E531" t="n">
+        <v>202</v>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G531" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H531" t="n">
+        <v>69</v>
+      </c>
+      <c r="I531" t="inlineStr"/>
+      <c r="J531" t="inlineStr"/>
+      <c r="K531" t="inlineStr"/>
+      <c r="L531" t="inlineStr"/>
+      <c r="M531" t="inlineStr"/>
+      <c r="N531" t="inlineStr"/>
+      <c r="O531" t="inlineStr"/>
+      <c r="P531" t="inlineStr"/>
+      <c r="Q531" t="inlineStr"/>
+      <c r="R531" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -26963,7 +28359,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46202</v>
+        <v>46205</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -26972,59 +28368,55 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>2305</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>全友</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>995</v>
+        <v>37.6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>80</v>
-      </c>
-      <c r="I2" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0.75</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>855</v>
+        <v>31.95</v>
       </c>
       <c r="L2" t="n">
-        <v>-14.07</v>
+        <v>-15.03</v>
       </c>
       <c r="M2" t="n">
-        <v>1710</v>
+        <v>68.7</v>
       </c>
       <c r="N2" t="n">
-        <v>71.86</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr"/>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="n">
-        <v>71.86</v>
+        <v>82.70999999999999</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46260</v>
+        <v>46202</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -27042,7 +28434,7 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1065</v>
+        <v>995</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -27064,24 +28456,28 @@
         <v>0.75</v>
       </c>
       <c r="K3" t="n">
+        <v>855</v>
+      </c>
+      <c r="L3" t="n">
+        <v>-14.07</v>
+      </c>
+      <c r="M3" t="n">
         <v>1710</v>
       </c>
-      <c r="L3" t="n">
-        <v>60.56</v>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="N3" t="n">
+        <v>71.86</v>
+      </c>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr"/>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>60.56</v>
+        <v>71.86</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46202</v>
+        <v>46260</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -27090,16 +28486,16 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2300</v>
+        <v>1065</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -27112,37 +28508,33 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I4" t="n">
-        <v>24.6</v>
+        <v>21.8</v>
       </c>
       <c r="J4" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="K4" t="n">
-        <v>2095</v>
+        <v>1710</v>
       </c>
       <c r="L4" t="n">
-        <v>-8.91</v>
-      </c>
-      <c r="M4" t="n">
-        <v>3555</v>
-      </c>
-      <c r="N4" t="n">
-        <v>54.57</v>
-      </c>
+        <v>60.56</v>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>54.57</v>
+        <v>60.56</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -27160,7 +28552,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2165</v>
+        <v>2300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -27182,24 +28574,28 @@
         <v>0.66</v>
       </c>
       <c r="K5" t="n">
-        <v>3235</v>
+        <v>2095</v>
       </c>
       <c r="L5" t="n">
-        <v>49.42</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+        <v>-8.91</v>
+      </c>
+      <c r="M5" t="n">
+        <v>3555</v>
+      </c>
+      <c r="N5" t="n">
+        <v>54.57</v>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>49.42</v>
+        <v>54.57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46234</v>
+        <v>46218</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -27217,7 +28613,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2320</v>
+        <v>2165</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -27239,10 +28635,10 @@
         <v>0.66</v>
       </c>
       <c r="K6" t="n">
-        <v>3425</v>
+        <v>3235</v>
       </c>
       <c r="L6" t="n">
-        <v>47.63</v>
+        <v>49.42</v>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
@@ -27251,7 +28647,7 @@
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>47.63</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="7">
@@ -27265,41 +28661,41 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>821</v>
+        <v>2320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="I7" t="n">
-        <v>38.8</v>
+        <v>24.6</v>
       </c>
       <c r="J7" t="n">
-        <v>1.03</v>
+        <v>0.66</v>
       </c>
       <c r="K7" t="n">
-        <v>1180</v>
+        <v>3425</v>
       </c>
       <c r="L7" t="n">
-        <v>43.73</v>
+        <v>47.63</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -27308,7 +28704,7 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>43.73</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="8">
@@ -27322,41 +28718,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>902</v>
+        <v>821</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I8" t="n">
-        <v>21.8</v>
+        <v>38.8</v>
       </c>
       <c r="J8" t="n">
-        <v>0.75</v>
+        <v>1.03</v>
       </c>
       <c r="K8" t="n">
-        <v>1250</v>
+        <v>1180</v>
       </c>
       <c r="L8" t="n">
-        <v>38.58</v>
+        <v>43.73</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -27365,12 +28761,12 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>38.58</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46252</v>
+        <v>46234</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -27388,7 +28784,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1005</v>
+        <v>902</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -27410,10 +28806,10 @@
         <v>0.75</v>
       </c>
       <c r="K9" t="n">
-        <v>1385</v>
+        <v>1250</v>
       </c>
       <c r="L9" t="n">
-        <v>37.81</v>
+        <v>38.58</v>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
@@ -27422,12 +28818,12 @@
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>37.81</v>
+        <v>38.58</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -27445,7 +28841,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -27470,7 +28866,7 @@
         <v>1385</v>
       </c>
       <c r="L10" t="n">
-        <v>37.13</v>
+        <v>37.81</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -27479,12 +28875,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>37.13</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -27493,16 +28889,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>131</v>
+        <v>1010</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -27515,19 +28911,19 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I11" t="n">
-        <v>14.1</v>
+        <v>21.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="K11" t="n">
-        <v>179.5</v>
+        <v>1385</v>
       </c>
       <c r="L11" t="n">
-        <v>37.02</v>
+        <v>37.13</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -27536,7 +28932,7 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>37.02</v>
+        <v>37.13</v>
       </c>
     </row>
     <row r="12">
@@ -27550,16 +28946,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>369</v>
+        <v>131</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -27575,16 +28971,16 @@
         <v>90</v>
       </c>
       <c r="I12" t="n">
-        <v>21.2</v>
+        <v>14.1</v>
       </c>
       <c r="J12" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="K12" t="n">
-        <v>496.5</v>
+        <v>179.5</v>
       </c>
       <c r="L12" t="n">
-        <v>34.55</v>
+        <v>37.02</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -27593,12 +28989,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>34.55</v>
+        <v>37.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46210</v>
+        <v>46234</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -27607,37 +29003,41 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>185.5</v>
+        <v>369</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>69</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="I13" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.92</v>
+      </c>
       <c r="K13" t="n">
-        <v>247</v>
+        <v>496.5</v>
       </c>
       <c r="L13" t="n">
-        <v>33.15</v>
+        <v>34.55</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -27646,12 +29046,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>33.15</v>
+        <v>34.55</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -27660,41 +29060,37 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>145.5</v>
+        <v>185.5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>62</v>
-      </c>
-      <c r="I14" t="n">
-        <v>10</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.31</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>193.5</v>
+        <v>247</v>
       </c>
       <c r="L14" t="n">
-        <v>32.99</v>
+        <v>33.15</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -27703,12 +29099,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>32.99</v>
+        <v>33.15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -27717,16 +29113,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5115</v>
+        <v>145.5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -27735,23 +29131,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I15" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="J15" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="K15" t="n">
-        <v>6620</v>
+        <v>193.5</v>
       </c>
       <c r="L15" t="n">
-        <v>29.42</v>
+        <v>32.99</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -27760,12 +29156,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>29.42</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -27774,20 +29170,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>181.5</v>
+        <v>5115</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -27796,15 +29192,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>69</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="I16" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.26</v>
+      </c>
       <c r="K16" t="n">
-        <v>233</v>
+        <v>6620</v>
       </c>
       <c r="L16" t="n">
-        <v>28.37</v>
+        <v>29.42</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -27813,12 +29213,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>28.37</v>
+        <v>29.42</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46244</v>
+        <v>46218</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -27827,41 +29227,37 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>401.5</v>
+        <v>181.5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>90</v>
-      </c>
-      <c r="I17" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.92</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>509</v>
+        <v>233</v>
       </c>
       <c r="L17" t="n">
-        <v>26.77</v>
+        <v>28.37</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -27870,12 +29266,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>26.77</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46211</v>
+        <v>46205</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -27884,55 +29280,55 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5050</v>
+        <v>407</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>65</v>
-      </c>
-      <c r="I18" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.26</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>6265</v>
+        <v>396.5</v>
       </c>
       <c r="L18" t="n">
-        <v>24.06</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+        <v>-2.58</v>
+      </c>
+      <c r="M18" t="n">
+        <v>519</v>
+      </c>
+      <c r="N18" t="n">
+        <v>27.52</v>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>24.06</v>
+        <v>27.52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46202</v>
+        <v>46244</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -27941,16 +29337,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>97.40000000000001</v>
+        <v>401.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -27963,37 +29359,33 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="I19" t="n">
-        <v>12.4</v>
+        <v>21.2</v>
       </c>
       <c r="J19" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="K19" t="n">
-        <v>99.3</v>
+        <v>509</v>
       </c>
       <c r="L19" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M19" t="n">
-        <v>120</v>
-      </c>
-      <c r="N19" t="n">
-        <v>23.2</v>
-      </c>
+        <v>26.77</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>23.2</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46244</v>
+        <v>46211</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -28002,16 +29394,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2765</v>
+        <v>5050</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -28020,23 +29412,23 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>100</v>
+        <v>65</v>
       </c>
       <c r="I20" t="n">
-        <v>24.6</v>
+        <v>9.6</v>
       </c>
       <c r="J20" t="n">
-        <v>0.66</v>
+        <v>0.26</v>
       </c>
       <c r="K20" t="n">
-        <v>3380</v>
+        <v>6265</v>
       </c>
       <c r="L20" t="n">
-        <v>22.24</v>
+        <v>24.06</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -28045,12 +29437,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>22.24</v>
+        <v>24.06</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -28059,16 +29451,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>155.5</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -28077,32 +29469,36 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>62</v>
+        <v>97</v>
       </c>
       <c r="I21" t="n">
-        <v>10</v>
+        <v>12.4</v>
       </c>
       <c r="J21" t="n">
-        <v>0.31</v>
+        <v>0.73</v>
       </c>
       <c r="K21" t="n">
-        <v>189.5</v>
+        <v>99.3</v>
       </c>
       <c r="L21" t="n">
-        <v>21.86</v>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+        <v>1.95</v>
+      </c>
+      <c r="M21" t="n">
+        <v>120</v>
+      </c>
+      <c r="N21" t="n">
+        <v>23.2</v>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>21.86</v>
+        <v>23.2</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R531"/>
+  <dimension ref="A1:R532"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28245,6 +28245,56 @@
       <c r="P531" t="inlineStr"/>
       <c r="Q531" t="inlineStr"/>
       <c r="R531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="E532" t="n">
+        <v>2110</v>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G532" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H532" t="n">
+        <v>65</v>
+      </c>
+      <c r="I532" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J532" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K532" t="inlineStr"/>
+      <c r="L532" t="inlineStr"/>
+      <c r="M532" t="inlineStr"/>
+      <c r="N532" t="inlineStr"/>
+      <c r="O532" t="inlineStr"/>
+      <c r="P532" t="inlineStr"/>
+      <c r="Q532" t="inlineStr"/>
+      <c r="R532" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -30542,7 +30592,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46210</v>
+        <v>46226</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -30551,38 +30601,38 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34.15</v>
+        <v>1190</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="I18" t="n">
-        <v>5.9</v>
+        <v>38.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.42</v>
+        <v>1.03</v>
       </c>
       <c r="K18" t="n">
-        <v>27.75</v>
+        <v>967</v>
       </c>
       <c r="L18" t="n">
         <v>-18.74</v>
@@ -30599,7 +30649,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46226</v>
+        <v>46210</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -30608,38 +30658,38 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1190</v>
+        <v>34.15</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="I19" t="n">
-        <v>38.8</v>
+        <v>5.9</v>
       </c>
       <c r="J19" t="n">
-        <v>1.03</v>
+        <v>0.42</v>
       </c>
       <c r="K19" t="n">
-        <v>967</v>
+        <v>27.75</v>
       </c>
       <c r="L19" t="n">
         <v>-18.74</v>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="C2" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.87</v>
+        <v>-0.89</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.25</v>
+        <v>-1.31</v>
       </c>
       <c r="F2" t="n">
         <v>60.56</v>
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="D2" t="n">
-        <v>43.2</v>
+        <v>43.1</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.87</v>
+        <v>-0.89</v>
       </c>
     </row>
     <row r="3">
@@ -21121,8 +21121,12 @@
       </c>
       <c r="I387" t="inlineStr"/>
       <c r="J387" t="inlineStr"/>
-      <c r="K387" t="inlineStr"/>
-      <c r="L387" t="inlineStr"/>
+      <c r="K387" t="n">
+        <v>33.35</v>
+      </c>
+      <c r="L387" t="n">
+        <v>-8.130000000000001</v>
+      </c>
       <c r="M387" t="inlineStr"/>
       <c r="N387" t="inlineStr"/>
       <c r="O387" t="inlineStr"/>
@@ -30592,7 +30596,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46226</v>
+        <v>46210</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -30601,38 +30605,38 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1190</v>
+        <v>34.15</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="I18" t="n">
-        <v>38.8</v>
+        <v>5.9</v>
       </c>
       <c r="J18" t="n">
-        <v>1.03</v>
+        <v>0.42</v>
       </c>
       <c r="K18" t="n">
-        <v>967</v>
+        <v>27.75</v>
       </c>
       <c r="L18" t="n">
         <v>-18.74</v>
@@ -30649,7 +30653,7 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46210</v>
+        <v>46226</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -30658,38 +30662,38 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>34.15</v>
+        <v>1190</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="I19" t="n">
-        <v>5.9</v>
+        <v>38.8</v>
       </c>
       <c r="J19" t="n">
-        <v>0.42</v>
+        <v>1.03</v>
       </c>
       <c r="K19" t="n">
-        <v>27.75</v>
+        <v>967</v>
       </c>
       <c r="L19" t="n">
         <v>-18.74</v>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="C2" t="n">
-        <v>43.1</v>
+        <v>43.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.89</v>
+        <v>-0.63</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.31</v>
+        <v>-1.2</v>
       </c>
       <c r="F2" t="n">
         <v>60.56</v>
@@ -493,16 +493,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="C3" t="n">
-        <v>39.5</v>
+        <v>37.5</v>
       </c>
       <c r="D3" t="n">
-        <v>1.26</v>
+        <v>0.58</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.91</v>
+        <v>-4.4</v>
       </c>
       <c r="F3" t="n">
         <v>82.70999999999999</v>
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>288</v>
+        <v>322</v>
       </c>
       <c r="D2" t="n">
-        <v>43.1</v>
+        <v>43.5</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.89</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>38</v>
+        <v>72</v>
       </c>
       <c r="D3" t="n">
-        <v>39.5</v>
+        <v>37.5</v>
       </c>
       <c r="E3" t="n">
-        <v>1.26</v>
+        <v>0.58</v>
       </c>
     </row>
   </sheetData>
@@ -6473,8 +6473,12 @@
       <c r="L111" t="n">
         <v>-7.89</v>
       </c>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
+      <c r="M111" t="n">
+        <v>154</v>
+      </c>
+      <c r="N111" t="n">
+        <v>-2.84</v>
+      </c>
       <c r="O111" t="inlineStr"/>
       <c r="P111" t="inlineStr"/>
       <c r="Q111" t="inlineStr"/>
@@ -6527,8 +6531,12 @@
       <c r="L112" t="n">
         <v>-1.36</v>
       </c>
-      <c r="M112" t="inlineStr"/>
-      <c r="N112" t="inlineStr"/>
+      <c r="M112" t="n">
+        <v>620</v>
+      </c>
+      <c r="N112" t="n">
+        <v>20.16</v>
+      </c>
       <c r="O112" t="inlineStr"/>
       <c r="P112" t="inlineStr"/>
       <c r="Q112" t="inlineStr"/>
@@ -6581,8 +6589,12 @@
       <c r="L113" t="n">
         <v>-0.8100000000000001</v>
       </c>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+      <c r="M113" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="N113" t="n">
+        <v>-4.47</v>
+      </c>
       <c r="O113" t="inlineStr"/>
       <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr"/>
@@ -6635,8 +6647,12 @@
       <c r="L114" t="n">
         <v>-12.08</v>
       </c>
-      <c r="M114" t="inlineStr"/>
-      <c r="N114" t="inlineStr"/>
+      <c r="M114" t="n">
+        <v>345</v>
+      </c>
+      <c r="N114" t="n">
+        <v>-4.17</v>
+      </c>
       <c r="O114" t="inlineStr"/>
       <c r="P114" t="inlineStr"/>
       <c r="Q114" t="inlineStr"/>
@@ -6689,8 +6705,12 @@
       <c r="L115" t="n">
         <v>-9.5</v>
       </c>
-      <c r="M115" t="inlineStr"/>
-      <c r="N115" t="inlineStr"/>
+      <c r="M115" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="N115" t="n">
+        <v>-12.27</v>
+      </c>
       <c r="O115" t="inlineStr"/>
       <c r="P115" t="inlineStr"/>
       <c r="Q115" t="inlineStr"/>
@@ -6743,8 +6763,12 @@
       <c r="L116" t="n">
         <v>-11.9</v>
       </c>
-      <c r="M116" t="inlineStr"/>
-      <c r="N116" t="inlineStr"/>
+      <c r="M116" t="n">
+        <v>140</v>
+      </c>
+      <c r="N116" t="n">
+        <v>-4.76</v>
+      </c>
       <c r="O116" t="inlineStr"/>
       <c r="P116" t="inlineStr"/>
       <c r="Q116" t="inlineStr"/>
@@ -6797,8 +6821,12 @@
       <c r="L117" t="n">
         <v>11.6</v>
       </c>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
+      <c r="M117" t="n">
+        <v>254</v>
+      </c>
+      <c r="N117" t="n">
+        <v>7.17</v>
+      </c>
       <c r="O117" t="inlineStr"/>
       <c r="P117" t="inlineStr"/>
       <c r="Q117" t="inlineStr"/>
@@ -6851,8 +6879,12 @@
       <c r="L118" t="n">
         <v>-5.91</v>
       </c>
-      <c r="M118" t="inlineStr"/>
-      <c r="N118" t="inlineStr"/>
+      <c r="M118" t="n">
+        <v>1125</v>
+      </c>
+      <c r="N118" t="n">
+        <v>-5.06</v>
+      </c>
       <c r="O118" t="inlineStr"/>
       <c r="P118" t="inlineStr"/>
       <c r="Q118" t="inlineStr"/>
@@ -6905,8 +6937,12 @@
       <c r="L119" t="n">
         <v>0.15</v>
       </c>
-      <c r="M119" t="inlineStr"/>
-      <c r="N119" t="inlineStr"/>
+      <c r="M119" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="N119" t="n">
+        <v>-10.86</v>
+      </c>
       <c r="O119" t="inlineStr"/>
       <c r="P119" t="inlineStr"/>
       <c r="Q119" t="inlineStr"/>
@@ -6959,8 +6995,12 @@
       <c r="L120" t="n">
         <v>20</v>
       </c>
-      <c r="M120" t="inlineStr"/>
-      <c r="N120" t="inlineStr"/>
+      <c r="M120" t="n">
+        <v>3585</v>
+      </c>
+      <c r="N120" t="n">
+        <v>46.33</v>
+      </c>
       <c r="O120" t="inlineStr"/>
       <c r="P120" t="inlineStr"/>
       <c r="Q120" t="inlineStr"/>
@@ -7013,8 +7053,12 @@
       <c r="L121" t="n">
         <v>-5.32</v>
       </c>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+      <c r="M121" t="n">
+        <v>790</v>
+      </c>
+      <c r="N121" t="n">
+        <v>-10.53</v>
+      </c>
       <c r="O121" t="inlineStr"/>
       <c r="P121" t="inlineStr"/>
       <c r="Q121" t="inlineStr"/>
@@ -7067,8 +7111,12 @@
       <c r="L122" t="n">
         <v>-3.07</v>
       </c>
-      <c r="M122" t="inlineStr"/>
-      <c r="N122" t="inlineStr"/>
+      <c r="M122" t="n">
+        <v>2575</v>
+      </c>
+      <c r="N122" t="n">
+        <v>5.53</v>
+      </c>
       <c r="O122" t="inlineStr"/>
       <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr"/>
@@ -7121,8 +7169,12 @@
       <c r="L123" t="n">
         <v>6.8</v>
       </c>
-      <c r="M123" t="inlineStr"/>
-      <c r="N123" t="inlineStr"/>
+      <c r="M123" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="N123" t="n">
+        <v>14.08</v>
+      </c>
       <c r="O123" t="inlineStr"/>
       <c r="P123" t="inlineStr"/>
       <c r="Q123" t="inlineStr"/>
@@ -7175,8 +7227,12 @@
       <c r="L124" t="n">
         <v>-10.16</v>
       </c>
-      <c r="M124" t="inlineStr"/>
-      <c r="N124" t="inlineStr"/>
+      <c r="M124" t="n">
+        <v>113</v>
+      </c>
+      <c r="N124" t="n">
+        <v>-8.130000000000001</v>
+      </c>
       <c r="O124" t="inlineStr"/>
       <c r="P124" t="inlineStr"/>
       <c r="Q124" t="inlineStr"/>
@@ -7229,8 +7285,12 @@
       <c r="L125" t="n">
         <v>-18.74</v>
       </c>
-      <c r="M125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
+      <c r="M125" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="N125" t="n">
+        <v>-27.38</v>
+      </c>
       <c r="O125" t="inlineStr"/>
       <c r="P125" t="inlineStr"/>
       <c r="Q125" t="inlineStr"/>
@@ -7283,8 +7343,12 @@
       <c r="L126" t="n">
         <v>-3.59</v>
       </c>
-      <c r="M126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
+      <c r="M126" t="n">
+        <v>104</v>
+      </c>
+      <c r="N126" t="n">
+        <v>-6.73</v>
+      </c>
       <c r="O126" t="inlineStr"/>
       <c r="P126" t="inlineStr"/>
       <c r="Q126" t="inlineStr"/>
@@ -7337,8 +7401,12 @@
       <c r="L127" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="M127" t="inlineStr"/>
-      <c r="N127" t="inlineStr"/>
+      <c r="M127" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="N127" t="n">
+        <v>2.8</v>
+      </c>
       <c r="O127" t="inlineStr"/>
       <c r="P127" t="inlineStr"/>
       <c r="Q127" t="inlineStr"/>
@@ -7391,8 +7459,12 @@
       <c r="L128" t="n">
         <v>2</v>
       </c>
-      <c r="M128" t="inlineStr"/>
-      <c r="N128" t="inlineStr"/>
+      <c r="M128" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="N128" t="n">
+        <v>-1.18</v>
+      </c>
       <c r="O128" t="inlineStr"/>
       <c r="P128" t="inlineStr"/>
       <c r="Q128" t="inlineStr"/>
@@ -7445,8 +7517,12 @@
       <c r="L129" t="n">
         <v>5.11</v>
       </c>
-      <c r="M129" t="inlineStr"/>
-      <c r="N129" t="inlineStr"/>
+      <c r="M129" t="n">
+        <v>890</v>
+      </c>
+      <c r="N129" t="n">
+        <v>-24.26</v>
+      </c>
       <c r="O129" t="inlineStr"/>
       <c r="P129" t="inlineStr"/>
       <c r="Q129" t="inlineStr"/>
@@ -7499,8 +7575,12 @@
       <c r="L130" t="n">
         <v>-16.4</v>
       </c>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+      <c r="M130" t="n">
+        <v>557</v>
+      </c>
+      <c r="N130" t="n">
+        <v>17.14</v>
+      </c>
       <c r="O130" t="inlineStr"/>
       <c r="P130" t="inlineStr"/>
       <c r="Q130" t="inlineStr"/>
@@ -7553,8 +7633,12 @@
       <c r="L131" t="n">
         <v>7.29</v>
       </c>
-      <c r="M131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+      <c r="M131" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="N131" t="n">
+        <v>17.71</v>
+      </c>
       <c r="O131" t="inlineStr"/>
       <c r="P131" t="inlineStr"/>
       <c r="Q131" t="inlineStr"/>
@@ -7607,8 +7691,12 @@
       <c r="L132" t="n">
         <v>-5.74</v>
       </c>
-      <c r="M132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+      <c r="M132" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="N132" t="n">
+        <v>-5.01</v>
+      </c>
       <c r="O132" t="inlineStr"/>
       <c r="P132" t="inlineStr"/>
       <c r="Q132" t="inlineStr"/>
@@ -7661,8 +7749,12 @@
       <c r="L133" t="n">
         <v>-1.83</v>
       </c>
-      <c r="M133" t="inlineStr"/>
-      <c r="N133" t="inlineStr"/>
+      <c r="M133" t="n">
+        <v>2075</v>
+      </c>
+      <c r="N133" t="n">
+        <v>-15.48</v>
+      </c>
       <c r="O133" t="inlineStr"/>
       <c r="P133" t="inlineStr"/>
       <c r="Q133" t="inlineStr"/>
@@ -7715,8 +7807,12 @@
       <c r="L134" t="n">
         <v>9.279999999999999</v>
       </c>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
+      <c r="M134" t="n">
+        <v>1550</v>
+      </c>
+      <c r="N134" t="n">
+        <v>59.79</v>
+      </c>
       <c r="O134" t="inlineStr"/>
       <c r="P134" t="inlineStr"/>
       <c r="Q134" t="inlineStr"/>
@@ -7769,8 +7865,12 @@
       <c r="L135" t="n">
         <v>5.92</v>
       </c>
-      <c r="M135" t="inlineStr"/>
-      <c r="N135" t="inlineStr"/>
+      <c r="M135" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.57</v>
+      </c>
       <c r="O135" t="inlineStr"/>
       <c r="P135" t="inlineStr"/>
       <c r="Q135" t="inlineStr"/>
@@ -7823,8 +7923,12 @@
       <c r="L136" t="n">
         <v>-0.66</v>
       </c>
-      <c r="M136" t="inlineStr"/>
-      <c r="N136" t="inlineStr"/>
+      <c r="M136" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-27.85</v>
+      </c>
       <c r="O136" t="inlineStr"/>
       <c r="P136" t="inlineStr"/>
       <c r="Q136" t="inlineStr"/>
@@ -7877,8 +7981,12 @@
       <c r="L137" t="n">
         <v>-14.2</v>
       </c>
-      <c r="M137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
+      <c r="M137" t="n">
+        <v>54</v>
+      </c>
+      <c r="N137" t="n">
+        <v>-18.43</v>
+      </c>
       <c r="O137" t="inlineStr"/>
       <c r="P137" t="inlineStr"/>
       <c r="Q137" t="inlineStr"/>
@@ -7931,8 +8039,12 @@
       <c r="L138" t="n">
         <v>-19.03</v>
       </c>
-      <c r="M138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
+      <c r="M138" t="n">
+        <v>331</v>
+      </c>
+      <c r="N138" t="n">
+        <v>-11.26</v>
+      </c>
       <c r="O138" t="inlineStr"/>
       <c r="P138" t="inlineStr"/>
       <c r="Q138" t="inlineStr"/>
@@ -7985,8 +8097,12 @@
       <c r="L139" t="n">
         <v>21.86</v>
       </c>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+      <c r="M139" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="N139" t="n">
+        <v>21.86</v>
+      </c>
       <c r="O139" t="inlineStr"/>
       <c r="P139" t="inlineStr"/>
       <c r="Q139" t="inlineStr"/>
@@ -8039,8 +8155,12 @@
       <c r="L140" t="n">
         <v>-6</v>
       </c>
-      <c r="M140" t="inlineStr"/>
-      <c r="N140" t="inlineStr"/>
+      <c r="M140" t="n">
+        <v>1475</v>
+      </c>
+      <c r="N140" t="n">
+        <v>-1.67</v>
+      </c>
       <c r="O140" t="inlineStr"/>
       <c r="P140" t="inlineStr"/>
       <c r="Q140" t="inlineStr"/>
@@ -8089,8 +8209,12 @@
       <c r="L141" t="n">
         <v>-11.6</v>
       </c>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
+      <c r="M141" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="N141" t="n">
+        <v>-13.62</v>
+      </c>
       <c r="O141" t="inlineStr"/>
       <c r="P141" t="inlineStr"/>
       <c r="Q141" t="inlineStr"/>
@@ -8139,8 +8263,12 @@
       <c r="L142" t="n">
         <v>4.21</v>
       </c>
-      <c r="M142" t="inlineStr"/>
-      <c r="N142" t="inlineStr"/>
+      <c r="M142" t="n">
+        <v>378</v>
+      </c>
+      <c r="N142" t="n">
+        <v>-6.44</v>
+      </c>
       <c r="O142" t="inlineStr"/>
       <c r="P142" t="inlineStr"/>
       <c r="Q142" t="inlineStr"/>
@@ -8189,8 +8317,12 @@
       <c r="L143" t="n">
         <v>-2.94</v>
       </c>
-      <c r="M143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
+      <c r="M143" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="N143" t="n">
+        <v>-5.03</v>
+      </c>
       <c r="O143" t="inlineStr"/>
       <c r="P143" t="inlineStr"/>
       <c r="Q143" t="inlineStr"/>
@@ -8239,8 +8371,12 @@
       <c r="L144" t="n">
         <v>33.15</v>
       </c>
-      <c r="M144" t="inlineStr"/>
-      <c r="N144" t="inlineStr"/>
+      <c r="M144" t="n">
+        <v>200.5</v>
+      </c>
+      <c r="N144" t="n">
+        <v>8.09</v>
+      </c>
       <c r="O144" t="inlineStr"/>
       <c r="P144" t="inlineStr"/>
       <c r="Q144" t="inlineStr"/>
@@ -21175,8 +21311,12 @@
       <c r="J388" t="n">
         <v>1.29</v>
       </c>
-      <c r="K388" t="inlineStr"/>
-      <c r="L388" t="inlineStr"/>
+      <c r="K388" t="n">
+        <v>154</v>
+      </c>
+      <c r="L388" t="n">
+        <v>-1.6</v>
+      </c>
       <c r="M388" t="inlineStr"/>
       <c r="N388" t="inlineStr"/>
       <c r="O388" t="inlineStr"/>
@@ -21225,8 +21365,12 @@
       <c r="J389" t="n">
         <v>1.11</v>
       </c>
-      <c r="K389" t="inlineStr"/>
-      <c r="L389" t="inlineStr"/>
+      <c r="K389" t="n">
+        <v>620</v>
+      </c>
+      <c r="L389" t="n">
+        <v>17.65</v>
+      </c>
       <c r="M389" t="inlineStr"/>
       <c r="N389" t="inlineStr"/>
       <c r="O389" t="inlineStr"/>
@@ -21275,8 +21419,12 @@
       <c r="J390" t="n">
         <v>1.26</v>
       </c>
-      <c r="K390" t="inlineStr"/>
-      <c r="L390" t="inlineStr"/>
+      <c r="K390" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="L390" t="n">
+        <v>-3.69</v>
+      </c>
       <c r="M390" t="inlineStr"/>
       <c r="N390" t="inlineStr"/>
       <c r="O390" t="inlineStr"/>
@@ -21325,8 +21473,12 @@
       <c r="J391" t="n">
         <v>1.22</v>
       </c>
-      <c r="K391" t="inlineStr"/>
-      <c r="L391" t="inlineStr"/>
+      <c r="K391" t="n">
+        <v>345</v>
+      </c>
+      <c r="L391" t="n">
+        <v>15.38</v>
+      </c>
       <c r="M391" t="inlineStr"/>
       <c r="N391" t="inlineStr"/>
       <c r="O391" t="inlineStr"/>
@@ -21375,8 +21527,12 @@
       <c r="J392" t="n">
         <v>1.36</v>
       </c>
-      <c r="K392" t="inlineStr"/>
-      <c r="L392" t="inlineStr"/>
+      <c r="K392" t="n">
+        <v>82.2</v>
+      </c>
+      <c r="L392" t="n">
+        <v>1.23</v>
+      </c>
       <c r="M392" t="inlineStr"/>
       <c r="N392" t="inlineStr"/>
       <c r="O392" t="inlineStr"/>
@@ -21425,8 +21581,12 @@
       <c r="J393" t="n">
         <v>1.11</v>
       </c>
-      <c r="K393" t="inlineStr"/>
-      <c r="L393" t="inlineStr"/>
+      <c r="K393" t="n">
+        <v>140</v>
+      </c>
+      <c r="L393" t="n">
+        <v>16.67</v>
+      </c>
       <c r="M393" t="inlineStr"/>
       <c r="N393" t="inlineStr"/>
       <c r="O393" t="inlineStr"/>
@@ -21475,8 +21635,12 @@
       <c r="J394" t="n">
         <v>1.16</v>
       </c>
-      <c r="K394" t="inlineStr"/>
-      <c r="L394" t="inlineStr"/>
+      <c r="K394" t="n">
+        <v>254</v>
+      </c>
+      <c r="L394" t="n">
+        <v>2.63</v>
+      </c>
       <c r="M394" t="inlineStr"/>
       <c r="N394" t="inlineStr"/>
       <c r="O394" t="inlineStr"/>
@@ -21525,8 +21689,12 @@
       <c r="J395" t="n">
         <v>1.03</v>
       </c>
-      <c r="K395" t="inlineStr"/>
-      <c r="L395" t="inlineStr"/>
+      <c r="K395" t="n">
+        <v>1125</v>
+      </c>
+      <c r="L395" t="n">
+        <v>4.65</v>
+      </c>
       <c r="M395" t="inlineStr"/>
       <c r="N395" t="inlineStr"/>
       <c r="O395" t="inlineStr"/>
@@ -21575,8 +21743,12 @@
       <c r="J396" t="n">
         <v>1.35</v>
       </c>
-      <c r="K396" t="inlineStr"/>
-      <c r="L396" t="inlineStr"/>
+      <c r="K396" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="L396" t="n">
+        <v>-10.31</v>
+      </c>
       <c r="M396" t="inlineStr"/>
       <c r="N396" t="inlineStr"/>
       <c r="O396" t="inlineStr"/>
@@ -21625,8 +21797,12 @@
       <c r="J397" t="n">
         <v>0.66</v>
       </c>
-      <c r="K397" t="inlineStr"/>
-      <c r="L397" t="inlineStr"/>
+      <c r="K397" t="n">
+        <v>3585</v>
+      </c>
+      <c r="L397" t="n">
+        <v>8.640000000000001</v>
+      </c>
       <c r="M397" t="inlineStr"/>
       <c r="N397" t="inlineStr"/>
       <c r="O397" t="inlineStr"/>
@@ -21675,8 +21851,12 @@
       <c r="J398" t="n">
         <v>0.4</v>
       </c>
-      <c r="K398" t="inlineStr"/>
-      <c r="L398" t="inlineStr"/>
+      <c r="K398" t="n">
+        <v>790</v>
+      </c>
+      <c r="L398" t="n">
+        <v>10.96</v>
+      </c>
       <c r="M398" t="inlineStr"/>
       <c r="N398" t="inlineStr"/>
       <c r="O398" t="inlineStr"/>
@@ -21725,8 +21905,12 @@
       <c r="J399" t="n">
         <v>0.78</v>
       </c>
-      <c r="K399" t="inlineStr"/>
-      <c r="L399" t="inlineStr"/>
+      <c r="K399" t="n">
+        <v>2575</v>
+      </c>
+      <c r="L399" t="n">
+        <v>7.74</v>
+      </c>
       <c r="M399" t="inlineStr"/>
       <c r="N399" t="inlineStr"/>
       <c r="O399" t="inlineStr"/>
@@ -21775,8 +21959,12 @@
       <c r="J400" t="n">
         <v>0.73</v>
       </c>
-      <c r="K400" t="inlineStr"/>
-      <c r="L400" t="inlineStr"/>
+      <c r="K400" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="L400" t="n">
+        <v>7.8</v>
+      </c>
       <c r="M400" t="inlineStr"/>
       <c r="N400" t="inlineStr"/>
       <c r="O400" t="inlineStr"/>
@@ -21825,8 +22013,12 @@
       <c r="J401" t="n">
         <v>0.64</v>
       </c>
-      <c r="K401" t="inlineStr"/>
-      <c r="L401" t="inlineStr"/>
+      <c r="K401" t="n">
+        <v>113</v>
+      </c>
+      <c r="L401" t="n">
+        <v>-1.31</v>
+      </c>
       <c r="M401" t="inlineStr"/>
       <c r="N401" t="inlineStr"/>
       <c r="O401" t="inlineStr"/>
@@ -21875,8 +22067,12 @@
       <c r="J402" t="n">
         <v>0.42</v>
       </c>
-      <c r="K402" t="inlineStr"/>
-      <c r="L402" t="inlineStr"/>
+      <c r="K402" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="L402" t="n">
+        <v>-8.99</v>
+      </c>
       <c r="M402" t="inlineStr"/>
       <c r="N402" t="inlineStr"/>
       <c r="O402" t="inlineStr"/>
@@ -21925,8 +22121,12 @@
       <c r="J403" t="n">
         <v>0.76</v>
       </c>
-      <c r="K403" t="inlineStr"/>
-      <c r="L403" t="inlineStr"/>
+      <c r="K403" t="n">
+        <v>104</v>
+      </c>
+      <c r="L403" t="n">
+        <v>-5.45</v>
+      </c>
       <c r="M403" t="inlineStr"/>
       <c r="N403" t="inlineStr"/>
       <c r="O403" t="inlineStr"/>
@@ -21975,8 +22175,12 @@
       <c r="J404" t="n">
         <v>0.59</v>
       </c>
-      <c r="K404" t="inlineStr"/>
-      <c r="L404" t="inlineStr"/>
+      <c r="K404" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="L404" t="n">
+        <v>1.94</v>
+      </c>
       <c r="M404" t="inlineStr"/>
       <c r="N404" t="inlineStr"/>
       <c r="O404" t="inlineStr"/>
@@ -22025,8 +22229,12 @@
       <c r="J405" t="n">
         <v>0.84</v>
       </c>
-      <c r="K405" t="inlineStr"/>
-      <c r="L405" t="inlineStr"/>
+      <c r="K405" t="n">
+        <v>41.9</v>
+      </c>
+      <c r="L405" t="n">
+        <v>-2.1</v>
+      </c>
       <c r="M405" t="inlineStr"/>
       <c r="N405" t="inlineStr"/>
       <c r="O405" t="inlineStr"/>
@@ -22075,8 +22283,12 @@
       <c r="J406" t="n">
         <v>0.67</v>
       </c>
-      <c r="K406" t="inlineStr"/>
-      <c r="L406" t="inlineStr"/>
+      <c r="K406" t="n">
+        <v>890</v>
+      </c>
+      <c r="L406" t="n">
+        <v>-6.12</v>
+      </c>
       <c r="M406" t="inlineStr"/>
       <c r="N406" t="inlineStr"/>
       <c r="O406" t="inlineStr"/>
@@ -22125,8 +22337,12 @@
       <c r="J407" t="n">
         <v>0.92</v>
       </c>
-      <c r="K407" t="inlineStr"/>
-      <c r="L407" t="inlineStr"/>
+      <c r="K407" t="n">
+        <v>557</v>
+      </c>
+      <c r="L407" t="n">
+        <v>14.26</v>
+      </c>
       <c r="M407" t="inlineStr"/>
       <c r="N407" t="inlineStr"/>
       <c r="O407" t="inlineStr"/>
@@ -22175,8 +22391,12 @@
       <c r="J408" t="n">
         <v>0.73</v>
       </c>
-      <c r="K408" t="inlineStr"/>
-      <c r="L408" t="inlineStr"/>
+      <c r="K408" t="n">
+        <v>169.5</v>
+      </c>
+      <c r="L408" t="n">
+        <v>3.04</v>
+      </c>
       <c r="M408" t="inlineStr"/>
       <c r="N408" t="inlineStr"/>
       <c r="O408" t="inlineStr"/>
@@ -22225,8 +22445,12 @@
       <c r="J409" t="n">
         <v>0.2</v>
       </c>
-      <c r="K409" t="inlineStr"/>
-      <c r="L409" t="inlineStr"/>
+      <c r="K409" t="n">
+        <v>38.9</v>
+      </c>
+      <c r="L409" t="n">
+        <v>-1.52</v>
+      </c>
       <c r="M409" t="inlineStr"/>
       <c r="N409" t="inlineStr"/>
       <c r="O409" t="inlineStr"/>
@@ -22275,8 +22499,12 @@
       <c r="J410" t="n">
         <v>0.82</v>
       </c>
-      <c r="K410" t="inlineStr"/>
-      <c r="L410" t="inlineStr"/>
+      <c r="K410" t="n">
+        <v>2075</v>
+      </c>
+      <c r="L410" t="n">
+        <v>-0.72</v>
+      </c>
       <c r="M410" t="inlineStr"/>
       <c r="N410" t="inlineStr"/>
       <c r="O410" t="inlineStr"/>
@@ -22325,8 +22553,12 @@
       <c r="J411" t="n">
         <v>0.75</v>
       </c>
-      <c r="K411" t="inlineStr"/>
-      <c r="L411" t="inlineStr"/>
+      <c r="K411" t="n">
+        <v>1550</v>
+      </c>
+      <c r="L411" t="n">
+        <v>14.81</v>
+      </c>
       <c r="M411" t="inlineStr"/>
       <c r="N411" t="inlineStr"/>
       <c r="O411" t="inlineStr"/>
@@ -22375,8 +22607,12 @@
       <c r="J412" t="n">
         <v>0.36</v>
       </c>
-      <c r="K412" t="inlineStr"/>
-      <c r="L412" t="inlineStr"/>
+      <c r="K412" t="n">
+        <v>88.3</v>
+      </c>
+      <c r="L412" t="n">
+        <v>-0.34</v>
+      </c>
       <c r="M412" t="inlineStr"/>
       <c r="N412" t="inlineStr"/>
       <c r="O412" t="inlineStr"/>
@@ -22425,8 +22661,12 @@
       <c r="J413" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="K413" t="inlineStr"/>
-      <c r="L413" t="inlineStr"/>
+      <c r="K413" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="L413" t="n">
+        <v>-10.82</v>
+      </c>
       <c r="M413" t="inlineStr"/>
       <c r="N413" t="inlineStr"/>
       <c r="O413" t="inlineStr"/>
@@ -22475,8 +22715,12 @@
       <c r="J414" t="n">
         <v>0.71</v>
       </c>
-      <c r="K414" t="inlineStr"/>
-      <c r="L414" t="inlineStr"/>
+      <c r="K414" t="n">
+        <v>54</v>
+      </c>
+      <c r="L414" t="n">
+        <v>-0.74</v>
+      </c>
       <c r="M414" t="inlineStr"/>
       <c r="N414" t="inlineStr"/>
       <c r="O414" t="inlineStr"/>
@@ -22525,8 +22769,12 @@
       <c r="J415" t="n">
         <v>0.49</v>
       </c>
-      <c r="K415" t="inlineStr"/>
-      <c r="L415" t="inlineStr"/>
+      <c r="K415" t="n">
+        <v>331</v>
+      </c>
+      <c r="L415" t="n">
+        <v>-1.19</v>
+      </c>
       <c r="M415" t="inlineStr"/>
       <c r="N415" t="inlineStr"/>
       <c r="O415" t="inlineStr"/>
@@ -22575,8 +22823,12 @@
       <c r="J416" t="n">
         <v>0.31</v>
       </c>
-      <c r="K416" t="inlineStr"/>
-      <c r="L416" t="inlineStr"/>
+      <c r="K416" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="L416" t="n">
+        <v>0.53</v>
+      </c>
       <c r="M416" t="inlineStr"/>
       <c r="N416" t="inlineStr"/>
       <c r="O416" t="inlineStr"/>
@@ -22625,8 +22877,12 @@
       <c r="J417" t="n">
         <v>0.36</v>
       </c>
-      <c r="K417" t="inlineStr"/>
-      <c r="L417" t="inlineStr"/>
+      <c r="K417" t="n">
+        <v>1475</v>
+      </c>
+      <c r="L417" t="n">
+        <v>2.43</v>
+      </c>
       <c r="M417" t="inlineStr"/>
       <c r="N417" t="inlineStr"/>
       <c r="O417" t="inlineStr"/>
@@ -22671,8 +22927,12 @@
       </c>
       <c r="I418" t="inlineStr"/>
       <c r="J418" t="inlineStr"/>
-      <c r="K418" t="inlineStr"/>
-      <c r="L418" t="inlineStr"/>
+      <c r="K418" t="n">
+        <v>68.5</v>
+      </c>
+      <c r="L418" t="n">
+        <v>-2.14</v>
+      </c>
       <c r="M418" t="inlineStr"/>
       <c r="N418" t="inlineStr"/>
       <c r="O418" t="inlineStr"/>
@@ -22717,8 +22977,12 @@
       </c>
       <c r="I419" t="inlineStr"/>
       <c r="J419" t="inlineStr"/>
-      <c r="K419" t="inlineStr"/>
-      <c r="L419" t="inlineStr"/>
+      <c r="K419" t="n">
+        <v>378</v>
+      </c>
+      <c r="L419" t="n">
+        <v>-4.3</v>
+      </c>
       <c r="M419" t="inlineStr"/>
       <c r="N419" t="inlineStr"/>
       <c r="O419" t="inlineStr"/>
@@ -22763,8 +23027,12 @@
       </c>
       <c r="I420" t="inlineStr"/>
       <c r="J420" t="inlineStr"/>
-      <c r="K420" t="inlineStr"/>
-      <c r="L420" t="inlineStr"/>
+      <c r="K420" t="n">
+        <v>22.65</v>
+      </c>
+      <c r="L420" t="n">
+        <v>-6.98</v>
+      </c>
       <c r="M420" t="inlineStr"/>
       <c r="N420" t="inlineStr"/>
       <c r="O420" t="inlineStr"/>
@@ -22809,8 +23077,12 @@
       </c>
       <c r="I421" t="inlineStr"/>
       <c r="J421" t="inlineStr"/>
-      <c r="K421" t="inlineStr"/>
-      <c r="L421" t="inlineStr"/>
+      <c r="K421" t="n">
+        <v>200.5</v>
+      </c>
+      <c r="L421" t="n">
+        <v>-7.6</v>
+      </c>
       <c r="M421" t="inlineStr"/>
       <c r="N421" t="inlineStr"/>
       <c r="O421" t="inlineStr"/>
@@ -28588,7 +28860,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -28597,16 +28869,16 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2300</v>
+        <v>970</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -28619,37 +28891,37 @@
         </is>
       </c>
       <c r="H5" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I5" t="n">
-        <v>24.6</v>
+        <v>21.8</v>
       </c>
       <c r="J5" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="K5" t="n">
-        <v>2095</v>
+        <v>1060</v>
       </c>
       <c r="L5" t="n">
-        <v>-8.91</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>3555</v>
+        <v>1550</v>
       </c>
       <c r="N5" t="n">
-        <v>54.57</v>
+        <v>59.79</v>
       </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>54.57</v>
+        <v>59.79</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -28667,7 +28939,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2165</v>
+        <v>2300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -28689,24 +28961,28 @@
         <v>0.66</v>
       </c>
       <c r="K6" t="n">
-        <v>3235</v>
+        <v>2095</v>
       </c>
       <c r="L6" t="n">
-        <v>49.42</v>
-      </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+        <v>-8.91</v>
+      </c>
+      <c r="M6" t="n">
+        <v>3555</v>
+      </c>
+      <c r="N6" t="n">
+        <v>54.57</v>
+      </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>49.42</v>
+        <v>54.57</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46234</v>
+        <v>46218</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -28724,7 +29000,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2320</v>
+        <v>2165</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -28746,10 +29022,10 @@
         <v>0.66</v>
       </c>
       <c r="K7" t="n">
-        <v>3425</v>
+        <v>3235</v>
       </c>
       <c r="L7" t="n">
-        <v>47.63</v>
+        <v>49.42</v>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -28758,7 +29034,7 @@
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>47.63</v>
+        <v>49.42</v>
       </c>
     </row>
     <row r="8">
@@ -28772,41 +29048,41 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>821</v>
+        <v>2320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="I8" t="n">
-        <v>38.8</v>
+        <v>24.6</v>
       </c>
       <c r="J8" t="n">
-        <v>1.03</v>
+        <v>0.66</v>
       </c>
       <c r="K8" t="n">
-        <v>1180</v>
+        <v>3425</v>
       </c>
       <c r="L8" t="n">
-        <v>43.73</v>
+        <v>47.63</v>
       </c>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
@@ -28815,12 +29091,12 @@
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>43.73</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46234</v>
+        <v>46210</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -28829,16 +29105,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>902</v>
+        <v>2450</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -28851,33 +29127,37 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I9" t="n">
-        <v>21.8</v>
+        <v>24.6</v>
       </c>
       <c r="J9" t="n">
-        <v>0.75</v>
+        <v>0.66</v>
       </c>
       <c r="K9" t="n">
-        <v>1250</v>
+        <v>2940</v>
       </c>
       <c r="L9" t="n">
-        <v>38.58</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="M9" t="n">
+        <v>3585</v>
+      </c>
+      <c r="N9" t="n">
+        <v>46.33</v>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>38.58</v>
+        <v>46.33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46252</v>
+        <v>46234</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -28886,41 +29166,41 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1005</v>
+        <v>821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I10" t="n">
-        <v>21.8</v>
+        <v>38.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0.75</v>
+        <v>1.03</v>
       </c>
       <c r="K10" t="n">
-        <v>1385</v>
+        <v>1180</v>
       </c>
       <c r="L10" t="n">
-        <v>37.81</v>
+        <v>43.73</v>
       </c>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
@@ -28929,12 +29209,12 @@
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>37.81</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46244</v>
+        <v>46234</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -28952,7 +29232,7 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1010</v>
+        <v>902</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -28974,10 +29254,10 @@
         <v>0.75</v>
       </c>
       <c r="K11" t="n">
-        <v>1385</v>
+        <v>1250</v>
       </c>
       <c r="L11" t="n">
-        <v>37.13</v>
+        <v>38.58</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -28986,12 +29266,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>37.13</v>
+        <v>38.58</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46234</v>
+        <v>46252</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -29000,16 +29280,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>131</v>
+        <v>1005</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -29022,19 +29302,19 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I12" t="n">
-        <v>14.1</v>
+        <v>21.8</v>
       </c>
       <c r="J12" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="K12" t="n">
-        <v>179.5</v>
+        <v>1385</v>
       </c>
       <c r="L12" t="n">
-        <v>37.02</v>
+        <v>37.81</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -29043,12 +29323,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>37.02</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -29057,16 +29337,16 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>369</v>
+        <v>1010</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -29079,19 +29359,19 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I13" t="n">
-        <v>21.2</v>
+        <v>21.8</v>
       </c>
       <c r="J13" t="n">
-        <v>0.92</v>
+        <v>0.75</v>
       </c>
       <c r="K13" t="n">
-        <v>496.5</v>
+        <v>1385</v>
       </c>
       <c r="L13" t="n">
-        <v>34.55</v>
+        <v>37.13</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -29100,12 +29380,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>34.55</v>
+        <v>37.13</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46210</v>
+        <v>46234</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -29114,37 +29394,41 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>185.5</v>
+        <v>131</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>69</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="I14" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0.73</v>
+      </c>
       <c r="K14" t="n">
-        <v>247</v>
+        <v>179.5</v>
       </c>
       <c r="L14" t="n">
-        <v>33.15</v>
+        <v>37.02</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -29153,12 +29437,12 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>33.15</v>
+        <v>37.02</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46218</v>
+        <v>46234</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -29167,16 +29451,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>145.5</v>
+        <v>369</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -29185,23 +29469,23 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="I15" t="n">
-        <v>10</v>
+        <v>21.2</v>
       </c>
       <c r="J15" t="n">
-        <v>0.31</v>
+        <v>0.92</v>
       </c>
       <c r="K15" t="n">
-        <v>193.5</v>
+        <v>496.5</v>
       </c>
       <c r="L15" t="n">
-        <v>32.99</v>
+        <v>34.55</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -29210,12 +29494,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>32.99</v>
+        <v>34.55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -29224,16 +29508,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5115</v>
+        <v>145.5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -29242,23 +29526,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I16" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="K16" t="n">
-        <v>6620</v>
+        <v>193.5</v>
       </c>
       <c r="L16" t="n">
-        <v>29.42</v>
+        <v>32.99</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -29267,12 +29551,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>29.42</v>
+        <v>32.99</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -29281,20 +29565,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>181.5</v>
+        <v>5115</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -29303,15 +29587,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>69</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="I17" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.26</v>
+      </c>
       <c r="K17" t="n">
-        <v>233</v>
+        <v>6620</v>
       </c>
       <c r="L17" t="n">
-        <v>28.37</v>
+        <v>29.42</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -29320,12 +29608,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>28.37</v>
+        <v>29.42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46205</v>
+        <v>46218</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -29334,16 +29622,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>8271</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>宇瞻</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>407</v>
+        <v>181.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -29352,37 +29640,33 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="n">
-        <v>396.5</v>
+        <v>233</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.58</v>
-      </c>
-      <c r="M18" t="n">
-        <v>519</v>
-      </c>
-      <c r="N18" t="n">
-        <v>27.52</v>
-      </c>
+        <v>28.37</v>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>27.52</v>
+        <v>28.37</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46244</v>
+        <v>46205</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -29391,55 +29675,55 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>401.5</v>
+        <v>407</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>90</v>
-      </c>
-      <c r="I19" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.92</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
-        <v>509</v>
+        <v>396.5</v>
       </c>
       <c r="L19" t="n">
-        <v>26.77</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+        <v>-2.58</v>
+      </c>
+      <c r="M19" t="n">
+        <v>519</v>
+      </c>
+      <c r="N19" t="n">
+        <v>27.52</v>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>26.77</v>
+        <v>27.52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46211</v>
+        <v>46244</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -29448,16 +29732,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5050</v>
+        <v>401.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -29466,23 +29750,23 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="I20" t="n">
-        <v>9.6</v>
+        <v>21.2</v>
       </c>
       <c r="J20" t="n">
-        <v>0.26</v>
+        <v>0.92</v>
       </c>
       <c r="K20" t="n">
-        <v>6265</v>
+        <v>509</v>
       </c>
       <c r="L20" t="n">
-        <v>24.06</v>
+        <v>26.77</v>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
@@ -29491,12 +29775,12 @@
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>24.06</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46202</v>
+        <v>46211</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -29505,16 +29789,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>97.40000000000001</v>
+        <v>5050</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -29523,36 +29807,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>97</v>
+        <v>65</v>
       </c>
       <c r="I21" t="n">
-        <v>12.4</v>
+        <v>9.6</v>
       </c>
       <c r="J21" t="n">
-        <v>0.73</v>
+        <v>0.26</v>
       </c>
       <c r="K21" t="n">
-        <v>99.3</v>
+        <v>6265</v>
       </c>
       <c r="L21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M21" t="n">
-        <v>120</v>
-      </c>
-      <c r="N21" t="n">
-        <v>23.2</v>
-      </c>
+        <v>24.06</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>23.2</v>
+        <v>24.06</v>
       </c>
     </row>
   </sheetData>
@@ -30010,7 +30290,7 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -30019,16 +30299,16 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>34.2</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -30037,41 +30317,41 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H8" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="I8" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="J8" t="n">
-        <v>0.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K8" t="n">
-        <v>27.65</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>-19.15</v>
+        <v>-0.66</v>
       </c>
       <c r="M8" t="n">
-        <v>25.05</v>
+        <v>54.4</v>
       </c>
       <c r="N8" t="n">
-        <v>-26.75</v>
+        <v>-27.85</v>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>-26.75</v>
+        <v>-27.85</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46251</v>
+        <v>46210</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -30080,46 +30360,54 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>47.15</v>
+        <v>34.15</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>75</v>
-      </c>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="I9" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.42</v>
+      </c>
       <c r="K9" t="n">
-        <v>34.8</v>
+        <v>27.75</v>
       </c>
       <c r="L9" t="n">
-        <v>-26.19</v>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+        <v>-18.74</v>
+      </c>
+      <c r="M9" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-27.38</v>
+      </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>-26.19</v>
+        <v>-27.38</v>
       </c>
     </row>
     <row r="10">
@@ -30133,16 +30421,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1215</v>
+        <v>34.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -30155,37 +30443,37 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I10" t="n">
-        <v>25</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
-        <v>0.67</v>
+        <v>0.42</v>
       </c>
       <c r="K10" t="n">
-        <v>981</v>
+        <v>27.65</v>
       </c>
       <c r="L10" t="n">
-        <v>-19.26</v>
+        <v>-19.15</v>
       </c>
       <c r="M10" t="n">
-        <v>897</v>
+        <v>25.05</v>
       </c>
       <c r="N10" t="n">
-        <v>-26.17</v>
+        <v>-26.75</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>-26.17</v>
+        <v>-26.75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46202</v>
+        <v>46251</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -30194,20 +30482,20 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>71.7</v>
+        <v>47.15</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -30216,32 +30504,24 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>78</v>
-      </c>
-      <c r="I11" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J11" t="n">
-        <v>0.5600000000000001</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="n">
-        <v>70.7</v>
+        <v>34.8</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.39</v>
-      </c>
-      <c r="M11" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="N11" t="n">
-        <v>-21.62</v>
-      </c>
+        <v>-26.19</v>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-21.62</v>
+        <v>-26.19</v>
       </c>
     </row>
     <row r="12">
@@ -30255,16 +30535,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>955</v>
+        <v>1215</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -30277,37 +30557,37 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
-        <v>14.2</v>
+        <v>25</v>
       </c>
       <c r="J12" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="K12" t="n">
-        <v>671</v>
+        <v>981</v>
       </c>
       <c r="L12" t="n">
-        <v>-29.74</v>
+        <v>-19.26</v>
       </c>
       <c r="M12" t="n">
-        <v>753</v>
+        <v>897</v>
       </c>
       <c r="N12" t="n">
-        <v>-21.15</v>
+        <v>-26.17</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-21.15</v>
+        <v>-26.17</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -30316,55 +30596,59 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>158</v>
+        <v>1175</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>77</v>
+        <v>90</v>
       </c>
       <c r="I13" t="n">
-        <v>16.4</v>
+        <v>25</v>
       </c>
       <c r="J13" t="n">
-        <v>1.11</v>
+        <v>0.67</v>
       </c>
       <c r="K13" t="n">
-        <v>125.5</v>
+        <v>1235</v>
       </c>
       <c r="L13" t="n">
-        <v>-20.57</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+        <v>5.11</v>
+      </c>
+      <c r="M13" t="n">
+        <v>890</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-24.26</v>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-20.57</v>
+        <v>-24.26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46244</v>
+        <v>46202</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -30382,7 +30666,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>66.7</v>
+        <v>71.7</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -30404,24 +30688,28 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>53.9</v>
+        <v>70.7</v>
       </c>
       <c r="L14" t="n">
-        <v>-19.19</v>
-      </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+        <v>-1.39</v>
+      </c>
+      <c r="M14" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-21.62</v>
+      </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-19.19</v>
+        <v>-21.62</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46252</v>
+        <v>46202</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -30430,16 +30718,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2225</v>
+        <v>955</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -30452,33 +30740,37 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I15" t="n">
-        <v>30.7</v>
+        <v>14.2</v>
       </c>
       <c r="J15" t="n">
-        <v>0.82</v>
+        <v>0.4</v>
       </c>
       <c r="K15" t="n">
-        <v>1800</v>
+        <v>671</v>
       </c>
       <c r="L15" t="n">
-        <v>-19.1</v>
-      </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+        <v>-29.74</v>
+      </c>
+      <c r="M15" t="n">
+        <v>753</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-21.15</v>
+      </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-19.1</v>
+        <v>-21.15</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -30487,20 +30779,20 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>2382</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>廣達</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>373</v>
+        <v>158</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -30509,19 +30801,19 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="I16" t="n">
-        <v>13.2</v>
+        <v>16.4</v>
       </c>
       <c r="J16" t="n">
-        <v>0.49</v>
+        <v>1.11</v>
       </c>
       <c r="K16" t="n">
-        <v>302</v>
+        <v>125.5</v>
       </c>
       <c r="L16" t="n">
-        <v>-19.03</v>
+        <v>-20.57</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -30530,12 +30822,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-19.03</v>
+        <v>-20.57</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46202</v>
+        <v>46244</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -30544,16 +30836,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>2340</v>
+        <v>66.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -30562,41 +30854,37 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I17" t="n">
-        <v>30.7</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
-        <v>0.82</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>1910</v>
+        <v>53.9</v>
       </c>
       <c r="L17" t="n">
-        <v>-18.38</v>
-      </c>
-      <c r="M17" t="n">
-        <v>1895</v>
-      </c>
-      <c r="N17" t="n">
-        <v>-19.02</v>
-      </c>
+        <v>-19.19</v>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-19.02</v>
+        <v>-19.19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46210</v>
+        <v>46252</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -30605,16 +30893,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>34.15</v>
+        <v>2225</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -30627,19 +30915,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>94</v>
+        <v>80</v>
       </c>
       <c r="I18" t="n">
-        <v>5.9</v>
+        <v>30.7</v>
       </c>
       <c r="J18" t="n">
-        <v>0.42</v>
+        <v>0.82</v>
       </c>
       <c r="K18" t="n">
-        <v>27.75</v>
+        <v>1800</v>
       </c>
       <c r="L18" t="n">
-        <v>-18.74</v>
+        <v>-19.1</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -30648,12 +30936,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-18.74</v>
+        <v>-19.1</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46226</v>
+        <v>46202</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -30662,55 +30950,59 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1190</v>
+        <v>2340</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I19" t="n">
-        <v>38.8</v>
+        <v>30.7</v>
       </c>
       <c r="J19" t="n">
-        <v>1.03</v>
+        <v>0.82</v>
       </c>
       <c r="K19" t="n">
-        <v>967</v>
+        <v>1910</v>
       </c>
       <c r="L19" t="n">
-        <v>-18.74</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+        <v>-18.38</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-19.02</v>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-18.74</v>
+        <v>-19.02</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46202</v>
+        <v>46226</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -30719,20 +31011,20 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>65.5</v>
+        <v>1190</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -30741,37 +31033,33 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I20" t="n">
-        <v>10.4</v>
+        <v>38.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="K20" t="n">
-        <v>51.7</v>
+        <v>967</v>
       </c>
       <c r="L20" t="n">
-        <v>-21.07</v>
-      </c>
-      <c r="M20" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-18.63</v>
-      </c>
+        <v>-18.74</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-18.63</v>
+        <v>-18.74</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46226</v>
+        <v>46202</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -30780,16 +31068,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>4933</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>友輝</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1180</v>
+        <v>65.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -30798,32 +31086,36 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>90</v>
+        <v>77</v>
       </c>
       <c r="I21" t="n">
-        <v>25</v>
+        <v>10.4</v>
       </c>
       <c r="J21" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="K21" t="n">
-        <v>967</v>
+        <v>51.7</v>
       </c>
       <c r="L21" t="n">
-        <v>-18.05</v>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+        <v>-21.07</v>
+      </c>
+      <c r="M21" t="n">
+        <v>53.3</v>
+      </c>
+      <c r="N21" t="n">
+        <v>-18.63</v>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-18.05</v>
+        <v>-18.63</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -493,22 +493,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C3" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="D3" t="n">
-        <v>0.58</v>
+        <v>-0.18</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.4</v>
+        <v>-4.47</v>
       </c>
       <c r="F3" t="n">
         <v>82.70999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-54.37</v>
+        <v>-54.65</v>
       </c>
     </row>
     <row r="4">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D3" t="n">
-        <v>37.5</v>
+        <v>37</v>
       </c>
       <c r="E3" t="n">
-        <v>0.58</v>
+        <v>-0.18</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R532"/>
+  <dimension ref="A1:R533"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9769,8 +9769,12 @@
       <c r="L172" t="n">
         <v>24.06</v>
       </c>
-      <c r="M172" t="inlineStr"/>
-      <c r="N172" t="inlineStr"/>
+      <c r="M172" t="n">
+        <v>2290</v>
+      </c>
+      <c r="N172" t="n">
+        <v>-54.65</v>
+      </c>
       <c r="O172" t="inlineStr"/>
       <c r="P172" t="inlineStr"/>
       <c r="Q172" t="inlineStr"/>
@@ -28571,6 +28575,52 @@
       <c r="P532" t="inlineStr"/>
       <c r="Q532" t="inlineStr"/>
       <c r="R532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>信立</t>
+        </is>
+      </c>
+      <c r="E533" t="n">
+        <v>31.2</v>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G533" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H533" t="n">
+        <v>75</v>
+      </c>
+      <c r="I533" t="inlineStr"/>
+      <c r="J533" t="inlineStr"/>
+      <c r="K533" t="inlineStr"/>
+      <c r="L533" t="inlineStr"/>
+      <c r="M533" t="inlineStr"/>
+      <c r="N533" t="inlineStr"/>
+      <c r="O533" t="inlineStr"/>
+      <c r="P533" t="inlineStr"/>
+      <c r="Q533" t="inlineStr"/>
+      <c r="R533" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -29780,7 +29830,7 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46211</v>
+        <v>46202</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -29789,16 +29839,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3029</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>零壹</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5050</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -29807,32 +29857,36 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>65</v>
+        <v>97</v>
       </c>
       <c r="I21" t="n">
-        <v>9.6</v>
+        <v>12.4</v>
       </c>
       <c r="J21" t="n">
-        <v>0.26</v>
+        <v>0.73</v>
       </c>
       <c r="K21" t="n">
-        <v>6265</v>
+        <v>99.3</v>
       </c>
       <c r="L21" t="n">
-        <v>24.06</v>
-      </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
+        <v>1.95</v>
+      </c>
+      <c r="M21" t="n">
+        <v>120</v>
+      </c>
+      <c r="N21" t="n">
+        <v>23.2</v>
+      </c>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>24.06</v>
+        <v>23.2</v>
       </c>
     </row>
   </sheetData>
@@ -30176,7 +30230,7 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46203</v>
+        <v>46211</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -30194,7 +30248,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4635</v>
+        <v>5050</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -30216,28 +30270,28 @@
         <v>0.26</v>
       </c>
       <c r="K6" t="n">
-        <v>4900</v>
+        <v>6265</v>
       </c>
       <c r="L6" t="n">
-        <v>5.72</v>
+        <v>24.06</v>
       </c>
       <c r="M6" t="n">
-        <v>2115</v>
+        <v>2290</v>
       </c>
       <c r="N6" t="n">
-        <v>-54.37</v>
+        <v>-54.65</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>-54.37</v>
+        <v>-54.65</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46259</v>
+        <v>46203</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -30246,20 +30300,20 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>53.2</v>
+        <v>4635</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -30268,29 +30322,37 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>75</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="I7" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.26</v>
+      </c>
       <c r="K7" t="n">
-        <v>34.05</v>
+        <v>4900</v>
       </c>
       <c r="L7" t="n">
-        <v>-36</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+        <v>5.72</v>
+      </c>
+      <c r="M7" t="n">
+        <v>2115</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-54.37</v>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>-36</v>
+        <v>-54.37</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46210</v>
+        <v>46259</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -30299,20 +30361,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>75.40000000000001</v>
+        <v>53.2</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -30321,32 +30383,24 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>78</v>
-      </c>
-      <c r="I8" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0.5600000000000001</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="n">
-        <v>74.90000000000001</v>
+        <v>34.05</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="M8" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="N8" t="n">
-        <v>-27.85</v>
-      </c>
+        <v>-36</v>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>-27.85</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="9">
@@ -30360,16 +30414,16 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>34.15</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -30378,41 +30432,41 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="I9" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="J9" t="n">
-        <v>0.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>27.75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>-18.74</v>
+        <v>-0.66</v>
       </c>
       <c r="M9" t="n">
-        <v>24.8</v>
+        <v>54.4</v>
       </c>
       <c r="N9" t="n">
-        <v>-27.38</v>
+        <v>-27.85</v>
       </c>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>-27.38</v>
+        <v>-27.85</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -30430,7 +30484,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>34.2</v>
+        <v>34.15</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -30452,28 +30506,28 @@
         <v>0.42</v>
       </c>
       <c r="K10" t="n">
-        <v>27.65</v>
+        <v>27.75</v>
       </c>
       <c r="L10" t="n">
-        <v>-19.15</v>
+        <v>-18.74</v>
       </c>
       <c r="M10" t="n">
-        <v>25.05</v>
+        <v>24.8</v>
       </c>
       <c r="N10" t="n">
-        <v>-26.75</v>
+        <v>-27.38</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>-26.75</v>
+        <v>-27.38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46251</v>
+        <v>46202</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -30482,51 +30536,59 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>47.15</v>
+        <v>34.2</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>75</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="I11" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.42</v>
+      </c>
       <c r="K11" t="n">
-        <v>34.8</v>
+        <v>27.65</v>
       </c>
       <c r="L11" t="n">
-        <v>-26.19</v>
-      </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+        <v>-19.15</v>
+      </c>
+      <c r="M11" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-26.75</v>
+      </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-26.19</v>
+        <v>-26.75</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46202</v>
+        <v>46251</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -30535,59 +30597,51 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1215</v>
+        <v>47.15</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>90</v>
-      </c>
-      <c r="I12" t="n">
-        <v>25</v>
-      </c>
-      <c r="J12" t="n">
-        <v>0.67</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>981</v>
+        <v>34.8</v>
       </c>
       <c r="L12" t="n">
-        <v>-19.26</v>
-      </c>
-      <c r="M12" t="n">
-        <v>897</v>
-      </c>
-      <c r="N12" t="n">
-        <v>-26.17</v>
-      </c>
+        <v>-26.19</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-26.17</v>
+        <v>-26.19</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -30605,7 +30659,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1175</v>
+        <v>1215</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -30627,28 +30681,28 @@
         <v>0.67</v>
       </c>
       <c r="K13" t="n">
-        <v>1235</v>
+        <v>981</v>
       </c>
       <c r="L13" t="n">
-        <v>5.11</v>
+        <v>-19.26</v>
       </c>
       <c r="M13" t="n">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="N13" t="n">
-        <v>-24.26</v>
+        <v>-26.17</v>
       </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-24.26</v>
+        <v>-26.17</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -30657,16 +30711,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>71.7</v>
+        <v>1175</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -30675,36 +30729,36 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I14" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="J14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="K14" t="n">
-        <v>70.7</v>
+        <v>1235</v>
       </c>
       <c r="L14" t="n">
-        <v>-1.39</v>
+        <v>5.11</v>
       </c>
       <c r="M14" t="n">
-        <v>56.2</v>
+        <v>890</v>
       </c>
       <c r="N14" t="n">
-        <v>-21.62</v>
+        <v>-24.26</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-21.62</v>
+        <v>-24.26</v>
       </c>
     </row>
     <row r="15">
@@ -30718,16 +30772,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>955</v>
+        <v>71.7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -30736,41 +30790,41 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="I15" t="n">
-        <v>14.2</v>
+        <v>6.8</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>671</v>
+        <v>70.7</v>
       </c>
       <c r="L15" t="n">
-        <v>-29.74</v>
+        <v>-1.39</v>
       </c>
       <c r="M15" t="n">
-        <v>753</v>
+        <v>56.2</v>
       </c>
       <c r="N15" t="n">
-        <v>-21.15</v>
+        <v>-21.62</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-21.15</v>
+        <v>-21.62</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -30779,55 +30833,59 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>158</v>
+        <v>955</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>77</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>16.4</v>
+        <v>14.2</v>
       </c>
       <c r="J16" t="n">
-        <v>1.11</v>
+        <v>0.4</v>
       </c>
       <c r="K16" t="n">
-        <v>125.5</v>
+        <v>671</v>
       </c>
       <c r="L16" t="n">
-        <v>-20.57</v>
-      </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+        <v>-29.74</v>
+      </c>
+      <c r="M16" t="n">
+        <v>753</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-21.15</v>
+      </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-20.57</v>
+        <v>-21.15</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46244</v>
+        <v>46218</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -30836,20 +30894,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>3402</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>66.7</v>
+        <v>158</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -30858,19 +30916,19 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>16.4</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.11</v>
       </c>
       <c r="K17" t="n">
-        <v>53.9</v>
+        <v>125.5</v>
       </c>
       <c r="L17" t="n">
-        <v>-19.19</v>
+        <v>-20.57</v>
       </c>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
@@ -30879,12 +30937,12 @@
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-19.19</v>
+        <v>-20.57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46252</v>
+        <v>46244</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -30893,16 +30951,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2225</v>
+        <v>66.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -30911,23 +30969,23 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I18" t="n">
-        <v>30.7</v>
+        <v>6.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.82</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>1800</v>
+        <v>53.9</v>
       </c>
       <c r="L18" t="n">
-        <v>-19.1</v>
+        <v>-19.19</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -30936,12 +30994,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-19.1</v>
+        <v>-19.19</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46202</v>
+        <v>46252</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -30959,7 +31017,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2340</v>
+        <v>2225</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -30981,28 +31039,24 @@
         <v>0.82</v>
       </c>
       <c r="K19" t="n">
-        <v>1910</v>
+        <v>1800</v>
       </c>
       <c r="L19" t="n">
-        <v>-18.38</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1895</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-19.02</v>
-      </c>
+        <v>-19.1</v>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-19.02</v>
+        <v>-19.1</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46226</v>
+        <v>46202</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -31011,55 +31065,59 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1190</v>
+        <v>2340</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I20" t="n">
-        <v>38.8</v>
+        <v>30.7</v>
       </c>
       <c r="J20" t="n">
-        <v>1.03</v>
+        <v>0.82</v>
       </c>
       <c r="K20" t="n">
-        <v>967</v>
+        <v>1910</v>
       </c>
       <c r="L20" t="n">
-        <v>-18.74</v>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+        <v>-18.38</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1895</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-19.02</v>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-18.74</v>
+        <v>-19.02</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46202</v>
+        <v>46226</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -31068,20 +31126,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4933</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>友輝</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>65.5</v>
+        <v>1190</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -31090,32 +31148,28 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I21" t="n">
-        <v>10.4</v>
+        <v>38.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0.71</v>
+        <v>1.03</v>
       </c>
       <c r="K21" t="n">
-        <v>51.7</v>
+        <v>967</v>
       </c>
       <c r="L21" t="n">
-        <v>-21.07</v>
-      </c>
-      <c r="M21" t="n">
-        <v>53.3</v>
-      </c>
-      <c r="N21" t="n">
-        <v>-18.63</v>
-      </c>
+        <v>-18.74</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-18.63</v>
+        <v>-18.74</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C2" t="n">
         <v>43.5</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.63</v>
+        <v>-0.65</v>
       </c>
       <c r="E2" t="n">
         <v>-1.2</v>
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D2" t="n">
         <v>43.5</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.63</v>
+        <v>-0.65</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R533"/>
+  <dimension ref="A1:R539"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23135,8 +23135,12 @@
       <c r="J422" t="n">
         <v>0.26</v>
       </c>
-      <c r="K422" t="inlineStr"/>
-      <c r="L422" t="inlineStr"/>
+      <c r="K422" t="n">
+        <v>2240</v>
+      </c>
+      <c r="L422" t="n">
+        <v>-10.04</v>
+      </c>
       <c r="M422" t="inlineStr"/>
       <c r="N422" t="inlineStr"/>
       <c r="O422" t="inlineStr"/>
@@ -23181,8 +23185,12 @@
       </c>
       <c r="I423" t="inlineStr"/>
       <c r="J423" t="inlineStr"/>
-      <c r="K423" t="inlineStr"/>
-      <c r="L423" t="inlineStr"/>
+      <c r="K423" t="n">
+        <v>49.4</v>
+      </c>
+      <c r="L423" t="n">
+        <v>3.89</v>
+      </c>
       <c r="M423" t="inlineStr"/>
       <c r="N423" t="inlineStr"/>
       <c r="O423" t="inlineStr"/>
@@ -28621,6 +28629,306 @@
       <c r="P533" t="inlineStr"/>
       <c r="Q533" t="inlineStr"/>
       <c r="R533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>大車隊</t>
+        </is>
+      </c>
+      <c r="E534" t="n">
+        <v>155</v>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G534" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H534" t="n">
+        <v>97</v>
+      </c>
+      <c r="I534" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J534" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K534" t="inlineStr"/>
+      <c r="L534" t="inlineStr"/>
+      <c r="M534" t="inlineStr"/>
+      <c r="N534" t="inlineStr"/>
+      <c r="O534" t="inlineStr"/>
+      <c r="P534" t="inlineStr"/>
+      <c r="Q534" t="inlineStr"/>
+      <c r="R534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>崇友</t>
+        </is>
+      </c>
+      <c r="E535" t="n">
+        <v>118</v>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G535" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H535" t="n">
+        <v>91</v>
+      </c>
+      <c r="I535" t="n">
+        <v>15</v>
+      </c>
+      <c r="J535" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K535" t="inlineStr"/>
+      <c r="L535" t="inlineStr"/>
+      <c r="M535" t="inlineStr"/>
+      <c r="N535" t="inlineStr"/>
+      <c r="O535" t="inlineStr"/>
+      <c r="P535" t="inlineStr"/>
+      <c r="Q535" t="inlineStr"/>
+      <c r="R535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>零壹</t>
+        </is>
+      </c>
+      <c r="E536" t="n">
+        <v>115.5</v>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G536" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H536" t="n">
+        <v>97</v>
+      </c>
+      <c r="I536" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J536" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K536" t="inlineStr"/>
+      <c r="L536" t="inlineStr"/>
+      <c r="M536" t="inlineStr"/>
+      <c r="N536" t="inlineStr"/>
+      <c r="O536" t="inlineStr"/>
+      <c r="P536" t="inlineStr"/>
+      <c r="Q536" t="inlineStr"/>
+      <c r="R536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="E537" t="n">
+        <v>118</v>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G537" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H537" t="n">
+        <v>94</v>
+      </c>
+      <c r="I537" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J537" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K537" t="inlineStr"/>
+      <c r="L537" t="inlineStr"/>
+      <c r="M537" t="inlineStr"/>
+      <c r="N537" t="inlineStr"/>
+      <c r="O537" t="inlineStr"/>
+      <c r="P537" t="inlineStr"/>
+      <c r="Q537" t="inlineStr"/>
+      <c r="R537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>隆大</t>
+        </is>
+      </c>
+      <c r="E538" t="n">
+        <v>24.8</v>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G538" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H538" t="n">
+        <v>94</v>
+      </c>
+      <c r="I538" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J538" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K538" t="inlineStr"/>
+      <c r="L538" t="inlineStr"/>
+      <c r="M538" t="inlineStr"/>
+      <c r="N538" t="inlineStr"/>
+      <c r="O538" t="inlineStr"/>
+      <c r="P538" t="inlineStr"/>
+      <c r="Q538" t="inlineStr"/>
+      <c r="R538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>東科-KY</t>
+        </is>
+      </c>
+      <c r="E539" t="n">
+        <v>53.2</v>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G539" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H539" t="n">
+        <v>78</v>
+      </c>
+      <c r="I539" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J539" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K539" t="inlineStr"/>
+      <c r="L539" t="inlineStr"/>
+      <c r="M539" t="inlineStr"/>
+      <c r="N539" t="inlineStr"/>
+      <c r="O539" t="inlineStr"/>
+      <c r="P539" t="inlineStr"/>
+      <c r="Q539" t="inlineStr"/>
+      <c r="R539" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R539"/>
+  <dimension ref="A1:R567"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -28929,6 +28929,1390 @@
       <c r="P539" t="inlineStr"/>
       <c r="Q539" t="inlineStr"/>
       <c r="R539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+      <c r="E540" t="n">
+        <v>596</v>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G540" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H540" t="n">
+        <v>96</v>
+      </c>
+      <c r="I540" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J540" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K540" t="inlineStr"/>
+      <c r="L540" t="inlineStr"/>
+      <c r="M540" t="inlineStr"/>
+      <c r="N540" t="inlineStr"/>
+      <c r="O540" t="inlineStr"/>
+      <c r="P540" t="inlineStr"/>
+      <c r="Q540" t="inlineStr"/>
+      <c r="R540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+      <c r="E541" t="n">
+        <v>381.5</v>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G541" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H541" t="n">
+        <v>90</v>
+      </c>
+      <c r="I541" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J541" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K541" t="inlineStr"/>
+      <c r="L541" t="inlineStr"/>
+      <c r="M541" t="inlineStr"/>
+      <c r="N541" t="inlineStr"/>
+      <c r="O541" t="inlineStr"/>
+      <c r="P541" t="inlineStr"/>
+      <c r="Q541" t="inlineStr"/>
+      <c r="R541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+      <c r="E542" t="n">
+        <v>83.7</v>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G542" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H542" t="n">
+        <v>87</v>
+      </c>
+      <c r="I542" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J542" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K542" t="inlineStr"/>
+      <c r="L542" t="inlineStr"/>
+      <c r="M542" t="inlineStr"/>
+      <c r="N542" t="inlineStr"/>
+      <c r="O542" t="inlineStr"/>
+      <c r="P542" t="inlineStr"/>
+      <c r="Q542" t="inlineStr"/>
+      <c r="R542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>漢科</t>
+        </is>
+      </c>
+      <c r="E543" t="n">
+        <v>139.5</v>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G543" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H543" t="n">
+        <v>77</v>
+      </c>
+      <c r="I543" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J543" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K543" t="inlineStr"/>
+      <c r="L543" t="inlineStr"/>
+      <c r="M543" t="inlineStr"/>
+      <c r="N543" t="inlineStr"/>
+      <c r="O543" t="inlineStr"/>
+      <c r="P543" t="inlineStr"/>
+      <c r="Q543" t="inlineStr"/>
+      <c r="R543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="E544" t="n">
+        <v>249</v>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G544" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H544" t="n">
+        <v>77</v>
+      </c>
+      <c r="I544" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J544" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K544" t="inlineStr"/>
+      <c r="L544" t="inlineStr"/>
+      <c r="M544" t="inlineStr"/>
+      <c r="N544" t="inlineStr"/>
+      <c r="O544" t="inlineStr"/>
+      <c r="P544" t="inlineStr"/>
+      <c r="Q544" t="inlineStr"/>
+      <c r="R544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="E545" t="n">
+        <v>1080</v>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G545" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H545" t="n">
+        <v>76</v>
+      </c>
+      <c r="I545" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J545" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K545" t="inlineStr"/>
+      <c r="L545" t="inlineStr"/>
+      <c r="M545" t="inlineStr"/>
+      <c r="N545" t="inlineStr"/>
+      <c r="O545" t="inlineStr"/>
+      <c r="P545" t="inlineStr"/>
+      <c r="Q545" t="inlineStr"/>
+      <c r="R545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="E546" t="n">
+        <v>57.5</v>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G546" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H546" t="n">
+        <v>68</v>
+      </c>
+      <c r="I546" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J546" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K546" t="inlineStr"/>
+      <c r="L546" t="inlineStr"/>
+      <c r="M546" t="inlineStr"/>
+      <c r="N546" t="inlineStr"/>
+      <c r="O546" t="inlineStr"/>
+      <c r="P546" t="inlineStr"/>
+      <c r="Q546" t="inlineStr"/>
+      <c r="R546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="E547" t="n">
+        <v>3440</v>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G547" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H547" t="n">
+        <v>100</v>
+      </c>
+      <c r="I547" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J547" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K547" t="inlineStr"/>
+      <c r="L547" t="inlineStr"/>
+      <c r="M547" t="inlineStr"/>
+      <c r="N547" t="inlineStr"/>
+      <c r="O547" t="inlineStr"/>
+      <c r="P547" t="inlineStr"/>
+      <c r="Q547" t="inlineStr"/>
+      <c r="R547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="E548" t="n">
+        <v>778</v>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G548" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H548" t="n">
+        <v>100</v>
+      </c>
+      <c r="I548" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J548" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K548" t="inlineStr"/>
+      <c r="L548" t="inlineStr"/>
+      <c r="M548" t="inlineStr"/>
+      <c r="N548" t="inlineStr"/>
+      <c r="O548" t="inlineStr"/>
+      <c r="P548" t="inlineStr"/>
+      <c r="Q548" t="inlineStr"/>
+      <c r="R548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E549" t="n">
+        <v>2550</v>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G549" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H549" t="n">
+        <v>100</v>
+      </c>
+      <c r="I549" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J549" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K549" t="inlineStr"/>
+      <c r="L549" t="inlineStr"/>
+      <c r="M549" t="inlineStr"/>
+      <c r="N549" t="inlineStr"/>
+      <c r="O549" t="inlineStr"/>
+      <c r="P549" t="inlineStr"/>
+      <c r="Q549" t="inlineStr"/>
+      <c r="R549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="E550" t="n">
+        <v>106.5</v>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G550" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H550" t="n">
+        <v>94</v>
+      </c>
+      <c r="I550" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J550" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K550" t="inlineStr"/>
+      <c r="L550" t="inlineStr"/>
+      <c r="M550" t="inlineStr"/>
+      <c r="N550" t="inlineStr"/>
+      <c r="O550" t="inlineStr"/>
+      <c r="P550" t="inlineStr"/>
+      <c r="Q550" t="inlineStr"/>
+      <c r="R550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>八方雲集</t>
+        </is>
+      </c>
+      <c r="E551" t="n">
+        <v>185</v>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G551" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H551" t="n">
+        <v>94</v>
+      </c>
+      <c r="I551" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J551" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K551" t="inlineStr"/>
+      <c r="L551" t="inlineStr"/>
+      <c r="M551" t="inlineStr"/>
+      <c r="N551" t="inlineStr"/>
+      <c r="O551" t="inlineStr"/>
+      <c r="P551" t="inlineStr"/>
+      <c r="Q551" t="inlineStr"/>
+      <c r="R551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="E552" t="n">
+        <v>41.4</v>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G552" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H552" t="n">
+        <v>92</v>
+      </c>
+      <c r="I552" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J552" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K552" t="inlineStr"/>
+      <c r="L552" t="inlineStr"/>
+      <c r="M552" t="inlineStr"/>
+      <c r="N552" t="inlineStr"/>
+      <c r="O552" t="inlineStr"/>
+      <c r="P552" t="inlineStr"/>
+      <c r="Q552" t="inlineStr"/>
+      <c r="R552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="E553" t="n">
+        <v>874</v>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G553" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H553" t="n">
+        <v>90</v>
+      </c>
+      <c r="I553" t="n">
+        <v>25</v>
+      </c>
+      <c r="J553" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K553" t="inlineStr"/>
+      <c r="L553" t="inlineStr"/>
+      <c r="M553" t="inlineStr"/>
+      <c r="N553" t="inlineStr"/>
+      <c r="O553" t="inlineStr"/>
+      <c r="P553" t="inlineStr"/>
+      <c r="Q553" t="inlineStr"/>
+      <c r="R553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="E554" t="n">
+        <v>582</v>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G554" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H554" t="n">
+        <v>90</v>
+      </c>
+      <c r="I554" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J554" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K554" t="inlineStr"/>
+      <c r="L554" t="inlineStr"/>
+      <c r="M554" t="inlineStr"/>
+      <c r="N554" t="inlineStr"/>
+      <c r="O554" t="inlineStr"/>
+      <c r="P554" t="inlineStr"/>
+      <c r="Q554" t="inlineStr"/>
+      <c r="R554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="E555" t="n">
+        <v>168</v>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G555" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H555" t="n">
+        <v>90</v>
+      </c>
+      <c r="I555" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J555" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K555" t="inlineStr"/>
+      <c r="L555" t="inlineStr"/>
+      <c r="M555" t="inlineStr"/>
+      <c r="N555" t="inlineStr"/>
+      <c r="O555" t="inlineStr"/>
+      <c r="P555" t="inlineStr"/>
+      <c r="Q555" t="inlineStr"/>
+      <c r="R555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+      <c r="E556" t="n">
+        <v>38.1</v>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G556" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H556" t="n">
+        <v>84</v>
+      </c>
+      <c r="I556" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J556" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K556" t="inlineStr"/>
+      <c r="L556" t="inlineStr"/>
+      <c r="M556" t="inlineStr"/>
+      <c r="N556" t="inlineStr"/>
+      <c r="O556" t="inlineStr"/>
+      <c r="P556" t="inlineStr"/>
+      <c r="Q556" t="inlineStr"/>
+      <c r="R556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="E557" t="n">
+        <v>2070</v>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G557" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H557" t="n">
+        <v>80</v>
+      </c>
+      <c r="I557" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J557" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K557" t="inlineStr"/>
+      <c r="L557" t="inlineStr"/>
+      <c r="M557" t="inlineStr"/>
+      <c r="N557" t="inlineStr"/>
+      <c r="O557" t="inlineStr"/>
+      <c r="P557" t="inlineStr"/>
+      <c r="Q557" t="inlineStr"/>
+      <c r="R557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="E558" t="n">
+        <v>1520</v>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G558" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H558" t="n">
+        <v>80</v>
+      </c>
+      <c r="I558" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J558" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K558" t="inlineStr"/>
+      <c r="L558" t="inlineStr"/>
+      <c r="M558" t="inlineStr"/>
+      <c r="N558" t="inlineStr"/>
+      <c r="O558" t="inlineStr"/>
+      <c r="P558" t="inlineStr"/>
+      <c r="Q558" t="inlineStr"/>
+      <c r="R558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>達欣工</t>
+        </is>
+      </c>
+      <c r="E559" t="n">
+        <v>91.40000000000001</v>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G559" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H559" t="n">
+        <v>79</v>
+      </c>
+      <c r="I559" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J559" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K559" t="inlineStr"/>
+      <c r="L559" t="inlineStr"/>
+      <c r="M559" t="inlineStr"/>
+      <c r="N559" t="inlineStr"/>
+      <c r="O559" t="inlineStr"/>
+      <c r="P559" t="inlineStr"/>
+      <c r="Q559" t="inlineStr"/>
+      <c r="R559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>友輝</t>
+        </is>
+      </c>
+      <c r="E560" t="n">
+        <v>53</v>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G560" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H560" t="n">
+        <v>77</v>
+      </c>
+      <c r="I560" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J560" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K560" t="inlineStr"/>
+      <c r="L560" t="inlineStr"/>
+      <c r="M560" t="inlineStr"/>
+      <c r="N560" t="inlineStr"/>
+      <c r="O560" t="inlineStr"/>
+      <c r="P560" t="inlineStr"/>
+      <c r="Q560" t="inlineStr"/>
+      <c r="R560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="E561" t="n">
+        <v>325.5</v>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G561" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H561" t="n">
+        <v>65</v>
+      </c>
+      <c r="I561" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J561" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K561" t="inlineStr"/>
+      <c r="L561" t="inlineStr"/>
+      <c r="M561" t="inlineStr"/>
+      <c r="N561" t="inlineStr"/>
+      <c r="O561" t="inlineStr"/>
+      <c r="P561" t="inlineStr"/>
+      <c r="Q561" t="inlineStr"/>
+      <c r="R561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="E562" t="n">
+        <v>188.5</v>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G562" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H562" t="n">
+        <v>62</v>
+      </c>
+      <c r="I562" t="n">
+        <v>10</v>
+      </c>
+      <c r="J562" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K562" t="inlineStr"/>
+      <c r="L562" t="inlineStr"/>
+      <c r="M562" t="inlineStr"/>
+      <c r="N562" t="inlineStr"/>
+      <c r="O562" t="inlineStr"/>
+      <c r="P562" t="inlineStr"/>
+      <c r="Q562" t="inlineStr"/>
+      <c r="R562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+      <c r="E563" t="n">
+        <v>1490</v>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G563" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H563" t="n">
+        <v>60</v>
+      </c>
+      <c r="I563" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J563" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K563" t="inlineStr"/>
+      <c r="L563" t="inlineStr"/>
+      <c r="M563" t="inlineStr"/>
+      <c r="N563" t="inlineStr"/>
+      <c r="O563" t="inlineStr"/>
+      <c r="P563" t="inlineStr"/>
+      <c r="Q563" t="inlineStr"/>
+      <c r="R563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>德昌</t>
+        </is>
+      </c>
+      <c r="E564" t="n">
+        <v>70</v>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G564" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H564" t="n">
+        <v>79</v>
+      </c>
+      <c r="I564" t="inlineStr"/>
+      <c r="J564" t="inlineStr"/>
+      <c r="K564" t="inlineStr"/>
+      <c r="L564" t="inlineStr"/>
+      <c r="M564" t="inlineStr"/>
+      <c r="N564" t="inlineStr"/>
+      <c r="O564" t="inlineStr"/>
+      <c r="P564" t="inlineStr"/>
+      <c r="Q564" t="inlineStr"/>
+      <c r="R564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+      <c r="E565" t="n">
+        <v>362.5</v>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G565" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H565" t="n">
+        <v>77</v>
+      </c>
+      <c r="I565" t="inlineStr"/>
+      <c r="J565" t="inlineStr"/>
+      <c r="K565" t="inlineStr"/>
+      <c r="L565" t="inlineStr"/>
+      <c r="M565" t="inlineStr"/>
+      <c r="N565" t="inlineStr"/>
+      <c r="O565" t="inlineStr"/>
+      <c r="P565" t="inlineStr"/>
+      <c r="Q565" t="inlineStr"/>
+      <c r="R565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>鑫龍騰</t>
+        </is>
+      </c>
+      <c r="E566" t="n">
+        <v>22.85</v>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G566" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H566" t="n">
+        <v>77</v>
+      </c>
+      <c r="I566" t="inlineStr"/>
+      <c r="J566" t="inlineStr"/>
+      <c r="K566" t="inlineStr"/>
+      <c r="L566" t="inlineStr"/>
+      <c r="M566" t="inlineStr"/>
+      <c r="N566" t="inlineStr"/>
+      <c r="O566" t="inlineStr"/>
+      <c r="P566" t="inlineStr"/>
+      <c r="Q566" t="inlineStr"/>
+      <c r="R566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="E567" t="n">
+        <v>199.5</v>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G567" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H567" t="n">
+        <v>69</v>
+      </c>
+      <c r="I567" t="inlineStr"/>
+      <c r="J567" t="inlineStr"/>
+      <c r="K567" t="inlineStr"/>
+      <c r="L567" t="inlineStr"/>
+      <c r="M567" t="inlineStr"/>
+      <c r="N567" t="inlineStr"/>
+      <c r="O567" t="inlineStr"/>
+      <c r="P567" t="inlineStr"/>
+      <c r="Q567" t="inlineStr"/>
+      <c r="R567" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R567"/>
+  <dimension ref="A1:R568"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30313,6 +30313,56 @@
       <c r="P567" t="inlineStr"/>
       <c r="Q567" t="inlineStr"/>
       <c r="R567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>6669</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="E568" t="n">
+        <v>2240</v>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G568" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H568" t="n">
+        <v>65</v>
+      </c>
+      <c r="I568" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J568" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="K568" t="inlineStr"/>
+      <c r="L568" t="inlineStr"/>
+      <c r="M568" t="inlineStr"/>
+      <c r="N568" t="inlineStr"/>
+      <c r="O568" t="inlineStr"/>
+      <c r="P568" t="inlineStr"/>
+      <c r="Q568" t="inlineStr"/>
+      <c r="R568" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="C2" t="n">
-        <v>43.5</v>
+        <v>43.8</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.65</v>
+        <v>-0.63</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.2</v>
+        <v>-1.19</v>
       </c>
       <c r="F2" t="n">
         <v>60.56</v>
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>324</v>
+        <v>331</v>
       </c>
       <c r="D2" t="n">
-        <v>43.5</v>
+        <v>43.8</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.65</v>
+        <v>-0.63</v>
       </c>
     </row>
     <row r="3">
@@ -23235,8 +23235,12 @@
       </c>
       <c r="I424" t="inlineStr"/>
       <c r="J424" t="inlineStr"/>
-      <c r="K424" t="inlineStr"/>
-      <c r="L424" t="inlineStr"/>
+      <c r="K424" t="n">
+        <v>32.05</v>
+      </c>
+      <c r="L424" t="n">
+        <v>-13.14</v>
+      </c>
       <c r="M424" t="inlineStr"/>
       <c r="N424" t="inlineStr"/>
       <c r="O424" t="inlineStr"/>
@@ -23285,8 +23289,12 @@
       <c r="J425" t="n">
         <v>1.29</v>
       </c>
-      <c r="K425" t="inlineStr"/>
-      <c r="L425" t="inlineStr"/>
+      <c r="K425" t="n">
+        <v>155.5</v>
+      </c>
+      <c r="L425" t="n">
+        <v>1.3</v>
+      </c>
       <c r="M425" t="inlineStr"/>
       <c r="N425" t="inlineStr"/>
       <c r="O425" t="inlineStr"/>
@@ -23335,8 +23343,12 @@
       <c r="J426" t="n">
         <v>1.26</v>
       </c>
-      <c r="K426" t="inlineStr"/>
-      <c r="L426" t="inlineStr"/>
+      <c r="K426" t="n">
+        <v>118</v>
+      </c>
+      <c r="L426" t="n">
+        <v>-1.67</v>
+      </c>
       <c r="M426" t="inlineStr"/>
       <c r="N426" t="inlineStr"/>
       <c r="O426" t="inlineStr"/>
@@ -23385,8 +23397,12 @@
       <c r="J427" t="n">
         <v>0.73</v>
       </c>
-      <c r="K427" t="inlineStr"/>
-      <c r="L427" t="inlineStr"/>
+      <c r="K427" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="L427" t="n">
+        <v>2.58</v>
+      </c>
       <c r="M427" t="inlineStr"/>
       <c r="N427" t="inlineStr"/>
       <c r="O427" t="inlineStr"/>
@@ -23435,8 +23451,12 @@
       <c r="J428" t="n">
         <v>0.64</v>
       </c>
-      <c r="K428" t="inlineStr"/>
-      <c r="L428" t="inlineStr"/>
+      <c r="K428" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="L428" t="n">
+        <v>9.220000000000001</v>
+      </c>
       <c r="M428" t="inlineStr"/>
       <c r="N428" t="inlineStr"/>
       <c r="O428" t="inlineStr"/>
@@ -23485,8 +23505,12 @@
       <c r="J429" t="n">
         <v>0.42</v>
       </c>
-      <c r="K429" t="inlineStr"/>
-      <c r="L429" t="inlineStr"/>
+      <c r="K429" t="n">
+        <v>25</v>
+      </c>
+      <c r="L429" t="n">
+        <v>-3.29</v>
+      </c>
       <c r="M429" t="inlineStr"/>
       <c r="N429" t="inlineStr"/>
       <c r="O429" t="inlineStr"/>
@@ -23535,8 +23559,12 @@
       <c r="J430" t="n">
         <v>0.5600000000000001</v>
       </c>
-      <c r="K430" t="inlineStr"/>
-      <c r="L430" t="inlineStr"/>
+      <c r="K430" t="n">
+        <v>55.5</v>
+      </c>
+      <c r="L430" t="n">
+        <v>4.72</v>
+      </c>
       <c r="M430" t="inlineStr"/>
       <c r="N430" t="inlineStr"/>
       <c r="O430" t="inlineStr"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -493,16 +493,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="C3" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.18</v>
+        <v>0.38</v>
       </c>
       <c r="E3" t="n">
-        <v>-4.47</v>
+        <v>-3.56</v>
       </c>
       <c r="F3" t="n">
         <v>82.70999999999999</v>
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>73</v>
+        <v>107</v>
       </c>
       <c r="D3" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.18</v>
+        <v>0.38</v>
       </c>
     </row>
   </sheetData>
@@ -9827,8 +9827,12 @@
       <c r="L173" t="n">
         <v>-4.14</v>
       </c>
-      <c r="M173" t="inlineStr"/>
-      <c r="N173" t="inlineStr"/>
+      <c r="M173" t="n">
+        <v>158</v>
+      </c>
+      <c r="N173" t="n">
+        <v>0.64</v>
+      </c>
       <c r="O173" t="inlineStr"/>
       <c r="P173" t="inlineStr"/>
       <c r="Q173" t="inlineStr"/>
@@ -9881,8 +9885,12 @@
       <c r="L174" t="n">
         <v>-6.29</v>
       </c>
-      <c r="M174" t="inlineStr"/>
-      <c r="N174" t="inlineStr"/>
+      <c r="M174" t="n">
+        <v>595</v>
+      </c>
+      <c r="N174" t="n">
+        <v>7.01</v>
+      </c>
       <c r="O174" t="inlineStr"/>
       <c r="P174" t="inlineStr"/>
       <c r="Q174" t="inlineStr"/>
@@ -9935,8 +9943,12 @@
       <c r="L175" t="n">
         <v>0.41</v>
       </c>
-      <c r="M175" t="inlineStr"/>
-      <c r="N175" t="inlineStr"/>
+      <c r="M175" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="N175" t="n">
+        <v>-4.08</v>
+      </c>
       <c r="O175" t="inlineStr"/>
       <c r="P175" t="inlineStr"/>
       <c r="Q175" t="inlineStr"/>
@@ -9989,8 +10001,12 @@
       <c r="L176" t="n">
         <v>-8.220000000000001</v>
       </c>
-      <c r="M176" t="inlineStr"/>
-      <c r="N176" t="inlineStr"/>
+      <c r="M176" t="n">
+        <v>360.5</v>
+      </c>
+      <c r="N176" t="n">
+        <v>7.77</v>
+      </c>
       <c r="O176" t="inlineStr"/>
       <c r="P176" t="inlineStr"/>
       <c r="Q176" t="inlineStr"/>
@@ -10043,8 +10059,12 @@
       <c r="L177" t="n">
         <v>-7.59</v>
       </c>
-      <c r="M177" t="inlineStr"/>
-      <c r="N177" t="inlineStr"/>
+      <c r="M177" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="N177" t="n">
+        <v>-13.56</v>
+      </c>
       <c r="O177" t="inlineStr"/>
       <c r="P177" t="inlineStr"/>
       <c r="Q177" t="inlineStr"/>
@@ -10097,8 +10117,12 @@
       <c r="L178" t="n">
         <v>-20.57</v>
       </c>
-      <c r="M178" t="inlineStr"/>
-      <c r="N178" t="inlineStr"/>
+      <c r="M178" t="n">
+        <v>135.5</v>
+      </c>
+      <c r="N178" t="n">
+        <v>-14.24</v>
+      </c>
       <c r="O178" t="inlineStr"/>
       <c r="P178" t="inlineStr"/>
       <c r="Q178" t="inlineStr"/>
@@ -10151,8 +10175,12 @@
       <c r="L179" t="n">
         <v>8.58</v>
       </c>
-      <c r="M179" t="inlineStr"/>
-      <c r="N179" t="inlineStr"/>
+      <c r="M179" t="n">
+        <v>240</v>
+      </c>
+      <c r="N179" t="n">
+        <v>0.42</v>
+      </c>
       <c r="O179" t="inlineStr"/>
       <c r="P179" t="inlineStr"/>
       <c r="Q179" t="inlineStr"/>
@@ -10205,8 +10233,12 @@
       <c r="L180" t="n">
         <v>-8.6</v>
       </c>
-      <c r="M180" t="inlineStr"/>
-      <c r="N180" t="inlineStr"/>
+      <c r="M180" t="n">
+        <v>991</v>
+      </c>
+      <c r="N180" t="n">
+        <v>-10.32</v>
+      </c>
       <c r="O180" t="inlineStr"/>
       <c r="P180" t="inlineStr"/>
       <c r="Q180" t="inlineStr"/>
@@ -10259,8 +10291,12 @@
       <c r="L181" t="n">
         <v>14.4</v>
       </c>
-      <c r="M181" t="inlineStr"/>
-      <c r="N181" t="inlineStr"/>
+      <c r="M181" t="n">
+        <v>57.3</v>
+      </c>
+      <c r="N181" t="n">
+        <v>-6.22</v>
+      </c>
       <c r="O181" t="inlineStr"/>
       <c r="P181" t="inlineStr"/>
       <c r="Q181" t="inlineStr"/>
@@ -10313,8 +10349,12 @@
       <c r="L182" t="n">
         <v>49.42</v>
       </c>
-      <c r="M182" t="inlineStr"/>
-      <c r="N182" t="inlineStr"/>
+      <c r="M182" t="n">
+        <v>3280</v>
+      </c>
+      <c r="N182" t="n">
+        <v>51.5</v>
+      </c>
       <c r="O182" t="inlineStr"/>
       <c r="P182" t="inlineStr"/>
       <c r="Q182" t="inlineStr"/>
@@ -10367,8 +10407,12 @@
       <c r="L183" t="n">
         <v>-10.84</v>
       </c>
-      <c r="M183" t="inlineStr"/>
-      <c r="N183" t="inlineStr"/>
+      <c r="M183" t="n">
+        <v>718</v>
+      </c>
+      <c r="N183" t="n">
+        <v>-19.78</v>
+      </c>
       <c r="O183" t="inlineStr"/>
       <c r="P183" t="inlineStr"/>
       <c r="Q183" t="inlineStr"/>
@@ -10421,8 +10465,12 @@
       <c r="L184" t="n">
         <v>-1.84</v>
       </c>
-      <c r="M184" t="inlineStr"/>
-      <c r="N184" t="inlineStr"/>
+      <c r="M184" t="n">
+        <v>2490</v>
+      </c>
+      <c r="N184" t="n">
+        <v>2.05</v>
+      </c>
       <c r="O184" t="inlineStr"/>
       <c r="P184" t="inlineStr"/>
       <c r="Q184" t="inlineStr"/>
@@ -10475,8 +10523,12 @@
       <c r="L185" t="n">
         <v>8.25</v>
       </c>
-      <c r="M185" t="inlineStr"/>
-      <c r="N185" t="inlineStr"/>
+      <c r="M185" t="n">
+        <v>120</v>
+      </c>
+      <c r="N185" t="n">
+        <v>16.5</v>
+      </c>
       <c r="O185" t="inlineStr"/>
       <c r="P185" t="inlineStr"/>
       <c r="Q185" t="inlineStr"/>
@@ -10529,8 +10581,12 @@
       <c r="L186" t="n">
         <v>-6.41</v>
       </c>
-      <c r="M186" t="inlineStr"/>
-      <c r="N186" t="inlineStr"/>
+      <c r="M186" t="n">
+        <v>118.5</v>
+      </c>
+      <c r="N186" t="n">
+        <v>1.28</v>
+      </c>
       <c r="O186" t="inlineStr"/>
       <c r="P186" t="inlineStr"/>
       <c r="Q186" t="inlineStr"/>
@@ -10583,8 +10639,12 @@
       <c r="L187" t="n">
         <v>-3.14</v>
       </c>
-      <c r="M187" t="inlineStr"/>
-      <c r="N187" t="inlineStr"/>
+      <c r="M187" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="N187" t="n">
+        <v>-14.14</v>
+      </c>
       <c r="O187" t="inlineStr"/>
       <c r="P187" t="inlineStr"/>
       <c r="Q187" t="inlineStr"/>
@@ -10637,8 +10697,12 @@
       <c r="L188" t="n">
         <v>-4.46</v>
       </c>
-      <c r="M188" t="inlineStr"/>
-      <c r="N188" t="inlineStr"/>
+      <c r="M188" t="n">
+        <v>106</v>
+      </c>
+      <c r="N188" t="n">
+        <v>-5.36</v>
+      </c>
       <c r="O188" t="inlineStr"/>
       <c r="P188" t="inlineStr"/>
       <c r="Q188" t="inlineStr"/>
@@ -10691,8 +10755,12 @@
       <c r="L189" t="n">
         <v>3.11</v>
       </c>
-      <c r="M189" t="inlineStr"/>
-      <c r="N189" t="inlineStr"/>
+      <c r="M189" t="n">
+        <v>183.5</v>
+      </c>
+      <c r="N189" t="n">
+        <v>3.67</v>
+      </c>
       <c r="O189" t="inlineStr"/>
       <c r="P189" t="inlineStr"/>
       <c r="Q189" t="inlineStr"/>
@@ -10745,8 +10813,12 @@
       <c r="L190" t="n">
         <v>-5.34</v>
       </c>
-      <c r="M190" t="inlineStr"/>
-      <c r="N190" t="inlineStr"/>
+      <c r="M190" t="n">
+        <v>43</v>
+      </c>
+      <c r="N190" t="n">
+        <v>2.02</v>
+      </c>
       <c r="O190" t="inlineStr"/>
       <c r="P190" t="inlineStr"/>
       <c r="Q190" t="inlineStr"/>
@@ -10799,8 +10871,12 @@
       <c r="L191" t="n">
         <v>-12.66</v>
       </c>
-      <c r="M191" t="inlineStr"/>
-      <c r="N191" t="inlineStr"/>
+      <c r="M191" t="n">
+        <v>838</v>
+      </c>
+      <c r="N191" t="n">
+        <v>-26.81</v>
+      </c>
       <c r="O191" t="inlineStr"/>
       <c r="P191" t="inlineStr"/>
       <c r="Q191" t="inlineStr"/>
@@ -10853,8 +10929,12 @@
       <c r="L192" t="n">
         <v>14.55</v>
       </c>
-      <c r="M192" t="inlineStr"/>
-      <c r="N192" t="inlineStr"/>
+      <c r="M192" t="n">
+        <v>572</v>
+      </c>
+      <c r="N192" t="n">
+        <v>34.27</v>
+      </c>
       <c r="O192" t="inlineStr"/>
       <c r="P192" t="inlineStr"/>
       <c r="Q192" t="inlineStr"/>
@@ -10907,8 +10987,12 @@
       <c r="L193" t="n">
         <v>5.04</v>
       </c>
-      <c r="M193" t="inlineStr"/>
-      <c r="N193" t="inlineStr"/>
+      <c r="M193" t="n">
+        <v>168</v>
+      </c>
+      <c r="N193" t="n">
+        <v>20.86</v>
+      </c>
       <c r="O193" t="inlineStr"/>
       <c r="P193" t="inlineStr"/>
       <c r="Q193" t="inlineStr"/>
@@ -10961,8 +11045,12 @@
       <c r="L194" t="n">
         <v>8.31</v>
       </c>
-      <c r="M194" t="inlineStr"/>
-      <c r="N194" t="inlineStr"/>
+      <c r="M194" t="n">
+        <v>38.65</v>
+      </c>
+      <c r="N194" t="n">
+        <v>0.39</v>
+      </c>
       <c r="O194" t="inlineStr"/>
       <c r="P194" t="inlineStr"/>
       <c r="Q194" t="inlineStr"/>
@@ -11015,8 +11103,12 @@
       <c r="L195" t="n">
         <v>-1.71</v>
       </c>
-      <c r="M195" t="inlineStr"/>
-      <c r="N195" t="inlineStr"/>
+      <c r="M195" t="n">
+        <v>2040</v>
+      </c>
+      <c r="N195" t="n">
+        <v>-12.82</v>
+      </c>
       <c r="O195" t="inlineStr"/>
       <c r="P195" t="inlineStr"/>
       <c r="Q195" t="inlineStr"/>
@@ -11069,8 +11161,12 @@
       <c r="L196" t="n">
         <v>12.72</v>
       </c>
-      <c r="M196" t="inlineStr"/>
-      <c r="N196" t="inlineStr"/>
+      <c r="M196" t="n">
+        <v>1475</v>
+      </c>
+      <c r="N196" t="n">
+        <v>64.62</v>
+      </c>
       <c r="O196" t="inlineStr"/>
       <c r="P196" t="inlineStr"/>
       <c r="Q196" t="inlineStr"/>
@@ -11123,8 +11219,12 @@
       <c r="L197" t="n">
         <v>0.23</v>
       </c>
-      <c r="M197" t="inlineStr"/>
-      <c r="N197" t="inlineStr"/>
+      <c r="M197" t="n">
+        <v>89</v>
+      </c>
+      <c r="N197" t="n">
+        <v>1.02</v>
+      </c>
       <c r="O197" t="inlineStr"/>
       <c r="P197" t="inlineStr"/>
       <c r="Q197" t="inlineStr"/>
@@ -11177,8 +11277,12 @@
       <c r="L198" t="n">
         <v>-16.09</v>
       </c>
-      <c r="M198" t="inlineStr"/>
-      <c r="N198" t="inlineStr"/>
+      <c r="M198" t="n">
+        <v>54.4</v>
+      </c>
+      <c r="N198" t="n">
+        <v>-25.17</v>
+      </c>
       <c r="O198" t="inlineStr"/>
       <c r="P198" t="inlineStr"/>
       <c r="Q198" t="inlineStr"/>
@@ -11231,8 +11335,12 @@
       <c r="L199" t="n">
         <v>-9.69</v>
       </c>
-      <c r="M199" t="inlineStr"/>
-      <c r="N199" t="inlineStr"/>
+      <c r="M199" t="n">
+        <v>51.4</v>
+      </c>
+      <c r="N199" t="n">
+        <v>-15.6</v>
+      </c>
       <c r="O199" t="inlineStr"/>
       <c r="P199" t="inlineStr"/>
       <c r="Q199" t="inlineStr"/>
@@ -11285,8 +11393,12 @@
       <c r="L200" t="n">
         <v>-14.04</v>
       </c>
-      <c r="M200" t="inlineStr"/>
-      <c r="N200" t="inlineStr"/>
+      <c r="M200" t="n">
+        <v>323</v>
+      </c>
+      <c r="N200" t="n">
+        <v>-15.22</v>
+      </c>
       <c r="O200" t="inlineStr"/>
       <c r="P200" t="inlineStr"/>
       <c r="Q200" t="inlineStr"/>
@@ -11339,8 +11451,12 @@
       <c r="L201" t="n">
         <v>32.99</v>
       </c>
-      <c r="M201" t="inlineStr"/>
-      <c r="N201" t="inlineStr"/>
+      <c r="M201" t="n">
+        <v>187</v>
+      </c>
+      <c r="N201" t="n">
+        <v>28.52</v>
+      </c>
       <c r="O201" t="inlineStr"/>
       <c r="P201" t="inlineStr"/>
       <c r="Q201" t="inlineStr"/>
@@ -11393,8 +11509,12 @@
       <c r="L202" t="n">
         <v>-8.91</v>
       </c>
-      <c r="M202" t="inlineStr"/>
-      <c r="N202" t="inlineStr"/>
+      <c r="M202" t="n">
+        <v>1540</v>
+      </c>
+      <c r="N202" t="n">
+        <v>1.65</v>
+      </c>
       <c r="O202" t="inlineStr"/>
       <c r="P202" t="inlineStr"/>
       <c r="Q202" t="inlineStr"/>
@@ -11443,8 +11563,12 @@
       <c r="L203" t="n">
         <v>3.24</v>
       </c>
-      <c r="M203" t="inlineStr"/>
-      <c r="N203" t="inlineStr"/>
+      <c r="M203" t="n">
+        <v>69.7</v>
+      </c>
+      <c r="N203" t="n">
+        <v>2.8</v>
+      </c>
       <c r="O203" t="inlineStr"/>
       <c r="P203" t="inlineStr"/>
       <c r="Q203" t="inlineStr"/>
@@ -11493,8 +11617,12 @@
       <c r="L204" t="n">
         <v>-1.47</v>
       </c>
-      <c r="M204" t="inlineStr"/>
-      <c r="N204" t="inlineStr"/>
+      <c r="M204" t="n">
+        <v>363</v>
+      </c>
+      <c r="N204" t="n">
+        <v>-11.03</v>
+      </c>
       <c r="O204" t="inlineStr"/>
       <c r="P204" t="inlineStr"/>
       <c r="Q204" t="inlineStr"/>
@@ -11543,8 +11671,12 @@
       <c r="L205" t="n">
         <v>-2.51</v>
       </c>
-      <c r="M205" t="inlineStr"/>
-      <c r="N205" t="inlineStr"/>
+      <c r="M205" t="n">
+        <v>23.05</v>
+      </c>
+      <c r="N205" t="n">
+        <v>-3.56</v>
+      </c>
       <c r="O205" t="inlineStr"/>
       <c r="P205" t="inlineStr"/>
       <c r="Q205" t="inlineStr"/>
@@ -11593,8 +11725,12 @@
       <c r="L206" t="n">
         <v>28.37</v>
       </c>
-      <c r="M206" t="inlineStr"/>
-      <c r="N206" t="inlineStr"/>
+      <c r="M206" t="n">
+        <v>189.5</v>
+      </c>
+      <c r="N206" t="n">
+        <v>4.41</v>
+      </c>
       <c r="O206" t="inlineStr"/>
       <c r="P206" t="inlineStr"/>
       <c r="Q206" t="inlineStr"/>
@@ -30623,7 +30759,7 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46260</v>
+        <v>46218</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -30641,7 +30777,7 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1065</v>
+        <v>896</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -30663,24 +30799,28 @@
         <v>0.75</v>
       </c>
       <c r="K4" t="n">
-        <v>1710</v>
+        <v>1010</v>
       </c>
       <c r="L4" t="n">
-        <v>60.56</v>
-      </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+        <v>12.72</v>
+      </c>
+      <c r="M4" t="n">
+        <v>1475</v>
+      </c>
+      <c r="N4" t="n">
+        <v>64.62</v>
+      </c>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>60.56</v>
+        <v>64.62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46210</v>
+        <v>46260</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -30698,7 +30838,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>970</v>
+        <v>1065</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -30720,28 +30860,24 @@
         <v>0.75</v>
       </c>
       <c r="K5" t="n">
-        <v>1060</v>
+        <v>1710</v>
       </c>
       <c r="L5" t="n">
-        <v>9.279999999999999</v>
-      </c>
-      <c r="M5" t="n">
-        <v>1550</v>
-      </c>
-      <c r="N5" t="n">
-        <v>59.79</v>
-      </c>
+        <v>60.56</v>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>59.79</v>
+        <v>60.56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -30750,16 +30886,16 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>奇鋐</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2300</v>
+        <v>970</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -30772,37 +30908,37 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="I6" t="n">
-        <v>24.6</v>
+        <v>21.8</v>
       </c>
       <c r="J6" t="n">
-        <v>0.66</v>
+        <v>0.75</v>
       </c>
       <c r="K6" t="n">
-        <v>2095</v>
+        <v>1060</v>
       </c>
       <c r="L6" t="n">
-        <v>-8.91</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>3555</v>
+        <v>1550</v>
       </c>
       <c r="N6" t="n">
-        <v>54.57</v>
+        <v>59.79</v>
       </c>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>54.57</v>
+        <v>59.79</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -30820,7 +30956,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2165</v>
+        <v>2300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -30842,24 +30978,28 @@
         <v>0.66</v>
       </c>
       <c r="K7" t="n">
-        <v>3235</v>
+        <v>2095</v>
       </c>
       <c r="L7" t="n">
-        <v>49.42</v>
-      </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+        <v>-8.91</v>
+      </c>
+      <c r="M7" t="n">
+        <v>3555</v>
+      </c>
+      <c r="N7" t="n">
+        <v>54.57</v>
+      </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>49.42</v>
+        <v>54.57</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46234</v>
+        <v>46218</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -30877,7 +31017,7 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2320</v>
+        <v>2165</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -30899,24 +31039,28 @@
         <v>0.66</v>
       </c>
       <c r="K8" t="n">
-        <v>3425</v>
+        <v>3235</v>
       </c>
       <c r="L8" t="n">
-        <v>47.63</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+        <v>49.42</v>
+      </c>
+      <c r="M8" t="n">
+        <v>3280</v>
+      </c>
+      <c r="N8" t="n">
+        <v>51.5</v>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>47.63</v>
+        <v>51.5</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46210</v>
+        <v>46234</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -30934,7 +31078,7 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2450</v>
+        <v>2320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -30956,28 +31100,24 @@
         <v>0.66</v>
       </c>
       <c r="K9" t="n">
-        <v>2940</v>
+        <v>3425</v>
       </c>
       <c r="L9" t="n">
-        <v>20</v>
-      </c>
-      <c r="M9" t="n">
-        <v>3585</v>
-      </c>
-      <c r="N9" t="n">
-        <v>46.33</v>
-      </c>
+        <v>47.63</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>46.33</v>
+        <v>47.63</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46234</v>
+        <v>46210</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -30986,50 +31126,54 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>3017</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>奇鋐</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>821</v>
+        <v>2450</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>76</v>
+        <v>100</v>
       </c>
       <c r="I10" t="n">
-        <v>38.8</v>
+        <v>24.6</v>
       </c>
       <c r="J10" t="n">
-        <v>1.03</v>
+        <v>0.66</v>
       </c>
       <c r="K10" t="n">
-        <v>1180</v>
+        <v>2940</v>
       </c>
       <c r="L10" t="n">
-        <v>43.73</v>
-      </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+        <v>20</v>
+      </c>
+      <c r="M10" t="n">
+        <v>3585</v>
+      </c>
+      <c r="N10" t="n">
+        <v>46.33</v>
+      </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>43.73</v>
+        <v>46.33</v>
       </c>
     </row>
     <row r="11">
@@ -31043,41 +31187,41 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3324</t>
+          <t>6739</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>竹陞科技</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>902</v>
+        <v>821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="I11" t="n">
-        <v>21.8</v>
+        <v>38.8</v>
       </c>
       <c r="J11" t="n">
-        <v>0.75</v>
+        <v>1.03</v>
       </c>
       <c r="K11" t="n">
-        <v>1250</v>
+        <v>1180</v>
       </c>
       <c r="L11" t="n">
-        <v>38.58</v>
+        <v>43.73</v>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
@@ -31086,12 +31230,12 @@
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>38.58</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46252</v>
+        <v>46234</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -31109,7 +31253,7 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1005</v>
+        <v>902</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -31131,10 +31275,10 @@
         <v>0.75</v>
       </c>
       <c r="K12" t="n">
-        <v>1385</v>
+        <v>1250</v>
       </c>
       <c r="L12" t="n">
-        <v>37.81</v>
+        <v>38.58</v>
       </c>
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
@@ -31143,12 +31287,12 @@
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>37.81</v>
+        <v>38.58</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -31166,7 +31310,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1010</v>
+        <v>1005</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -31191,7 +31335,7 @@
         <v>1385</v>
       </c>
       <c r="L13" t="n">
-        <v>37.13</v>
+        <v>37.81</v>
       </c>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
@@ -31200,12 +31344,12 @@
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>37.13</v>
+        <v>37.81</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46234</v>
+        <v>46244</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -31214,16 +31358,16 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>2421</t>
+          <t>3324</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>建準</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>131</v>
+        <v>1010</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -31236,19 +31380,19 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="I14" t="n">
-        <v>14.1</v>
+        <v>21.8</v>
       </c>
       <c r="J14" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="K14" t="n">
-        <v>179.5</v>
+        <v>1385</v>
       </c>
       <c r="L14" t="n">
-        <v>37.02</v>
+        <v>37.13</v>
       </c>
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
@@ -31257,7 +31401,7 @@
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>37.02</v>
+        <v>37.13</v>
       </c>
     </row>
     <row r="15">
@@ -31271,16 +31415,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2421</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>建準</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>369</v>
+        <v>131</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -31296,16 +31440,16 @@
         <v>90</v>
       </c>
       <c r="I15" t="n">
-        <v>21.2</v>
+        <v>14.1</v>
       </c>
       <c r="J15" t="n">
-        <v>0.92</v>
+        <v>0.73</v>
       </c>
       <c r="K15" t="n">
-        <v>496.5</v>
+        <v>179.5</v>
       </c>
       <c r="L15" t="n">
-        <v>34.55</v>
+        <v>37.02</v>
       </c>
       <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
@@ -31314,12 +31458,12 @@
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>34.55</v>
+        <v>37.02</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46218</v>
+        <v>46234</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -31328,16 +31472,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>145.5</v>
+        <v>369</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -31346,23 +31490,23 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>62</v>
+        <v>90</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>21.2</v>
       </c>
       <c r="J16" t="n">
-        <v>0.31</v>
+        <v>0.92</v>
       </c>
       <c r="K16" t="n">
-        <v>193.5</v>
+        <v>496.5</v>
       </c>
       <c r="L16" t="n">
-        <v>32.99</v>
+        <v>34.55</v>
       </c>
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
@@ -31371,12 +31515,12 @@
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>32.99</v>
+        <v>34.55</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -31385,16 +31529,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5115</v>
+        <v>426</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -31403,37 +31547,41 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="I17" t="n">
-        <v>9.6</v>
+        <v>21.2</v>
       </c>
       <c r="J17" t="n">
-        <v>0.26</v>
+        <v>0.92</v>
       </c>
       <c r="K17" t="n">
-        <v>6620</v>
+        <v>488</v>
       </c>
       <c r="L17" t="n">
-        <v>29.42</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+        <v>14.55</v>
+      </c>
+      <c r="M17" t="n">
+        <v>572</v>
+      </c>
+      <c r="N17" t="n">
+        <v>34.27</v>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>29.42</v>
+        <v>34.27</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -31442,20 +31590,20 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>8271</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>宇瞻</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>181.5</v>
+        <v>5115</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -31464,15 +31612,19 @@
         </is>
       </c>
       <c r="H18" t="n">
-        <v>69</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="I18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0.26</v>
+      </c>
       <c r="K18" t="n">
-        <v>233</v>
+        <v>6620</v>
       </c>
       <c r="L18" t="n">
-        <v>28.37</v>
+        <v>29.42</v>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
@@ -31481,12 +31633,12 @@
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>28.37</v>
+        <v>29.42</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46205</v>
+        <v>46218</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -31495,20 +31647,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>407</v>
+        <v>145.5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -31519,31 +31671,35 @@
       <c r="H19" t="n">
         <v>62</v>
       </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+      <c r="I19" t="n">
+        <v>10</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.31</v>
+      </c>
       <c r="K19" t="n">
-        <v>396.5</v>
+        <v>193.5</v>
       </c>
       <c r="L19" t="n">
-        <v>-2.58</v>
+        <v>32.99</v>
       </c>
       <c r="M19" t="n">
-        <v>519</v>
+        <v>187</v>
       </c>
       <c r="N19" t="n">
-        <v>27.52</v>
+        <v>28.52</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>27.52</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46244</v>
+        <v>46205</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -31552,55 +31708,55 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>401.5</v>
+        <v>407</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>90</v>
-      </c>
-      <c r="I20" t="n">
-        <v>21.2</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.92</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="n">
-        <v>509</v>
+        <v>396.5</v>
       </c>
       <c r="L20" t="n">
-        <v>26.77</v>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+        <v>-2.58</v>
+      </c>
+      <c r="M20" t="n">
+        <v>519</v>
+      </c>
+      <c r="N20" t="n">
+        <v>27.52</v>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>26.77</v>
+        <v>27.52</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46202</v>
+        <v>46244</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -31609,16 +31765,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>零壹</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>97.40000000000001</v>
+        <v>401.5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -31631,32 +31787,28 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>97</v>
+        <v>90</v>
       </c>
       <c r="I21" t="n">
-        <v>12.4</v>
+        <v>21.2</v>
       </c>
       <c r="J21" t="n">
-        <v>0.73</v>
+        <v>0.92</v>
       </c>
       <c r="K21" t="n">
-        <v>99.3</v>
+        <v>509</v>
       </c>
       <c r="L21" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="M21" t="n">
-        <v>120</v>
-      </c>
-      <c r="N21" t="n">
-        <v>23.2</v>
-      </c>
+        <v>26.77</v>
+      </c>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr"/>
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>23.2</v>
+        <v>26.77</v>
       </c>
     </row>
   </sheetData>
@@ -32297,7 +32449,7 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -32306,16 +32458,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>34.2</v>
+        <v>1145</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -32328,37 +32480,37 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I11" t="n">
-        <v>5.9</v>
+        <v>25</v>
       </c>
       <c r="J11" t="n">
-        <v>0.42</v>
+        <v>0.67</v>
       </c>
       <c r="K11" t="n">
-        <v>27.65</v>
+        <v>1000</v>
       </c>
       <c r="L11" t="n">
-        <v>-19.15</v>
+        <v>-12.66</v>
       </c>
       <c r="M11" t="n">
-        <v>25.05</v>
+        <v>838</v>
       </c>
       <c r="N11" t="n">
-        <v>-26.75</v>
+        <v>-26.81</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-26.75</v>
+        <v>-26.81</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46251</v>
+        <v>46202</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -32367,51 +32519,59 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>47.15</v>
+        <v>34.2</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>75</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="I12" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.42</v>
+      </c>
       <c r="K12" t="n">
-        <v>34.8</v>
+        <v>27.65</v>
       </c>
       <c r="L12" t="n">
-        <v>-26.19</v>
-      </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
+        <v>-19.15</v>
+      </c>
+      <c r="M12" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-26.75</v>
+      </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-26.19</v>
+        <v>-26.75</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46202</v>
+        <v>46251</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -32420,59 +32580,51 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1215</v>
+        <v>47.15</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>90</v>
-      </c>
-      <c r="I13" t="n">
-        <v>25</v>
-      </c>
-      <c r="J13" t="n">
-        <v>0.67</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="n">
-        <v>981</v>
+        <v>34.8</v>
       </c>
       <c r="L13" t="n">
-        <v>-19.26</v>
-      </c>
-      <c r="M13" t="n">
-        <v>897</v>
-      </c>
-      <c r="N13" t="n">
-        <v>-26.17</v>
-      </c>
+        <v>-26.19</v>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-26.17</v>
+        <v>-26.19</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46210</v>
+        <v>46202</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -32490,7 +32642,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1175</v>
+        <v>1215</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -32512,28 +32664,28 @@
         <v>0.67</v>
       </c>
       <c r="K14" t="n">
-        <v>1235</v>
+        <v>981</v>
       </c>
       <c r="L14" t="n">
-        <v>5.11</v>
+        <v>-19.26</v>
       </c>
       <c r="M14" t="n">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="N14" t="n">
-        <v>-24.26</v>
+        <v>-26.17</v>
       </c>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-24.26</v>
+        <v>-26.17</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -32551,7 +32703,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>71.7</v>
+        <v>72.7</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -32573,28 +32725,28 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>70.7</v>
+        <v>61</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.39</v>
+        <v>-16.09</v>
       </c>
       <c r="M15" t="n">
-        <v>56.2</v>
+        <v>54.4</v>
       </c>
       <c r="N15" t="n">
-        <v>-21.62</v>
+        <v>-25.17</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-21.62</v>
+        <v>-25.17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -32603,16 +32755,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>955</v>
+        <v>1175</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -32625,37 +32777,37 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="I16" t="n">
-        <v>14.2</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>0.4</v>
+        <v>0.67</v>
       </c>
       <c r="K16" t="n">
-        <v>671</v>
+        <v>1235</v>
       </c>
       <c r="L16" t="n">
-        <v>-29.74</v>
+        <v>5.11</v>
       </c>
       <c r="M16" t="n">
-        <v>753</v>
+        <v>890</v>
       </c>
       <c r="N16" t="n">
-        <v>-21.15</v>
+        <v>-24.26</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-21.15</v>
+        <v>-24.26</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -32664,20 +32816,20 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>158</v>
+        <v>71.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -32686,33 +32838,37 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I17" t="n">
-        <v>16.4</v>
+        <v>6.8</v>
       </c>
       <c r="J17" t="n">
-        <v>1.11</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K17" t="n">
-        <v>125.5</v>
+        <v>70.7</v>
       </c>
       <c r="L17" t="n">
-        <v>-20.57</v>
-      </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+        <v>-1.39</v>
+      </c>
+      <c r="M17" t="n">
+        <v>56.2</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-21.62</v>
+      </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-20.57</v>
+        <v>-21.62</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46244</v>
+        <v>46202</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -32721,16 +32877,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>66.7</v>
+        <v>955</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -32739,37 +32895,41 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="I18" t="n">
-        <v>6.8</v>
+        <v>14.2</v>
       </c>
       <c r="J18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="K18" t="n">
-        <v>53.9</v>
+        <v>671</v>
       </c>
       <c r="L18" t="n">
-        <v>-19.19</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+        <v>-29.74</v>
+      </c>
+      <c r="M18" t="n">
+        <v>753</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-21.15</v>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-19.19</v>
+        <v>-21.15</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46252</v>
+        <v>46218</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -32778,16 +32938,16 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>2225</v>
+        <v>895</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -32800,33 +32960,37 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="I19" t="n">
-        <v>30.7</v>
+        <v>14.2</v>
       </c>
       <c r="J19" t="n">
-        <v>0.82</v>
+        <v>0.4</v>
       </c>
       <c r="K19" t="n">
-        <v>1800</v>
+        <v>798</v>
       </c>
       <c r="L19" t="n">
-        <v>-19.1</v>
-      </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
+        <v>-10.84</v>
+      </c>
+      <c r="M19" t="n">
+        <v>718</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-19.78</v>
+      </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-19.1</v>
+        <v>-19.78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46202</v>
+        <v>46244</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -32835,16 +32999,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2340</v>
+        <v>66.7</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -32853,41 +33017,37 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I20" t="n">
-        <v>30.7</v>
+        <v>6.8</v>
       </c>
       <c r="J20" t="n">
-        <v>0.82</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>1910</v>
+        <v>53.9</v>
       </c>
       <c r="L20" t="n">
-        <v>-18.38</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1895</v>
-      </c>
-      <c r="N20" t="n">
-        <v>-19.02</v>
-      </c>
+        <v>-19.19</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-19.02</v>
+        <v>-19.19</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46226</v>
+        <v>46252</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -32896,41 +33056,41 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>6739</t>
+          <t>2345</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>竹陞科技</t>
+          <t>智邦</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1190</v>
+        <v>2225</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🟢成長未反映</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="I21" t="n">
-        <v>38.8</v>
+        <v>30.7</v>
       </c>
       <c r="J21" t="n">
-        <v>1.03</v>
+        <v>0.82</v>
       </c>
       <c r="K21" t="n">
-        <v>967</v>
+        <v>1800</v>
       </c>
       <c r="L21" t="n">
-        <v>-18.74</v>
+        <v>-19.1</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -32939,7 +33099,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-18.74</v>
+        <v>-19.1</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,16 +468,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="C2" t="n">
-        <v>43.8</v>
+        <v>45.1</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.63</v>
+        <v>-0.37</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.19</v>
+        <v>-0.72</v>
       </c>
       <c r="F2" t="n">
         <v>60.56</v>
@@ -493,22 +493,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C3" t="n">
-        <v>43</v>
+        <v>42.6</v>
       </c>
       <c r="D3" t="n">
-        <v>0.38</v>
+        <v>-0.17</v>
       </c>
       <c r="E3" t="n">
-        <v>-3.56</v>
+        <v>-3.82</v>
       </c>
       <c r="F3" t="n">
         <v>82.70999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>-54.65</v>
+        <v>-58.65</v>
       </c>
     </row>
     <row r="4">
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>331</v>
+        <v>359</v>
       </c>
       <c r="D2" t="n">
-        <v>43.8</v>
+        <v>45.1</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.63</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="3">
@@ -615,13 +615,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D3" t="n">
-        <v>43</v>
+        <v>42.6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.38</v>
+        <v>-0.17</v>
       </c>
     </row>
   </sheetData>
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R568"/>
+  <dimension ref="A1:R569"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11783,8 +11783,12 @@
       <c r="L207" t="n">
         <v>29.42</v>
       </c>
-      <c r="M207" t="inlineStr"/>
-      <c r="N207" t="inlineStr"/>
+      <c r="M207" t="n">
+        <v>2115</v>
+      </c>
+      <c r="N207" t="n">
+        <v>-58.65</v>
+      </c>
       <c r="O207" t="inlineStr"/>
       <c r="P207" t="inlineStr"/>
       <c r="Q207" t="inlineStr"/>
@@ -23749,8 +23753,12 @@
       <c r="J431" t="n">
         <v>1.11</v>
       </c>
-      <c r="K431" t="inlineStr"/>
-      <c r="L431" t="inlineStr"/>
+      <c r="K431" t="n">
+        <v>596</v>
+      </c>
+      <c r="L431" t="n">
+        <v>10.58</v>
+      </c>
       <c r="M431" t="inlineStr"/>
       <c r="N431" t="inlineStr"/>
       <c r="O431" t="inlineStr"/>
@@ -23799,8 +23807,12 @@
       <c r="J432" t="n">
         <v>1.22</v>
       </c>
-      <c r="K432" t="inlineStr"/>
-      <c r="L432" t="inlineStr"/>
+      <c r="K432" t="n">
+        <v>367</v>
+      </c>
+      <c r="L432" t="n">
+        <v>23.57</v>
+      </c>
       <c r="M432" t="inlineStr"/>
       <c r="N432" t="inlineStr"/>
       <c r="O432" t="inlineStr"/>
@@ -23849,8 +23861,12 @@
       <c r="J433" t="n">
         <v>1.36</v>
       </c>
-      <c r="K433" t="inlineStr"/>
-      <c r="L433" t="inlineStr"/>
+      <c r="K433" t="n">
+        <v>78.40000000000001</v>
+      </c>
+      <c r="L433" t="n">
+        <v>-4.85</v>
+      </c>
       <c r="M433" t="inlineStr"/>
       <c r="N433" t="inlineStr"/>
       <c r="O433" t="inlineStr"/>
@@ -23899,8 +23915,12 @@
       <c r="J434" t="n">
         <v>1.11</v>
       </c>
-      <c r="K434" t="inlineStr"/>
-      <c r="L434" t="inlineStr"/>
+      <c r="K434" t="n">
+        <v>135</v>
+      </c>
+      <c r="L434" t="n">
+        <v>9.31</v>
+      </c>
       <c r="M434" t="inlineStr"/>
       <c r="N434" t="inlineStr"/>
       <c r="O434" t="inlineStr"/>
@@ -23949,8 +23969,12 @@
       <c r="J435" t="n">
         <v>1.16</v>
       </c>
-      <c r="K435" t="inlineStr"/>
-      <c r="L435" t="inlineStr"/>
+      <c r="K435" t="n">
+        <v>243</v>
+      </c>
+      <c r="L435" t="n">
+        <v>-2.21</v>
+      </c>
       <c r="M435" t="inlineStr"/>
       <c r="N435" t="inlineStr"/>
       <c r="O435" t="inlineStr"/>
@@ -23999,8 +24023,12 @@
       <c r="J436" t="n">
         <v>1.03</v>
       </c>
-      <c r="K436" t="inlineStr"/>
-      <c r="L436" t="inlineStr"/>
+      <c r="K436" t="n">
+        <v>998</v>
+      </c>
+      <c r="L436" t="n">
+        <v>-12.84</v>
+      </c>
       <c r="M436" t="inlineStr"/>
       <c r="N436" t="inlineStr"/>
       <c r="O436" t="inlineStr"/>
@@ -24049,8 +24077,12 @@
       <c r="J437" t="n">
         <v>1.35</v>
       </c>
-      <c r="K437" t="inlineStr"/>
-      <c r="L437" t="inlineStr"/>
+      <c r="K437" t="n">
+        <v>58.3</v>
+      </c>
+      <c r="L437" t="n">
+        <v>-5.51</v>
+      </c>
       <c r="M437" t="inlineStr"/>
       <c r="N437" t="inlineStr"/>
       <c r="O437" t="inlineStr"/>
@@ -24099,8 +24131,12 @@
       <c r="J438" t="n">
         <v>0.66</v>
       </c>
-      <c r="K438" t="inlineStr"/>
-      <c r="L438" t="inlineStr"/>
+      <c r="K438" t="n">
+        <v>3315</v>
+      </c>
+      <c r="L438" t="n">
+        <v>0.15</v>
+      </c>
       <c r="M438" t="inlineStr"/>
       <c r="N438" t="inlineStr"/>
       <c r="O438" t="inlineStr"/>
@@ -24149,8 +24185,12 @@
       <c r="J439" t="n">
         <v>0.4</v>
       </c>
-      <c r="K439" t="inlineStr"/>
-      <c r="L439" t="inlineStr"/>
+      <c r="K439" t="n">
+        <v>720</v>
+      </c>
+      <c r="L439" t="n">
+        <v>2.42</v>
+      </c>
       <c r="M439" t="inlineStr"/>
       <c r="N439" t="inlineStr"/>
       <c r="O439" t="inlineStr"/>
@@ -24199,8 +24239,12 @@
       <c r="J440" t="n">
         <v>0.78</v>
       </c>
-      <c r="K440" t="inlineStr"/>
-      <c r="L440" t="inlineStr"/>
+      <c r="K440" t="n">
+        <v>2490</v>
+      </c>
+      <c r="L440" t="n">
+        <v>4.62</v>
+      </c>
       <c r="M440" t="inlineStr"/>
       <c r="N440" t="inlineStr"/>
       <c r="O440" t="inlineStr"/>
@@ -24249,8 +24293,12 @@
       <c r="J441" t="n">
         <v>0.76</v>
       </c>
-      <c r="K441" t="inlineStr"/>
-      <c r="L441" t="inlineStr"/>
+      <c r="K441" t="n">
+        <v>107.5</v>
+      </c>
+      <c r="L441" t="n">
+        <v>0</v>
+      </c>
       <c r="M441" t="inlineStr"/>
       <c r="N441" t="inlineStr"/>
       <c r="O441" t="inlineStr"/>
@@ -24299,8 +24347,12 @@
       <c r="J442" t="n">
         <v>0.59</v>
       </c>
-      <c r="K442" t="inlineStr"/>
-      <c r="L442" t="inlineStr"/>
+      <c r="K442" t="n">
+        <v>184</v>
+      </c>
+      <c r="L442" t="n">
+        <v>3.95</v>
+      </c>
       <c r="M442" t="inlineStr"/>
       <c r="N442" t="inlineStr"/>
       <c r="O442" t="inlineStr"/>
@@ -24349,8 +24401,12 @@
       <c r="J443" t="n">
         <v>0.84</v>
       </c>
-      <c r="K443" t="inlineStr"/>
-      <c r="L443" t="inlineStr"/>
+      <c r="K443" t="n">
+        <v>43.4</v>
+      </c>
+      <c r="L443" t="n">
+        <v>3.21</v>
+      </c>
       <c r="M443" t="inlineStr"/>
       <c r="N443" t="inlineStr"/>
       <c r="O443" t="inlineStr"/>
@@ -24399,8 +24455,12 @@
       <c r="J444" t="n">
         <v>0.67</v>
       </c>
-      <c r="K444" t="inlineStr"/>
-      <c r="L444" t="inlineStr"/>
+      <c r="K444" t="n">
+        <v>853</v>
+      </c>
+      <c r="L444" t="n">
+        <v>-3.72</v>
+      </c>
       <c r="M444" t="inlineStr"/>
       <c r="N444" t="inlineStr"/>
       <c r="O444" t="inlineStr"/>
@@ -24449,8 +24509,12 @@
       <c r="J445" t="n">
         <v>0.92</v>
       </c>
-      <c r="K445" t="inlineStr"/>
-      <c r="L445" t="inlineStr"/>
+      <c r="K445" t="n">
+        <v>603</v>
+      </c>
+      <c r="L445" t="n">
+        <v>18.24</v>
+      </c>
       <c r="M445" t="inlineStr"/>
       <c r="N445" t="inlineStr"/>
       <c r="O445" t="inlineStr"/>
@@ -24499,8 +24563,12 @@
       <c r="J446" t="n">
         <v>0.73</v>
       </c>
-      <c r="K446" t="inlineStr"/>
-      <c r="L446" t="inlineStr"/>
+      <c r="K446" t="n">
+        <v>171</v>
+      </c>
+      <c r="L446" t="n">
+        <v>4.91</v>
+      </c>
       <c r="M446" t="inlineStr"/>
       <c r="N446" t="inlineStr"/>
       <c r="O446" t="inlineStr"/>
@@ -24549,8 +24617,12 @@
       <c r="J447" t="n">
         <v>0.2</v>
       </c>
-      <c r="K447" t="inlineStr"/>
-      <c r="L447" t="inlineStr"/>
+      <c r="K447" t="n">
+        <v>39.15</v>
+      </c>
+      <c r="L447" t="n">
+        <v>1.16</v>
+      </c>
       <c r="M447" t="inlineStr"/>
       <c r="N447" t="inlineStr"/>
       <c r="O447" t="inlineStr"/>
@@ -24599,8 +24671,12 @@
       <c r="J448" t="n">
         <v>0.82</v>
       </c>
-      <c r="K448" t="inlineStr"/>
-      <c r="L448" t="inlineStr"/>
+      <c r="K448" t="n">
+        <v>2050</v>
+      </c>
+      <c r="L448" t="n">
+        <v>9.33</v>
+      </c>
       <c r="M448" t="inlineStr"/>
       <c r="N448" t="inlineStr"/>
       <c r="O448" t="inlineStr"/>
@@ -24649,8 +24725,12 @@
       <c r="J449" t="n">
         <v>0.75</v>
       </c>
-      <c r="K449" t="inlineStr"/>
-      <c r="L449" t="inlineStr"/>
+      <c r="K449" t="n">
+        <v>1490</v>
+      </c>
+      <c r="L449" t="n">
+        <v>14.18</v>
+      </c>
       <c r="M449" t="inlineStr"/>
       <c r="N449" t="inlineStr"/>
       <c r="O449" t="inlineStr"/>
@@ -24699,8 +24779,12 @@
       <c r="J450" t="n">
         <v>0.36</v>
       </c>
-      <c r="K450" t="inlineStr"/>
-      <c r="L450" t="inlineStr"/>
+      <c r="K450" t="n">
+        <v>89.40000000000001</v>
+      </c>
+      <c r="L450" t="n">
+        <v>-0.33</v>
+      </c>
       <c r="M450" t="inlineStr"/>
       <c r="N450" t="inlineStr"/>
       <c r="O450" t="inlineStr"/>
@@ -24749,8 +24833,12 @@
       <c r="J451" t="n">
         <v>0.71</v>
       </c>
-      <c r="K451" t="inlineStr"/>
-      <c r="L451" t="inlineStr"/>
+      <c r="K451" t="n">
+        <v>52.2</v>
+      </c>
+      <c r="L451" t="n">
+        <v>1.95</v>
+      </c>
       <c r="M451" t="inlineStr"/>
       <c r="N451" t="inlineStr"/>
       <c r="O451" t="inlineStr"/>
@@ -24799,8 +24887,12 @@
       <c r="J452" t="n">
         <v>0.49</v>
       </c>
-      <c r="K452" t="inlineStr"/>
-      <c r="L452" t="inlineStr"/>
+      <c r="K452" t="n">
+        <v>323</v>
+      </c>
+      <c r="L452" t="n">
+        <v>-2.86</v>
+      </c>
       <c r="M452" t="inlineStr"/>
       <c r="N452" t="inlineStr"/>
       <c r="O452" t="inlineStr"/>
@@ -24849,8 +24941,12 @@
       <c r="J453" t="n">
         <v>0.31</v>
       </c>
-      <c r="K453" t="inlineStr"/>
-      <c r="L453" t="inlineStr"/>
+      <c r="K453" t="n">
+        <v>187</v>
+      </c>
+      <c r="L453" t="n">
+        <v>3.31</v>
+      </c>
       <c r="M453" t="inlineStr"/>
       <c r="N453" t="inlineStr"/>
       <c r="O453" t="inlineStr"/>
@@ -24899,8 +24995,12 @@
       <c r="J454" t="n">
         <v>0.36</v>
       </c>
-      <c r="K454" t="inlineStr"/>
-      <c r="L454" t="inlineStr"/>
+      <c r="K454" t="n">
+        <v>1545</v>
+      </c>
+      <c r="L454" t="n">
+        <v>13.19</v>
+      </c>
       <c r="M454" t="inlineStr"/>
       <c r="N454" t="inlineStr"/>
       <c r="O454" t="inlineStr"/>
@@ -24945,8 +25045,12 @@
       </c>
       <c r="I455" t="inlineStr"/>
       <c r="J455" t="inlineStr"/>
-      <c r="K455" t="inlineStr"/>
-      <c r="L455" t="inlineStr"/>
+      <c r="K455" t="n">
+        <v>70.2</v>
+      </c>
+      <c r="L455" t="n">
+        <v>1.01</v>
+      </c>
       <c r="M455" t="inlineStr"/>
       <c r="N455" t="inlineStr"/>
       <c r="O455" t="inlineStr"/>
@@ -24991,8 +25095,12 @@
       </c>
       <c r="I456" t="inlineStr"/>
       <c r="J456" t="inlineStr"/>
-      <c r="K456" t="inlineStr"/>
-      <c r="L456" t="inlineStr"/>
+      <c r="K456" t="n">
+        <v>367.5</v>
+      </c>
+      <c r="L456" t="n">
+        <v>-7.66</v>
+      </c>
       <c r="M456" t="inlineStr"/>
       <c r="N456" t="inlineStr"/>
       <c r="O456" t="inlineStr"/>
@@ -25037,8 +25145,12 @@
       </c>
       <c r="I457" t="inlineStr"/>
       <c r="J457" t="inlineStr"/>
-      <c r="K457" t="inlineStr"/>
-      <c r="L457" t="inlineStr"/>
+      <c r="K457" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="L457" t="n">
+        <v>-3.17</v>
+      </c>
       <c r="M457" t="inlineStr"/>
       <c r="N457" t="inlineStr"/>
       <c r="O457" t="inlineStr"/>
@@ -25083,8 +25195,12 @@
       </c>
       <c r="I458" t="inlineStr"/>
       <c r="J458" t="inlineStr"/>
-      <c r="K458" t="inlineStr"/>
-      <c r="L458" t="inlineStr"/>
+      <c r="K458" t="n">
+        <v>191.5</v>
+      </c>
+      <c r="L458" t="n">
+        <v>-5.2</v>
+      </c>
       <c r="M458" t="inlineStr"/>
       <c r="N458" t="inlineStr"/>
       <c r="O458" t="inlineStr"/>
@@ -30527,6 +30643,52 @@
       <c r="P568" t="inlineStr"/>
       <c r="Q568" t="inlineStr"/>
       <c r="R568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>4303</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>信立</t>
+        </is>
+      </c>
+      <c r="E569" t="n">
+        <v>32.4</v>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G569" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H569" t="n">
+        <v>75</v>
+      </c>
+      <c r="I569" t="inlineStr"/>
+      <c r="J569" t="inlineStr"/>
+      <c r="K569" t="inlineStr"/>
+      <c r="L569" t="inlineStr"/>
+      <c r="M569" t="inlineStr"/>
+      <c r="N569" t="inlineStr"/>
+      <c r="O569" t="inlineStr"/>
+      <c r="P569" t="inlineStr"/>
+      <c r="Q569" t="inlineStr"/>
+      <c r="R569" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -31581,7 +31743,7 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46219</v>
+        <v>46218</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -31590,16 +31752,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6669</t>
+          <t>3231</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>緯穎</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5115</v>
+        <v>145.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -31608,37 +31770,41 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>C</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="I18" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="J18" t="n">
-        <v>0.26</v>
+        <v>0.31</v>
       </c>
       <c r="K18" t="n">
-        <v>6620</v>
+        <v>193.5</v>
       </c>
       <c r="L18" t="n">
-        <v>29.42</v>
-      </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
+        <v>32.99</v>
+      </c>
+      <c r="M18" t="n">
+        <v>187</v>
+      </c>
+      <c r="N18" t="n">
+        <v>28.52</v>
+      </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>29.42</v>
+        <v>28.52</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46218</v>
+        <v>46205</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -31647,20 +31813,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3231</t>
+          <t>2408</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>南亞科</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>145.5</v>
+        <v>407</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -31671,35 +31837,31 @@
       <c r="H19" t="n">
         <v>62</v>
       </c>
-      <c r="I19" t="n">
-        <v>10</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.31</v>
-      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
       <c r="K19" t="n">
-        <v>193.5</v>
+        <v>396.5</v>
       </c>
       <c r="L19" t="n">
-        <v>32.99</v>
+        <v>-2.58</v>
       </c>
       <c r="M19" t="n">
-        <v>187</v>
+        <v>519</v>
       </c>
       <c r="N19" t="n">
-        <v>28.52</v>
+        <v>27.52</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>28.52</v>
+        <v>27.52</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46205</v>
+        <v>46244</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -31708,55 +31870,55 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>2408</t>
+          <t>3044</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>南亞科</t>
+          <t>健鼎</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>407</v>
+        <v>401.5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>62</v>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+        <v>90</v>
+      </c>
+      <c r="I20" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.92</v>
+      </c>
       <c r="K20" t="n">
-        <v>396.5</v>
+        <v>509</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.58</v>
-      </c>
-      <c r="M20" t="n">
-        <v>519</v>
-      </c>
-      <c r="N20" t="n">
-        <v>27.52</v>
-      </c>
+        <v>26.77</v>
+      </c>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>27.52</v>
+        <v>26.77</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46244</v>
+        <v>46279</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -31765,20 +31927,20 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3044</t>
+          <t>6197</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>健鼎</t>
+          <t>佳必琪</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>401.5</v>
+        <v>297</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢成長未反映</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -31790,16 +31952,16 @@
         <v>90</v>
       </c>
       <c r="I21" t="n">
-        <v>21.2</v>
+        <v>27.5</v>
       </c>
       <c r="J21" t="n">
-        <v>0.92</v>
+        <v>1.22</v>
       </c>
       <c r="K21" t="n">
-        <v>509</v>
+        <v>367</v>
       </c>
       <c r="L21" t="n">
-        <v>26.77</v>
+        <v>23.57</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -31808,7 +31970,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>26.77</v>
+        <v>23.57</v>
       </c>
     </row>
   </sheetData>
@@ -32095,7 +32257,7 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46237</v>
+        <v>46219</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -32113,7 +32275,7 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5925</v>
+        <v>5115</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -32135,24 +32297,28 @@
         <v>0.26</v>
       </c>
       <c r="K5" t="n">
-        <v>2610</v>
+        <v>6620</v>
       </c>
       <c r="L5" t="n">
-        <v>-55.95</v>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+        <v>29.42</v>
+      </c>
+      <c r="M5" t="n">
+        <v>2115</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-58.65</v>
+      </c>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>-55.95</v>
+        <v>-58.65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46211</v>
+        <v>46237</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -32170,7 +32336,7 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5050</v>
+        <v>5925</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -32192,28 +32358,24 @@
         <v>0.26</v>
       </c>
       <c r="K6" t="n">
-        <v>6265</v>
+        <v>2610</v>
       </c>
       <c r="L6" t="n">
-        <v>24.06</v>
-      </c>
-      <c r="M6" t="n">
-        <v>2290</v>
-      </c>
-      <c r="N6" t="n">
-        <v>-54.65</v>
-      </c>
+        <v>-55.95</v>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="n">
-        <v>-54.65</v>
+        <v>-55.95</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46203</v>
+        <v>46211</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -32231,7 +32393,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4635</v>
+        <v>5050</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -32253,28 +32415,28 @@
         <v>0.26</v>
       </c>
       <c r="K7" t="n">
-        <v>4900</v>
+        <v>6265</v>
       </c>
       <c r="L7" t="n">
-        <v>5.72</v>
+        <v>24.06</v>
       </c>
       <c r="M7" t="n">
-        <v>2115</v>
+        <v>2290</v>
       </c>
       <c r="N7" t="n">
-        <v>-54.37</v>
+        <v>-54.65</v>
       </c>
       <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr"/>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="n">
-        <v>-54.37</v>
+        <v>-54.65</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46259</v>
+        <v>46203</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -32283,20 +32445,20 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>53.2</v>
+        <v>4635</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -32305,29 +32467,37 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>75</v>
-      </c>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+        <v>65</v>
+      </c>
+      <c r="I8" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.26</v>
+      </c>
       <c r="K8" t="n">
-        <v>34.05</v>
+        <v>4900</v>
       </c>
       <c r="L8" t="n">
-        <v>-36</v>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+        <v>5.72</v>
+      </c>
+      <c r="M8" t="n">
+        <v>2115</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-54.37</v>
+      </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr"/>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>
       <c r="S8" t="n">
-        <v>-36</v>
+        <v>-54.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46210</v>
+        <v>46259</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -32336,20 +32506,20 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>75.40000000000001</v>
+        <v>53.2</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -32358,32 +32528,24 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>78</v>
-      </c>
-      <c r="I9" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.5600000000000001</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="n">
-        <v>74.90000000000001</v>
+        <v>34.05</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.66</v>
-      </c>
-      <c r="M9" t="n">
-        <v>54.4</v>
-      </c>
-      <c r="N9" t="n">
-        <v>-27.85</v>
-      </c>
+        <v>-36</v>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr"/>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="n">
-        <v>-27.85</v>
+        <v>-36</v>
       </c>
     </row>
     <row r="10">
@@ -32397,16 +32559,16 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>34.15</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -32415,41 +32577,41 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="J10" t="n">
-        <v>0.42</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>27.75</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="L10" t="n">
-        <v>-18.74</v>
+        <v>-0.66</v>
       </c>
       <c r="M10" t="n">
-        <v>24.8</v>
+        <v>54.4</v>
       </c>
       <c r="N10" t="n">
-        <v>-27.38</v>
+        <v>-27.85</v>
       </c>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr"/>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr"/>
       <c r="S10" t="n">
-        <v>-27.38</v>
+        <v>-27.85</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46218</v>
+        <v>46210</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -32458,16 +32620,16 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1145</v>
+        <v>34.15</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -32480,37 +32642,37 @@
         </is>
       </c>
       <c r="H11" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="I11" t="n">
-        <v>25</v>
+        <v>5.9</v>
       </c>
       <c r="J11" t="n">
-        <v>0.67</v>
+        <v>0.42</v>
       </c>
       <c r="K11" t="n">
-        <v>1000</v>
+        <v>27.75</v>
       </c>
       <c r="L11" t="n">
-        <v>-12.66</v>
+        <v>-18.74</v>
       </c>
       <c r="M11" t="n">
-        <v>838</v>
+        <v>24.8</v>
       </c>
       <c r="N11" t="n">
-        <v>-26.81</v>
+        <v>-27.38</v>
       </c>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr"/>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr"/>
       <c r="S11" t="n">
-        <v>-26.81</v>
+        <v>-27.38</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46202</v>
+        <v>46218</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -32519,16 +32681,16 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>5519</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>隆大</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>34.2</v>
+        <v>1145</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -32541,37 +32703,37 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
-        <v>5.9</v>
+        <v>25</v>
       </c>
       <c r="J12" t="n">
-        <v>0.42</v>
+        <v>0.67</v>
       </c>
       <c r="K12" t="n">
-        <v>27.65</v>
+        <v>1000</v>
       </c>
       <c r="L12" t="n">
-        <v>-19.15</v>
+        <v>-12.66</v>
       </c>
       <c r="M12" t="n">
-        <v>25.05</v>
+        <v>838</v>
       </c>
       <c r="N12" t="n">
-        <v>-26.75</v>
+        <v>-26.81</v>
       </c>
       <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr"/>
       <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr"/>
       <c r="S12" t="n">
-        <v>-26.75</v>
+        <v>-26.81</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46251</v>
+        <v>46202</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -32580,51 +32742,59 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>4303</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>信立</t>
+          <t>隆大</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>47.15</v>
+        <v>34.2</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>🟢便宜</t>
+          <t>🟢未來便宜</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>75</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
+        <v>94</v>
+      </c>
+      <c r="I13" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.42</v>
+      </c>
       <c r="K13" t="n">
-        <v>34.8</v>
+        <v>27.65</v>
       </c>
       <c r="L13" t="n">
-        <v>-26.19</v>
-      </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+        <v>-19.15</v>
+      </c>
+      <c r="M13" t="n">
+        <v>25.05</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-26.75</v>
+      </c>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr"/>
       <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr"/>
       <c r="S13" t="n">
-        <v>-26.19</v>
+        <v>-26.75</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46202</v>
+        <v>46251</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -32633,59 +32803,51 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>4303</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>信立</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1215</v>
+        <v>47.15</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>🟢未來便宜</t>
+          <t>🟢便宜</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>90</v>
-      </c>
-      <c r="I14" t="n">
-        <v>25</v>
-      </c>
-      <c r="J14" t="n">
-        <v>0.67</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>981</v>
+        <v>34.8</v>
       </c>
       <c r="L14" t="n">
-        <v>-19.26</v>
-      </c>
-      <c r="M14" t="n">
-        <v>897</v>
-      </c>
-      <c r="N14" t="n">
-        <v>-26.17</v>
-      </c>
+        <v>-26.19</v>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr"/>
       <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr"/>
       <c r="S14" t="n">
-        <v>-26.17</v>
+        <v>-26.19</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -32694,16 +32856,16 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>72.7</v>
+        <v>1215</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -32712,41 +32874,41 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I15" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="K15" t="n">
-        <v>61</v>
+        <v>981</v>
       </c>
       <c r="L15" t="n">
-        <v>-16.09</v>
+        <v>-19.26</v>
       </c>
       <c r="M15" t="n">
-        <v>54.4</v>
+        <v>897</v>
       </c>
       <c r="N15" t="n">
-        <v>-25.17</v>
+        <v>-26.17</v>
       </c>
       <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr"/>
       <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr"/>
       <c r="S15" t="n">
-        <v>-25.17</v>
+        <v>-26.17</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46210</v>
+        <v>46218</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -32755,16 +32917,16 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>8210</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>勤誠</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1175</v>
+        <v>72.7</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -32773,41 +32935,41 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>6.8</v>
       </c>
       <c r="J16" t="n">
-        <v>0.67</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>1235</v>
+        <v>61</v>
       </c>
       <c r="L16" t="n">
-        <v>5.11</v>
+        <v>-16.09</v>
       </c>
       <c r="M16" t="n">
-        <v>890</v>
+        <v>54.4</v>
       </c>
       <c r="N16" t="n">
-        <v>-24.26</v>
+        <v>-25.17</v>
       </c>
       <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr"/>
       <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr"/>
       <c r="S16" t="n">
-        <v>-24.26</v>
+        <v>-25.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46202</v>
+        <v>46210</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -32816,16 +32978,16 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>8210</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>勤誠</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>71.7</v>
+        <v>1175</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -32834,36 +32996,36 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="I17" t="n">
-        <v>6.8</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.67</v>
       </c>
       <c r="K17" t="n">
-        <v>70.7</v>
+        <v>1235</v>
       </c>
       <c r="L17" t="n">
-        <v>-1.39</v>
+        <v>5.11</v>
       </c>
       <c r="M17" t="n">
-        <v>56.2</v>
+        <v>890</v>
       </c>
       <c r="N17" t="n">
-        <v>-21.62</v>
+        <v>-24.26</v>
       </c>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr"/>
       <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr"/>
       <c r="S17" t="n">
-        <v>-21.62</v>
+        <v>-24.26</v>
       </c>
     </row>
     <row r="18">
@@ -32877,16 +33039,16 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>6139</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>亞翔</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>955</v>
+        <v>71.7</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -32895,41 +33057,41 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="I18" t="n">
-        <v>14.2</v>
+        <v>6.8</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>671</v>
+        <v>70.7</v>
       </c>
       <c r="L18" t="n">
-        <v>-29.74</v>
+        <v>-1.39</v>
       </c>
       <c r="M18" t="n">
-        <v>753</v>
+        <v>56.2</v>
       </c>
       <c r="N18" t="n">
-        <v>-21.15</v>
+        <v>-21.62</v>
       </c>
       <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr"/>
       <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr"/>
       <c r="S18" t="n">
-        <v>-21.15</v>
+        <v>-21.62</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46218</v>
+        <v>46202</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -32947,7 +33109,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>895</v>
+        <v>955</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -32969,28 +33131,28 @@
         <v>0.4</v>
       </c>
       <c r="K19" t="n">
-        <v>798</v>
+        <v>671</v>
       </c>
       <c r="L19" t="n">
-        <v>-10.84</v>
+        <v>-29.74</v>
       </c>
       <c r="M19" t="n">
-        <v>718</v>
+        <v>753</v>
       </c>
       <c r="N19" t="n">
-        <v>-19.78</v>
+        <v>-21.15</v>
       </c>
       <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr"/>
       <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr"/>
       <c r="S19" t="n">
-        <v>-19.78</v>
+        <v>-21.15</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46244</v>
+        <v>46218</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -32999,16 +33161,16 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>5225</t>
+          <t>6139</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>東科-KY</t>
+          <t>亞翔</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>66.7</v>
+        <v>895</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -33017,37 +33179,41 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>A</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="I20" t="n">
-        <v>6.8</v>
+        <v>14.2</v>
       </c>
       <c r="J20" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="K20" t="n">
-        <v>53.9</v>
+        <v>798</v>
       </c>
       <c r="L20" t="n">
-        <v>-19.19</v>
-      </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
+        <v>-10.84</v>
+      </c>
+      <c r="M20" t="n">
+        <v>718</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-19.78</v>
+      </c>
       <c r="O20" t="inlineStr"/>
       <c r="P20" t="inlineStr"/>
       <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr"/>
       <c r="S20" t="n">
-        <v>-19.19</v>
+        <v>-19.78</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46252</v>
+        <v>46244</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -33056,16 +33222,16 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>5225</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>智邦</t>
+          <t>東科-KY</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2225</v>
+        <v>66.7</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -33074,23 +33240,23 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>B</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="I21" t="n">
-        <v>30.7</v>
+        <v>6.8</v>
       </c>
       <c r="J21" t="n">
-        <v>0.82</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>1800</v>
+        <v>53.9</v>
       </c>
       <c r="L21" t="n">
-        <v>-19.1</v>
+        <v>-19.19</v>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
@@ -33099,7 +33265,7 @@
       <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr"/>
       <c r="S21" t="n">
-        <v>-19.1</v>
+        <v>-19.19</v>
       </c>
     </row>
   </sheetData>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -468,13 +468,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="C2" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.37</v>
+        <v>-0.4</v>
       </c>
       <c r="E2" t="n">
         <v>-0.72</v>
@@ -594,13 +594,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="D2" t="n">
-        <v>45.1</v>
+        <v>45.2</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.37</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="3">
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R569"/>
+  <dimension ref="A1:R575"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25249,8 +25249,12 @@
       <c r="J459" t="n">
         <v>0.26</v>
       </c>
-      <c r="K459" t="inlineStr"/>
-      <c r="L459" t="inlineStr"/>
+      <c r="K459" t="n">
+        <v>1905</v>
+      </c>
+      <c r="L459" t="n">
+        <v>-17.71</v>
+      </c>
       <c r="M459" t="inlineStr"/>
       <c r="N459" t="inlineStr"/>
       <c r="O459" t="inlineStr"/>
@@ -25295,8 +25299,12 @@
       </c>
       <c r="I460" t="inlineStr"/>
       <c r="J460" t="inlineStr"/>
-      <c r="K460" t="inlineStr"/>
-      <c r="L460" t="inlineStr"/>
+      <c r="K460" t="n">
+        <v>50</v>
+      </c>
+      <c r="L460" t="n">
+        <v>7.3</v>
+      </c>
       <c r="M460" t="inlineStr"/>
       <c r="N460" t="inlineStr"/>
       <c r="O460" t="inlineStr"/>
@@ -30689,6 +30697,306 @@
       <c r="P569" t="inlineStr"/>
       <c r="Q569" t="inlineStr"/>
       <c r="R569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>2640</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>大車隊</t>
+        </is>
+      </c>
+      <c r="E570" t="n">
+        <v>157</v>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G570" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H570" t="n">
+        <v>97</v>
+      </c>
+      <c r="I570" t="n">
+        <v>14.7</v>
+      </c>
+      <c r="J570" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="K570" t="inlineStr"/>
+      <c r="L570" t="inlineStr"/>
+      <c r="M570" t="inlineStr"/>
+      <c r="N570" t="inlineStr"/>
+      <c r="O570" t="inlineStr"/>
+      <c r="P570" t="inlineStr"/>
+      <c r="Q570" t="inlineStr"/>
+      <c r="R570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>崇友</t>
+        </is>
+      </c>
+      <c r="E571" t="n">
+        <v>117</v>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G571" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H571" t="n">
+        <v>91</v>
+      </c>
+      <c r="I571" t="n">
+        <v>15</v>
+      </c>
+      <c r="J571" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K571" t="inlineStr"/>
+      <c r="L571" t="inlineStr"/>
+      <c r="M571" t="inlineStr"/>
+      <c r="N571" t="inlineStr"/>
+      <c r="O571" t="inlineStr"/>
+      <c r="P571" t="inlineStr"/>
+      <c r="Q571" t="inlineStr"/>
+      <c r="R571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>3029</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>零壹</t>
+        </is>
+      </c>
+      <c r="E572" t="n">
+        <v>119.5</v>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G572" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H572" t="n">
+        <v>97</v>
+      </c>
+      <c r="I572" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="J572" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K572" t="inlineStr"/>
+      <c r="L572" t="inlineStr"/>
+      <c r="M572" t="inlineStr"/>
+      <c r="N572" t="inlineStr"/>
+      <c r="O572" t="inlineStr"/>
+      <c r="P572" t="inlineStr"/>
+      <c r="Q572" t="inlineStr"/>
+      <c r="R572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>3689</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>湧德</t>
+        </is>
+      </c>
+      <c r="E573" t="n">
+        <v>117.5</v>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G573" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H573" t="n">
+        <v>94</v>
+      </c>
+      <c r="I573" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="J573" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="K573" t="inlineStr"/>
+      <c r="L573" t="inlineStr"/>
+      <c r="M573" t="inlineStr"/>
+      <c r="N573" t="inlineStr"/>
+      <c r="O573" t="inlineStr"/>
+      <c r="P573" t="inlineStr"/>
+      <c r="Q573" t="inlineStr"/>
+      <c r="R573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>5519</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>隆大</t>
+        </is>
+      </c>
+      <c r="E574" t="n">
+        <v>24.35</v>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G574" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H574" t="n">
+        <v>94</v>
+      </c>
+      <c r="I574" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="J574" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K574" t="inlineStr"/>
+      <c r="L574" t="inlineStr"/>
+      <c r="M574" t="inlineStr"/>
+      <c r="N574" t="inlineStr"/>
+      <c r="O574" t="inlineStr"/>
+      <c r="P574" t="inlineStr"/>
+      <c r="Q574" t="inlineStr"/>
+      <c r="R574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>5225</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>東科-KY</t>
+        </is>
+      </c>
+      <c r="E575" t="n">
+        <v>55</v>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G575" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H575" t="n">
+        <v>78</v>
+      </c>
+      <c r="I575" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="J575" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="K575" t="inlineStr"/>
+      <c r="L575" t="inlineStr"/>
+      <c r="M575" t="inlineStr"/>
+      <c r="N575" t="inlineStr"/>
+      <c r="O575" t="inlineStr"/>
+      <c r="P575" t="inlineStr"/>
+      <c r="Q575" t="inlineStr"/>
+      <c r="R575" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/推薦戰績.xlsx
+++ b/data/推薦戰績.xlsx
@@ -635,7 +635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R575"/>
+  <dimension ref="A1:R603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30997,6 +30997,1390 @@
       <c r="P575" t="inlineStr"/>
       <c r="Q575" t="inlineStr"/>
       <c r="R575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>5434</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>崇越</t>
+        </is>
+      </c>
+      <c r="E576" t="n">
+        <v>576</v>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G576" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H576" t="n">
+        <v>96</v>
+      </c>
+      <c r="I576" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="J576" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K576" t="inlineStr"/>
+      <c r="L576" t="inlineStr"/>
+      <c r="M576" t="inlineStr"/>
+      <c r="N576" t="inlineStr"/>
+      <c r="O576" t="inlineStr"/>
+      <c r="P576" t="inlineStr"/>
+      <c r="Q576" t="inlineStr"/>
+      <c r="R576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>6197</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>佳必琪</t>
+        </is>
+      </c>
+      <c r="E577" t="n">
+        <v>349</v>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G577" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H577" t="n">
+        <v>90</v>
+      </c>
+      <c r="I577" t="n">
+        <v>27.5</v>
+      </c>
+      <c r="J577" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="K577" t="inlineStr"/>
+      <c r="L577" t="inlineStr"/>
+      <c r="M577" t="inlineStr"/>
+      <c r="N577" t="inlineStr"/>
+      <c r="O577" t="inlineStr"/>
+      <c r="P577" t="inlineStr"/>
+      <c r="Q577" t="inlineStr"/>
+      <c r="R577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>4129</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>聯合</t>
+        </is>
+      </c>
+      <c r="E578" t="n">
+        <v>77.2</v>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G578" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H578" t="n">
+        <v>87</v>
+      </c>
+      <c r="I578" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="J578" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="K578" t="inlineStr"/>
+      <c r="L578" t="inlineStr"/>
+      <c r="M578" t="inlineStr"/>
+      <c r="N578" t="inlineStr"/>
+      <c r="O578" t="inlineStr"/>
+      <c r="P578" t="inlineStr"/>
+      <c r="Q578" t="inlineStr"/>
+      <c r="R578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>3402</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>漢科</t>
+        </is>
+      </c>
+      <c r="E579" t="n">
+        <v>132</v>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G579" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H579" t="n">
+        <v>77</v>
+      </c>
+      <c r="I579" t="n">
+        <v>16.4</v>
+      </c>
+      <c r="J579" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="K579" t="inlineStr"/>
+      <c r="L579" t="inlineStr"/>
+      <c r="M579" t="inlineStr"/>
+      <c r="N579" t="inlineStr"/>
+      <c r="O579" t="inlineStr"/>
+      <c r="P579" t="inlineStr"/>
+      <c r="Q579" t="inlineStr"/>
+      <c r="R579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>2317</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>鴻海</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>244</v>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H580" t="n">
+        <v>77</v>
+      </c>
+      <c r="I580" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="J580" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K580" t="inlineStr"/>
+      <c r="L580" t="inlineStr"/>
+      <c r="M580" t="inlineStr"/>
+      <c r="N580" t="inlineStr"/>
+      <c r="O580" t="inlineStr"/>
+      <c r="P580" t="inlineStr"/>
+      <c r="Q580" t="inlineStr"/>
+      <c r="R580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>6739</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>竹陞科技</t>
+        </is>
+      </c>
+      <c r="E581" t="n">
+        <v>960</v>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H581" t="n">
+        <v>76</v>
+      </c>
+      <c r="I581" t="n">
+        <v>38.8</v>
+      </c>
+      <c r="J581" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="K581" t="inlineStr"/>
+      <c r="L581" t="inlineStr"/>
+      <c r="M581" t="inlineStr"/>
+      <c r="N581" t="inlineStr"/>
+      <c r="O581" t="inlineStr"/>
+      <c r="P581" t="inlineStr"/>
+      <c r="Q581" t="inlineStr"/>
+      <c r="R581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>2356</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>英業達</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>59</v>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>🟢成長未反映</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H582" t="n">
+        <v>68</v>
+      </c>
+      <c r="I582" t="n">
+        <v>21.3</v>
+      </c>
+      <c r="J582" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="K582" t="inlineStr"/>
+      <c r="L582" t="inlineStr"/>
+      <c r="M582" t="inlineStr"/>
+      <c r="N582" t="inlineStr"/>
+      <c r="O582" t="inlineStr"/>
+      <c r="P582" t="inlineStr"/>
+      <c r="Q582" t="inlineStr"/>
+      <c r="R582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>3017</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>奇鋐</t>
+        </is>
+      </c>
+      <c r="E583" t="n">
+        <v>3315</v>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G583" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H583" t="n">
+        <v>100</v>
+      </c>
+      <c r="I583" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="J583" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="K583" t="inlineStr"/>
+      <c r="L583" t="inlineStr"/>
+      <c r="M583" t="inlineStr"/>
+      <c r="N583" t="inlineStr"/>
+      <c r="O583" t="inlineStr"/>
+      <c r="P583" t="inlineStr"/>
+      <c r="Q583" t="inlineStr"/>
+      <c r="R583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>6139</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>亞翔</t>
+        </is>
+      </c>
+      <c r="E584" t="n">
+        <v>677</v>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G584" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H584" t="n">
+        <v>100</v>
+      </c>
+      <c r="I584" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="J584" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="K584" t="inlineStr"/>
+      <c r="L584" t="inlineStr"/>
+      <c r="M584" t="inlineStr"/>
+      <c r="N584" t="inlineStr"/>
+      <c r="O584" t="inlineStr"/>
+      <c r="P584" t="inlineStr"/>
+      <c r="Q584" t="inlineStr"/>
+      <c r="R584" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>2330</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>台積電</t>
+        </is>
+      </c>
+      <c r="E585" t="n">
+        <v>2420</v>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G585" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H585" t="n">
+        <v>100</v>
+      </c>
+      <c r="I585" t="n">
+        <v>23.6</v>
+      </c>
+      <c r="J585" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="K585" t="inlineStr"/>
+      <c r="L585" t="inlineStr"/>
+      <c r="M585" t="inlineStr"/>
+      <c r="N585" t="inlineStr"/>
+      <c r="O585" t="inlineStr"/>
+      <c r="P585" t="inlineStr"/>
+      <c r="Q585" t="inlineStr"/>
+      <c r="R585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>1215</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>卜蜂</t>
+        </is>
+      </c>
+      <c r="E586" t="n">
+        <v>107</v>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G586" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H586" t="n">
+        <v>94</v>
+      </c>
+      <c r="I586" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="J586" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="K586" t="inlineStr"/>
+      <c r="L586" t="inlineStr"/>
+      <c r="M586" t="inlineStr"/>
+      <c r="N586" t="inlineStr"/>
+      <c r="O586" t="inlineStr"/>
+      <c r="P586" t="inlineStr"/>
+      <c r="Q586" t="inlineStr"/>
+      <c r="R586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>2753</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>八方雲集</t>
+        </is>
+      </c>
+      <c r="E587" t="n">
+        <v>184.5</v>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G587" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H587" t="n">
+        <v>94</v>
+      </c>
+      <c r="I587" t="n">
+        <v>11.4</v>
+      </c>
+      <c r="J587" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="K587" t="inlineStr"/>
+      <c r="L587" t="inlineStr"/>
+      <c r="M587" t="inlineStr"/>
+      <c r="N587" t="inlineStr"/>
+      <c r="O587" t="inlineStr"/>
+      <c r="P587" t="inlineStr"/>
+      <c r="Q587" t="inlineStr"/>
+      <c r="R587" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>2618</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>長榮航</t>
+        </is>
+      </c>
+      <c r="E588" t="n">
+        <v>43.7</v>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G588" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H588" t="n">
+        <v>92</v>
+      </c>
+      <c r="I588" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J588" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="K588" t="inlineStr"/>
+      <c r="L588" t="inlineStr"/>
+      <c r="M588" t="inlineStr"/>
+      <c r="N588" t="inlineStr"/>
+      <c r="O588" t="inlineStr"/>
+      <c r="P588" t="inlineStr"/>
+      <c r="Q588" t="inlineStr"/>
+      <c r="R588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>8210</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>勤誠</t>
+        </is>
+      </c>
+      <c r="E589" t="n">
+        <v>834</v>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G589" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H589" t="n">
+        <v>90</v>
+      </c>
+      <c r="I589" t="n">
+        <v>25</v>
+      </c>
+      <c r="J589" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="K589" t="inlineStr"/>
+      <c r="L589" t="inlineStr"/>
+      <c r="M589" t="inlineStr"/>
+      <c r="N589" t="inlineStr"/>
+      <c r="O589" t="inlineStr"/>
+      <c r="P589" t="inlineStr"/>
+      <c r="Q589" t="inlineStr"/>
+      <c r="R589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>3044</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>健鼎</t>
+        </is>
+      </c>
+      <c r="E590" t="n">
+        <v>584</v>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G590" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H590" t="n">
+        <v>90</v>
+      </c>
+      <c r="I590" t="n">
+        <v>21.2</v>
+      </c>
+      <c r="J590" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="K590" t="inlineStr"/>
+      <c r="L590" t="inlineStr"/>
+      <c r="M590" t="inlineStr"/>
+      <c r="N590" t="inlineStr"/>
+      <c r="O590" t="inlineStr"/>
+      <c r="P590" t="inlineStr"/>
+      <c r="Q590" t="inlineStr"/>
+      <c r="R590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>2421</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>建準</t>
+        </is>
+      </c>
+      <c r="E591" t="n">
+        <v>166</v>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G591" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H591" t="n">
+        <v>90</v>
+      </c>
+      <c r="I591" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J591" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="K591" t="inlineStr"/>
+      <c r="L591" t="inlineStr"/>
+      <c r="M591" t="inlineStr"/>
+      <c r="N591" t="inlineStr"/>
+      <c r="O591" t="inlineStr"/>
+      <c r="P591" t="inlineStr"/>
+      <c r="Q591" t="inlineStr"/>
+      <c r="R591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>1618</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>合機</t>
+        </is>
+      </c>
+      <c r="E592" t="n">
+        <v>39.1</v>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G592" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H592" t="n">
+        <v>84</v>
+      </c>
+      <c r="I592" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="J592" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="K592" t="inlineStr"/>
+      <c r="L592" t="inlineStr"/>
+      <c r="M592" t="inlineStr"/>
+      <c r="N592" t="inlineStr"/>
+      <c r="O592" t="inlineStr"/>
+      <c r="P592" t="inlineStr"/>
+      <c r="Q592" t="inlineStr"/>
+      <c r="R592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>2345</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>智邦</t>
+        </is>
+      </c>
+      <c r="E593" t="n">
+        <v>1980</v>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G593" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H593" t="n">
+        <v>80</v>
+      </c>
+      <c r="I593" t="n">
+        <v>30.7</v>
+      </c>
+      <c r="J593" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="K593" t="inlineStr"/>
+      <c r="L593" t="inlineStr"/>
+      <c r="M593" t="inlineStr"/>
+      <c r="N593" t="inlineStr"/>
+      <c r="O593" t="inlineStr"/>
+      <c r="P593" t="inlineStr"/>
+      <c r="Q593" t="inlineStr"/>
+      <c r="R593" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>3324</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>雙鴻</t>
+        </is>
+      </c>
+      <c r="E594" t="n">
+        <v>1425</v>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G594" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H594" t="n">
+        <v>80</v>
+      </c>
+      <c r="I594" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="J594" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="K594" t="inlineStr"/>
+      <c r="L594" t="inlineStr"/>
+      <c r="M594" t="inlineStr"/>
+      <c r="N594" t="inlineStr"/>
+      <c r="O594" t="inlineStr"/>
+      <c r="P594" t="inlineStr"/>
+      <c r="Q594" t="inlineStr"/>
+      <c r="R594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B595" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>2535</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>達欣工</t>
+        </is>
+      </c>
+      <c r="E595" t="n">
+        <v>90</v>
+      </c>
+      <c r="F595" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G595" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H595" t="n">
+        <v>79</v>
+      </c>
+      <c r="I595" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="J595" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K595" t="inlineStr"/>
+      <c r="L595" t="inlineStr"/>
+      <c r="M595" t="inlineStr"/>
+      <c r="N595" t="inlineStr"/>
+      <c r="O595" t="inlineStr"/>
+      <c r="P595" t="inlineStr"/>
+      <c r="Q595" t="inlineStr"/>
+      <c r="R595" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B596" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>4933</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>友輝</t>
+        </is>
+      </c>
+      <c r="E596" t="n">
+        <v>51.6</v>
+      </c>
+      <c r="F596" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G596" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H596" t="n">
+        <v>77</v>
+      </c>
+      <c r="I596" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="J596" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="K596" t="inlineStr"/>
+      <c r="L596" t="inlineStr"/>
+      <c r="M596" t="inlineStr"/>
+      <c r="N596" t="inlineStr"/>
+      <c r="O596" t="inlineStr"/>
+      <c r="P596" t="inlineStr"/>
+      <c r="Q596" t="inlineStr"/>
+      <c r="R596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B597" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>2382</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>廣達</t>
+        </is>
+      </c>
+      <c r="E597" t="n">
+        <v>322</v>
+      </c>
+      <c r="F597" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G597" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H597" t="n">
+        <v>65</v>
+      </c>
+      <c r="I597" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="J597" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="K597" t="inlineStr"/>
+      <c r="L597" t="inlineStr"/>
+      <c r="M597" t="inlineStr"/>
+      <c r="N597" t="inlineStr"/>
+      <c r="O597" t="inlineStr"/>
+      <c r="P597" t="inlineStr"/>
+      <c r="Q597" t="inlineStr"/>
+      <c r="R597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B598" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>3231</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>緯創</t>
+        </is>
+      </c>
+      <c r="E598" t="n">
+        <v>182.5</v>
+      </c>
+      <c r="F598" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G598" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H598" t="n">
+        <v>62</v>
+      </c>
+      <c r="I598" t="n">
+        <v>10</v>
+      </c>
+      <c r="J598" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="K598" t="inlineStr"/>
+      <c r="L598" t="inlineStr"/>
+      <c r="M598" t="inlineStr"/>
+      <c r="N598" t="inlineStr"/>
+      <c r="O598" t="inlineStr"/>
+      <c r="P598" t="inlineStr"/>
+      <c r="Q598" t="inlineStr"/>
+      <c r="R598" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B599" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>祥碩</t>
+        </is>
+      </c>
+      <c r="E599" t="n">
+        <v>1490</v>
+      </c>
+      <c r="F599" t="inlineStr">
+        <is>
+          <t>🟢未來便宜</t>
+        </is>
+      </c>
+      <c r="G599" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H599" t="n">
+        <v>60</v>
+      </c>
+      <c r="I599" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="J599" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K599" t="inlineStr"/>
+      <c r="L599" t="inlineStr"/>
+      <c r="M599" t="inlineStr"/>
+      <c r="N599" t="inlineStr"/>
+      <c r="O599" t="inlineStr"/>
+      <c r="P599" t="inlineStr"/>
+      <c r="Q599" t="inlineStr"/>
+      <c r="R599" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B600" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>5511</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>德昌</t>
+        </is>
+      </c>
+      <c r="E600" t="n">
+        <v>69.5</v>
+      </c>
+      <c r="F600" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G600" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H600" t="n">
+        <v>79</v>
+      </c>
+      <c r="I600" t="inlineStr"/>
+      <c r="J600" t="inlineStr"/>
+      <c r="K600" t="inlineStr"/>
+      <c r="L600" t="inlineStr"/>
+      <c r="M600" t="inlineStr"/>
+      <c r="N600" t="inlineStr"/>
+      <c r="O600" t="inlineStr"/>
+      <c r="P600" t="inlineStr"/>
+      <c r="Q600" t="inlineStr"/>
+      <c r="R600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B601" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>3260</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>威剛</t>
+        </is>
+      </c>
+      <c r="E601" t="n">
+        <v>360</v>
+      </c>
+      <c r="F601" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G601" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H601" t="n">
+        <v>77</v>
+      </c>
+      <c r="I601" t="inlineStr"/>
+      <c r="J601" t="inlineStr"/>
+      <c r="K601" t="inlineStr"/>
+      <c r="L601" t="inlineStr"/>
+      <c r="M601" t="inlineStr"/>
+      <c r="N601" t="inlineStr"/>
+      <c r="O601" t="inlineStr"/>
+      <c r="P601" t="inlineStr"/>
+      <c r="Q601" t="inlineStr"/>
+      <c r="R601" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B602" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>3188</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>鑫龍騰</t>
+        </is>
+      </c>
+      <c r="E602" t="n">
+        <v>22.9</v>
+      </c>
+      <c r="F602" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G602" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H602" t="n">
+        <v>77</v>
+      </c>
+      <c r="I602" t="inlineStr"/>
+      <c r="J602" t="inlineStr"/>
+      <c r="K602" t="inlineStr"/>
+      <c r="L602" t="inlineStr"/>
+      <c r="M602" t="inlineStr"/>
+      <c r="N602" t="inlineStr"/>
+      <c r="O602" t="inlineStr"/>
+      <c r="P602" t="inlineStr"/>
+      <c r="Q602" t="inlineStr"/>
+      <c r="R602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B603" t="inlineStr">
+        <is>
+          <t>TW</t>
+        </is>
+      </c>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>8271</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>宇瞻</t>
+        </is>
+      </c>
+      <c r="E603" t="n">
+        <v>187</v>
+      </c>
+      <c r="F603" t="inlineStr">
+        <is>
+          <t>🟢便宜</t>
+        </is>
+      </c>
+      <c r="G603" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H603" t="n">
+        <v>69</v>
+      </c>
+      <c r="I603" t="inlineStr"/>
+      <c r="J603" t="inlineStr"/>
+      <c r="K603" t="inlineStr"/>
+      <c r="L603" t="inlineStr"/>
+      <c r="M603" t="inlineStr"/>
+      <c r="N603" t="inlineStr"/>
+      <c r="O603" t="inlineStr"/>
+      <c r="P603" t="inlineStr"/>
+      <c r="Q603" t="inlineStr"/>
+      <c r="R603" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
